--- a/Schulauswahl/Adressen_Rollout_Umfrage_erweitert_300_reine_Grundschulen.xlsx
+++ b/Schulauswahl/Adressen_Rollout_Umfrage_erweitert_300_reine_Grundschulen.xlsx
@@ -661,6 +661,11 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>poststelle3115@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J3" s="9">
         <f>"Schule("&amp;B3&amp;")@schule.hessen.de"</f>
         <v/>
@@ -926,6 +931,11 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>poststelle3135@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J7" s="9">
         <f>"Schule("&amp;B7&amp;")@schule.hessen.de"</f>
         <v/>
@@ -1191,6 +1201,11 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>poststelle3158@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J11" s="9">
         <f>"Schule("&amp;B11&amp;")@schule.hessen.de"</f>
         <v/>
@@ -1307,6 +1322,11 @@
           <t>Heike Schley</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>poststelle3171@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J13" s="9">
         <f>"Schule("&amp;B13&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2116,6 +2136,11 @@
           <t>Frau Rothkirch</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>poststelle3215@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J24" s="9">
         <f>"Schule("&amp;B24&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2309,6 +2334,11 @@
           <t>Ivonne Köhler</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>poststelle3227@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J27" s="9">
         <f>"Schule("&amp;B27&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2343,6 +2373,11 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>poststelle3230@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J28" s="9">
         <f>"Schule("&amp;B28&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2377,6 +2412,11 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>poststelle3231@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J29" s="9">
         <f>"Schule("&amp;B29&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2411,6 +2451,11 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>poststelle3232@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J30" s="9">
         <f>"Schule("&amp;B30&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2450,6 +2495,11 @@
           <t>Birgit Schuster</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>poststelle3240@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J31" s="9">
         <f>"Schule("&amp;B31&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2484,6 +2534,11 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>poststelle3244@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J32" s="9">
         <f>"Schule("&amp;B32&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2518,6 +2573,11 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>poststelle3256@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J33" s="9">
         <f>"Schule("&amp;B33&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2629,6 +2689,11 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>poststelle3264@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J35" s="9">
         <f>"Schule("&amp;B35&amp;")@schule.hessen.de"</f>
         <v/>
@@ -2740,6 +2805,11 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>poststelle3275@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J37" s="9">
         <f>"Schule("&amp;B37&amp;")@schule.hessen.de"</f>
         <v/>
@@ -3280,6 +3350,11 @@
           <t>Frau Stefanie Grimm</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>poststelle3351@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J45" s="9">
         <f>"Schule("&amp;B45&amp;")@schule.hessen.de"</f>
         <v/>
@@ -3550,6 +3625,11 @@
           <t>Brigitte Wirth-Löffler</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>poststelle3364@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J49" s="9">
         <f>"Schule("&amp;B49&amp;")@schule.hessen.de"</f>
         <v/>
@@ -3931,6 +4011,11 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>poststelle3426@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J55" s="9">
         <f>"Schule("&amp;B55&amp;")@schule.hessen.de"</f>
         <v/>
@@ -4119,6 +4204,11 @@
           <t>DaDi</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>poststelle3521@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J58" s="9">
         <f>"Schule("&amp;B58&amp;")@schule.hessen.de"</f>
         <v/>
@@ -4389,6 +4479,11 @@
           <t>Stefanie Lange</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>poststelle3542@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J62" s="9">
         <f>"Schule("&amp;B62&amp;")@schule.hessen.de"</f>
         <v/>
@@ -4423,6 +4518,11 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>poststelle3553@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J63" s="9">
         <f>"Schule("&amp;B63&amp;")@schule.hessen.de"</f>
         <v/>
@@ -5189,6 +5289,11 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>poststelle3629@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J74" s="9">
         <f>"Schule("&amp;B74&amp;")@schule.hessen.de"</f>
         <v/>
@@ -5459,6 +5564,11 @@
           <t>Frau Weidner</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>poststelle3648@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J78" s="9">
         <f>"Schule("&amp;B78&amp;")@schule.hessen.de"</f>
         <v/>
@@ -5840,6 +5950,11 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>poststelle3700@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J84" s="9">
         <f>"Schule("&amp;B84&amp;")@schule.hessen.de"</f>
         <v/>
@@ -6105,6 +6220,11 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>poststelle3744@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J88" s="9">
         <f>"Schule("&amp;B88&amp;")@schule.hessen.de"</f>
         <v/>
@@ -6216,6 +6336,11 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>poststelle3761@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J90" s="9">
         <f>"Schule("&amp;B90&amp;")@schule.hessen.de"</f>
         <v/>
@@ -6717,6 +6842,11 @@
           <t>Anjali Nienhuys</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>poststelle3825@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J97" s="9">
         <f>"Schule("&amp;B97&amp;")@schule.hessen.de"</f>
         <v/>
@@ -6751,6 +6881,11 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>poststelle3828@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J98" s="9">
         <f>"Schule("&amp;B98&amp;")@schule.hessen.de"</f>
         <v/>
@@ -6790,6 +6925,11 @@
           <t>Frau Christine Zuber</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>poststelle3830@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J99" s="9">
         <f>"Schule("&amp;B99&amp;")@schule.hessen.de"</f>
         <v/>
@@ -6829,6 +6969,11 @@
           <t>Frau Carolin Seidenkranz</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>poststelle3831@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J100" s="9">
         <f>"Schule("&amp;B100&amp;")@schule.hessen.de"</f>
         <v/>
@@ -7017,6 +7162,11 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>poststelle3850@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J103" s="9">
         <f>"Schule("&amp;B103&amp;")@schule.hessen.de"</f>
         <v/>
@@ -7095,6 +7245,11 @@
           <t>Herr Dr. Alexander Karney</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>poststelle3861@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J105" s="9">
         <f>"Schule("&amp;B105&amp;")@schule.hessen.de"</f>
         <v/>
@@ -7283,6 +7438,11 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>poststelle3886@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J108" s="9">
         <f>"Schule("&amp;B108&amp;")@schule.hessen.de"</f>
         <v/>
@@ -7471,6 +7631,11 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>poststelle3894@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J111" s="9">
         <f>"Schule("&amp;B111&amp;")@schule.hessen.de"</f>
         <v/>
@@ -8622,6 +8787,11 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>poststelle4008@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J127" s="9">
         <f>"Schule("&amp;B127&amp;")@schule.hessen.de"</f>
         <v/>
@@ -8656,6 +8826,11 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>poststelle4012@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J128" s="9">
         <f>"Schule("&amp;B128&amp;")@schule.hessen.de"</f>
         <v/>
@@ -8690,6 +8865,11 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>poststelle4018@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J129" s="9">
         <f>"Schule("&amp;B129&amp;")@schule.hessen.de"</f>
         <v/>
@@ -8729,6 +8909,11 @@
           <t>Frau Carolin Titze</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>poststelle4020@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J130" s="9">
         <f>"Schule("&amp;B130&amp;")@schule.hessen.de"</f>
         <v/>
@@ -8763,6 +8948,11 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>poststelle4022@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J131" s="9">
         <f>"Schule("&amp;B131&amp;")@schule.hessen.de"</f>
         <v/>
@@ -8951,6 +9141,11 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>poststelle4047@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J134" s="9">
         <f>"Schule("&amp;B134&amp;")@schule.hessen.de"</f>
         <v/>
@@ -9062,6 +9257,11 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>poststelle4052@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J136" s="9">
         <f>"Schule("&amp;B136&amp;")@schule.hessen.de"</f>
         <v/>
@@ -9255,6 +9455,11 @@
           <t>Stefanie Michler</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>poststelle4054@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J139" s="9">
         <f>"Schule("&amp;B139&amp;")@schule.hessen.de"</f>
         <v/>
@@ -9366,6 +9571,11 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>poststelle4061@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J141" s="9">
         <f>"Schule("&amp;B141&amp;")@schule.hessen.de"</f>
         <v/>
@@ -9477,6 +9687,11 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>poststelle4075@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J143" s="9">
         <f>"Schule("&amp;B143&amp;")@schule.hessen.de"</f>
         <v/>
@@ -10286,6 +10501,11 @@
           <t>Julia Nolte</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>poststelle4176@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J154" s="9">
         <f>"Schule("&amp;B154&amp;")@schule.hessen.de"</f>
         <v/>
@@ -10628,6 +10848,11 @@
           <t>DaDi</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>poststelle4211@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J159" s="9">
         <f>"Schule("&amp;B159&amp;")@schule.hessen.de"</f>
         <v/>
@@ -10783,6 +11008,11 @@
           <t>Herr Peter Schubert</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>poststelle4220@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J162" s="9">
         <f>"Schule("&amp;B162&amp;")@schule.hessen.de"</f>
         <v/>
@@ -10894,6 +11124,11 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>poststelle4226@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J164" s="9">
         <f>"Schule("&amp;B164&amp;")@schule.hessen.de"</f>
         <v/>
@@ -11005,6 +11240,11 @@
           <t>DaDi</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>poststelle4243@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J166" s="9">
         <f>"Schule("&amp;B166&amp;")@schule.hessen.de"</f>
         <v/>
@@ -11121,6 +11361,11 @@
           <t>Tina Diehl-Schranz</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>poststelle4250@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J168" s="9">
         <f>"Schule("&amp;B168&amp;")@schule.hessen.de"</f>
         <v/>
@@ -12272,6 +12517,11 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>poststelle4384@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J184" s="9">
         <f>"Schule("&amp;B184&amp;")@schule.hessen.de"</f>
         <v/>
@@ -13192,6 +13442,11 @@
           <t>Frau Saner</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>poststelle4800@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J197" s="9">
         <f>"Schule("&amp;B197&amp;")@schule.hessen.de"</f>
         <v/>
@@ -13226,6 +13481,11 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>poststelle4801@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J198" s="9">
         <f>"Schule("&amp;B198&amp;")@schule.hessen.de"</f>
         <v/>
@@ -13799,6 +14059,11 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>poststelle7104@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J206" s="9">
         <f>"Schule("&amp;B206&amp;")@schule.hessen.de"</f>
         <v/>
@@ -13838,6 +14103,11 @@
           <t>Matthias Wirth</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>poststelle7105@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J207" s="9">
         <f>"Schule("&amp;B207&amp;")@schule.hessen.de"</f>
         <v/>
@@ -13877,6 +14147,11 @@
           <t>Michael Krönung</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>poststelle7106@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J208" s="9">
         <f>"Schule("&amp;B208&amp;")@schule.hessen.de"</f>
         <v/>
@@ -13911,6 +14186,11 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>poststelle7113@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J209" s="9">
         <f>"Schule("&amp;B209&amp;")@schule.hessen.de"</f>
         <v/>
@@ -13950,6 +14230,11 @@
           <t>Uta Klose</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>poststelle7121@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J210" s="9">
         <f>"Schule("&amp;B210&amp;")@schule.hessen.de"</f>
         <v/>
@@ -13984,6 +14269,11 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>poststelle7124@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J211" s="9">
         <f>"Schule("&amp;B211&amp;")@schule.hessen.de"</f>
         <v/>
@@ -14057,6 +14347,11 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>poststelle7127@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J213" s="9">
         <f>"Schule("&amp;B213&amp;")@schule.hessen.de"</f>
         <v/>
@@ -14635,6 +14930,11 @@
           <t>Herr Matthias Lange</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>poststelle7150@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J221" s="9">
         <f>"Schule("&amp;B221&amp;")@schule.hessen.de"</f>
         <v/>
@@ -14823,6 +15123,11 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>poststelle7162@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J224" s="9">
         <f>"Schule("&amp;B224&amp;")@schule.hessen.de"</f>
         <v/>
@@ -15088,6 +15393,11 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>poststelle7215@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J228" s="9">
         <f>"Schule("&amp;B228&amp;")@schule.hessen.de"</f>
         <v/>
@@ -15199,6 +15509,11 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>poststelle7233@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J230" s="9">
         <f>"Schule("&amp;B230&amp;")@schule.hessen.de"</f>
         <v/>
@@ -15431,6 +15746,11 @@
           <t>Frau Romy Körber</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>poststelle7260@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J234" s="9">
         <f>"Schule("&amp;B234&amp;")@schule.hessen.de"</f>
         <v/>
@@ -15778,6 +16098,11 @@
           <t>Claudia Meyer</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>poststelle7306@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J239" s="9">
         <f>"Schule("&amp;B239&amp;")@schule.hessen.de"</f>
         <v/>
@@ -16274,6 +16599,11 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>poststelle7395@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J246" s="9">
         <f>"Schule("&amp;B246&amp;")@schule.hessen.de"</f>
         <v/>
@@ -16539,6 +16869,11 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>poststelle7409@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J250" s="9">
         <f>"Schule("&amp;B250&amp;")@schule.hessen.de"</f>
         <v/>
@@ -16886,6 +17221,11 @@
           <t>Frau Sabine Hübler</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>poststelle7469@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J255" s="9">
         <f>"Schule("&amp;B255&amp;")@schule.hessen.de"</f>
         <v/>
@@ -17151,6 +17491,11 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>poststelle7517@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J259" s="9">
         <f>"Schule("&amp;B259&amp;")@schule.hessen.de"</f>
         <v/>
@@ -17185,6 +17530,11 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>poststelle7519@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J260" s="9">
         <f>"Schule("&amp;B260&amp;")@schule.hessen.de"</f>
         <v/>
@@ -17301,6 +17651,11 @@
           <t>Frau Ines Franke</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>poststelle7537@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J262" s="9">
         <f>"Schule("&amp;B262&amp;")@schule.hessen.de"</f>
         <v/>
@@ -17335,6 +17690,11 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>poststelle7542@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J263" s="9">
         <f>"Schule("&amp;B263&amp;")@schule.hessen.de"</f>
         <v/>
@@ -18260,7 +18620,11 @@
           <t>Barbara Kaufmann-Wechsel</t>
         </is>
       </c>
-      <c r="I276" s="4" t="n"/>
+      <c r="I276" s="4" t="inlineStr">
+        <is>
+          <t>poststelle7656@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J276" s="9">
         <f>"Schule("&amp;B276&amp;")@schule.hessen.de"</f>
         <v/>
@@ -18372,7 +18736,11 @@
           <t>MR</t>
         </is>
       </c>
-      <c r="I278" s="4" t="n"/>
+      <c r="I278" s="4" t="inlineStr">
+        <is>
+          <t>poststelle7663@schule.hessen.de</t>
+        </is>
+      </c>
       <c r="J278" s="9">
         <f>"Schule("&amp;B278&amp;")@schule.hessen.de"</f>
         <v/>
@@ -18854,6 +19222,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>poststelle3333@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J285">
+        <f>"Schule("&amp;B285&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="B286" t="n">
@@ -18869,6 +19246,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>poststelle3386@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J286">
+        <f>"Schule("&amp;B286&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="B287" t="n">
@@ -18884,6 +19270,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>poststelle4230@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J287">
+        <f>"Schule("&amp;B287&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="B288" t="n">
@@ -18899,6 +19294,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>poststelle3602@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J288">
+        <f>"Schule("&amp;B288&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="B289" t="n">
@@ -18914,6 +19318,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>poststelle3334@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J289">
+        <f>"Schule("&amp;B289&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="B290" t="n">
@@ -18929,6 +19342,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>poststelle3384@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J290">
+        <f>"Schule("&amp;B290&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="B291" t="n">
@@ -18944,6 +19366,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>poststelle3510@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J291">
+        <f>"Schule("&amp;B291&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="B292" t="n">
@@ -18959,6 +19390,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>poststelle3325@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J292">
+        <f>"Schule("&amp;B292&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="B293" t="n">
@@ -18974,6 +19414,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>poststelle3344@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J293">
+        <f>"Schule("&amp;B293&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="B294" t="n">
@@ -18989,6 +19438,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>poststelle3379@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J294">
+        <f>"Schule("&amp;B294&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="B295" t="n">
@@ -19004,6 +19462,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>poststelle3605@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J295">
+        <f>"Schule("&amp;B295&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="B296" t="n">
@@ -19019,6 +19486,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>poststelle3385@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J296">
+        <f>"Schule("&amp;B296&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="B297" t="n">
@@ -19034,6 +19510,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>poststelle4237@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J297">
+        <f>"Schule("&amp;B297&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="B298" t="n">
@@ -19049,6 +19534,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>poststelle3370@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J298">
+        <f>"Schule("&amp;B298&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="B299" t="n">
@@ -19064,6 +19558,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>poststelle3348@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J299">
+        <f>"Schule("&amp;B299&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="B300" t="n">
@@ -19079,6 +19582,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>poststelle3614@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J300">
+        <f>"Schule("&amp;B300&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="B301" t="n">
@@ -19094,6 +19606,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>poststelle3599@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J301">
+        <f>"Schule("&amp;B301&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="B302" t="n">
@@ -19109,6 +19630,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>poststelle3323@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J302">
+        <f>"Schule("&amp;B302&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="B303" t="n">
@@ -19124,6 +19654,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>poststelle3390@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J303">
+        <f>"Schule("&amp;B303&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="B304" t="n">
@@ -19139,6 +19678,15 @@
           <t>BOW</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>poststelle3608@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J304">
+        <f>"Schule("&amp;B304&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="B305" t="n">
@@ -19154,6 +19702,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>poststelle3539@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J305">
+        <f>"Schule("&amp;B305&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="B306" t="n">
@@ -19169,6 +19726,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>poststelle3509@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J306">
+        <f>"Schule("&amp;B306&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="B307" t="n">
@@ -19184,6 +19750,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>poststelle3482@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J307">
+        <f>"Schule("&amp;B307&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="B308" t="n">
@@ -19199,6 +19774,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>poststelle3525@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J308">
+        <f>"Schule("&amp;B308&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="B309" t="n">
@@ -19214,6 +19798,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>poststelle3502@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J309">
+        <f>"Schule("&amp;B309&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="B310" t="n">
@@ -19229,6 +19822,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>poststelle3201@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J310">
+        <f>"Schule("&amp;B310&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="B311" t="n">
@@ -19244,6 +19846,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>poststelle3489@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J311">
+        <f>"Schule("&amp;B311&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="B312" t="n">
@@ -19259,6 +19870,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>poststelle4338@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J312">
+        <f>"Schule("&amp;B312&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="B313" t="n">
@@ -19274,6 +19894,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>poststelle3224@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J313">
+        <f>"Schule("&amp;B313&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="B314" t="n">
@@ -19289,6 +19918,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>poststelle4253@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J314">
+        <f>"Schule("&amp;B314&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="B315" t="n">
@@ -19304,6 +19942,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>poststelle3511@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J315">
+        <f>"Schule("&amp;B315&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="B316" t="n">
@@ -19319,6 +19966,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>poststelle4188@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J316">
+        <f>"Schule("&amp;B316&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="B317" t="n">
@@ -19334,6 +19990,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>poststelle3481@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J317">
+        <f>"Schule("&amp;B317&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="B318" t="n">
@@ -19349,6 +20014,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>poststelle3480@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J318">
+        <f>"Schule("&amp;B318&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="B319" t="n">
@@ -19364,6 +20038,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>poststelle4284@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J319">
+        <f>"Schule("&amp;B319&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="B320" t="n">
@@ -19379,6 +20062,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>poststelle4336@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J320">
+        <f>"Schule("&amp;B320&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="B321" t="n">
@@ -19394,6 +20086,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>poststelle3523@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J321">
+        <f>"Schule("&amp;B321&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="B322" t="n">
@@ -19409,6 +20110,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>poststelle3528@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J322">
+        <f>"Schule("&amp;B322&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="B323" t="n">
@@ -19424,6 +20134,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>poststelle4191@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J323">
+        <f>"Schule("&amp;B323&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="B324" t="n">
@@ -19439,6 +20158,15 @@
           <t>DADI</t>
         </is>
       </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>poststelle4231@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J324">
+        <f>"Schule("&amp;B324&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="B325" t="n">
@@ -19454,6 +20182,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>poststelle3172@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J325">
+        <f>"Schule("&amp;B325&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="B326" t="n">
@@ -19469,6 +20206,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>poststelle4262@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J326">
+        <f>"Schule("&amp;B326&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="B327" t="n">
@@ -19484,6 +20230,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>poststelle3666@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J327">
+        <f>"Schule("&amp;B327&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="B328" t="n">
@@ -19499,6 +20254,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>poststelle3166@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J328">
+        <f>"Schule("&amp;B328&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="B329" t="n">
@@ -19514,6 +20278,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>poststelle3131@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J329">
+        <f>"Schule("&amp;B329&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="B330" t="n">
@@ -19529,6 +20302,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>poststelle3167@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J330">
+        <f>"Schule("&amp;B330&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="B331" t="n">
@@ -19544,6 +20326,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>poststelle3104@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J331">
+        <f>"Schule("&amp;B331&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="B332" t="n">
@@ -19559,6 +20350,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>poststelle3168@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J332">
+        <f>"Schule("&amp;B332&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="B333" t="n">
@@ -19574,6 +20374,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>poststelle3154@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J333">
+        <f>"Schule("&amp;B333&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="B334" t="n">
@@ -19589,6 +20398,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>poststelle3118@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J334">
+        <f>"Schule("&amp;B334&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="B335" t="n">
@@ -19604,6 +20422,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>poststelle4381@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J335">
+        <f>"Schule("&amp;B335&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="B336" t="n">
@@ -19619,6 +20446,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>poststelle3153@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J336">
+        <f>"Schule("&amp;B336&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="B337" t="n">
@@ -19634,6 +20470,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>poststelle4396@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J337">
+        <f>"Schule("&amp;B337&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="B338" t="n">
@@ -19649,6 +20494,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>poststelle3107@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J338">
+        <f>"Schule("&amp;B338&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="B339" t="n">
@@ -19664,6 +20518,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>poststelle4301@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J339">
+        <f>"Schule("&amp;B339&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="B340" t="n">
@@ -19679,6 +20542,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>poststelle3165@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J340">
+        <f>"Schule("&amp;B340&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="B341" t="n">
@@ -19694,6 +20566,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>poststelle3122@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J341">
+        <f>"Schule("&amp;B341&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="B342" t="n">
@@ -19709,6 +20590,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>poststelle3111@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J342">
+        <f>"Schule("&amp;B342&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="B343" t="n">
@@ -19724,6 +20614,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>poststelle3155@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J343">
+        <f>"Schule("&amp;B343&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="B344" t="n">
@@ -19739,6 +20638,15 @@
           <t>F</t>
         </is>
       </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>poststelle3116@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J344">
+        <f>"Schule("&amp;B344&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="B345" t="n">
@@ -19754,6 +20662,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>poststelle7356@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J345">
+        <f>"Schule("&amp;B345&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="B346" t="n">
@@ -19769,6 +20686,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>poststelle7258@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J346">
+        <f>"Schule("&amp;B346&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="B347" t="n">
@@ -19784,6 +20710,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>poststelle7254@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J347">
+        <f>"Schule("&amp;B347&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="B348" t="n">
@@ -19799,6 +20734,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>poststelle7263@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J348">
+        <f>"Schule("&amp;B348&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="B349" t="n">
@@ -19814,6 +20758,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>poststelle7238@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J349">
+        <f>"Schule("&amp;B349&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="B350" t="n">
@@ -19829,6 +20782,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>poststelle7237@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J350">
+        <f>"Schule("&amp;B350&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="B351" t="n">
@@ -19844,6 +20806,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>poststelle7367@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J351">
+        <f>"Schule("&amp;B351&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="B352" t="n">
@@ -19859,6 +20830,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>poststelle7283@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J352">
+        <f>"Schule("&amp;B352&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="B353" t="n">
@@ -19874,6 +20854,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>poststelle7285@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J353">
+        <f>"Schule("&amp;B353&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="B354" t="n">
@@ -19889,6 +20878,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>poststelle7234@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J354">
+        <f>"Schule("&amp;B354&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="B355" t="n">
@@ -19904,6 +20902,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>poststelle7245@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J355">
+        <f>"Schule("&amp;B355&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="B356" t="n">
@@ -19919,6 +20926,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>poststelle7290@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J356">
+        <f>"Schule("&amp;B356&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="B357" t="n">
@@ -19934,6 +20950,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>poststelle7100@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J357">
+        <f>"Schule("&amp;B357&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="B358" t="n">
@@ -19949,6 +20974,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>poststelle7236@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J358">
+        <f>"Schule("&amp;B358&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="B359" t="n">
@@ -19964,6 +20998,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>poststelle7288@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J359">
+        <f>"Schule("&amp;B359&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="B360" t="n">
@@ -19979,6 +21022,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>poststelle7294@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J360">
+        <f>"Schule("&amp;B360&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="B361" t="n">
@@ -19994,6 +21046,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>poststelle7373@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J361">
+        <f>"Schule("&amp;B361&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="B362" t="n">
@@ -20009,6 +21070,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>poststelle7661@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J362">
+        <f>"Schule("&amp;B362&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="B363" t="n">
@@ -20024,6 +21094,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>poststelle7281@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J363">
+        <f>"Schule("&amp;B363&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="B364" t="n">
@@ -20039,6 +21118,15 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>poststelle7248@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J364">
+        <f>"Schule("&amp;B364&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="B365" t="n">
@@ -20054,6 +21142,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>poststelle3782@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J365">
+        <f>"Schule("&amp;B365&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="B366" t="n">
@@ -20069,6 +21166,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>poststelle3932@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J366">
+        <f>"Schule("&amp;B366&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="B367" t="n">
@@ -20084,6 +21190,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>poststelle3934@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J367">
+        <f>"Schule("&amp;B367&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="B368" t="n">
@@ -20099,6 +21214,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>poststelle3796@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J368">
+        <f>"Schule("&amp;B368&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="B369" t="n">
@@ -20114,6 +21238,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>poststelle3813@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J369">
+        <f>"Schule("&amp;B369&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="B370" t="n">
@@ -20129,6 +21262,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>poststelle3933@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J370">
+        <f>"Schule("&amp;B370&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="B371" t="n">
@@ -20144,6 +21286,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>poststelle3936@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J371">
+        <f>"Schule("&amp;B371&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="B372" t="n">
@@ -20159,6 +21310,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>poststelle4196@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J372">
+        <f>"Schule("&amp;B372&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="B373" t="n">
@@ -20174,6 +21334,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>poststelle3780@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J373">
+        <f>"Schule("&amp;B373&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="B374" t="n">
@@ -20189,6 +21358,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>poststelle3956@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J374">
+        <f>"Schule("&amp;B374&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="B375" t="n">
@@ -20204,6 +21382,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>poststelle3787@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J375">
+        <f>"Schule("&amp;B375&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="B376" t="n">
@@ -20219,6 +21406,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>poststelle3794@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J376">
+        <f>"Schule("&amp;B376&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="377">
       <c r="B377" t="n">
@@ -20234,6 +21430,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>poststelle3921@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J377">
+        <f>"Schule("&amp;B377&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="378">
       <c r="B378" t="n">
@@ -20249,6 +21454,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>poststelle3789@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J378">
+        <f>"Schule("&amp;B378&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="B379" t="n">
@@ -20264,6 +21478,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>poststelle3812@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J379">
+        <f>"Schule("&amp;B379&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="B380" t="n">
@@ -20279,6 +21502,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>poststelle4308@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J380">
+        <f>"Schule("&amp;B380&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="B381" t="n">
@@ -20294,6 +21526,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>poststelle3930@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J381">
+        <f>"Schule("&amp;B381&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="B382" t="n">
@@ -20309,6 +21550,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>poststelle3795@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J382">
+        <f>"Schule("&amp;B382&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="B383" t="n">
@@ -20324,6 +21574,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>poststelle3792@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J383">
+        <f>"Schule("&amp;B383&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="B384" t="n">
@@ -20339,6 +21598,15 @@
           <t>GGMT</t>
         </is>
       </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>poststelle3776@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J384">
+        <f>"Schule("&amp;B384&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="B385" t="n">
@@ -20354,6 +21622,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>poststelle3869@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J385">
+        <f>"Schule("&amp;B385&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="B386" t="n">
@@ -20369,6 +21646,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>poststelle3862@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J386">
+        <f>"Schule("&amp;B386&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="B387" t="n">
@@ -20384,6 +21670,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>poststelle3767@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J387">
+        <f>"Schule("&amp;B387&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="B388" t="n">
@@ -20399,6 +21694,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>poststelle3772@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J388">
+        <f>"Schule("&amp;B388&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="B389" t="n">
@@ -20414,6 +21718,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>poststelle4285@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J389">
+        <f>"Schule("&amp;B389&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="390">
       <c r="B390" t="n">
@@ -20429,6 +21742,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>poststelle4157@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J390">
+        <f>"Schule("&amp;B390&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="391">
       <c r="B391" t="n">
@@ -20444,6 +21766,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>poststelle3304@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J391">
+        <f>"Schule("&amp;B391&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="392">
       <c r="B392" t="n">
@@ -20459,6 +21790,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>poststelle3301@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J392">
+        <f>"Schule("&amp;B392&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="393">
       <c r="B393" t="n">
@@ -20474,6 +21814,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>poststelle3764@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J393">
+        <f>"Schule("&amp;B393&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="394">
       <c r="B394" t="n">
@@ -20489,6 +21838,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>poststelle3724@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J394">
+        <f>"Schule("&amp;B394&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="395">
       <c r="B395" t="n">
@@ -20504,6 +21862,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>poststelle4178@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J395">
+        <f>"Schule("&amp;B395&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="396">
       <c r="B396" t="n">
@@ -20519,6 +21886,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>poststelle3228@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J396">
+        <f>"Schule("&amp;B396&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="397">
       <c r="B397" t="n">
@@ -20534,6 +21910,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>poststelle4222@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J397">
+        <f>"Schule("&amp;B397&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="398">
       <c r="B398" t="n">
@@ -20549,6 +21934,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>poststelle3311@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J398">
+        <f>"Schule("&amp;B398&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="399">
       <c r="B399" t="n">
@@ -20564,6 +21958,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>poststelle3733@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J399">
+        <f>"Schule("&amp;B399&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="400">
       <c r="B400" t="n">
@@ -20579,6 +21982,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>poststelle4181@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J400">
+        <f>"Schule("&amp;B400&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="401">
       <c r="B401" t="n">
@@ -20594,6 +22006,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>poststelle3229@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J401">
+        <f>"Schule("&amp;B401&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="402">
       <c r="B402" t="n">
@@ -20609,6 +22030,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>poststelle3735@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J402">
+        <f>"Schule("&amp;B402&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="403">
       <c r="B403" t="n">
@@ -20624,6 +22054,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>poststelle3740@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J403">
+        <f>"Schule("&amp;B403&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="404">
       <c r="B404" t="n">
@@ -20639,6 +22078,15 @@
           <t>GIVB</t>
         </is>
       </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>poststelle3758@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J404">
+        <f>"Schule("&amp;B404&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="405">
       <c r="B405" t="n">
@@ -20654,6 +22102,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>poststelle7522@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J405">
+        <f>"Schule("&amp;B405&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="406">
       <c r="B406" t="n">
@@ -20669,6 +22126,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>poststelle7512@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J406">
+        <f>"Schule("&amp;B406&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="407">
       <c r="B407" t="n">
@@ -20684,6 +22150,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>poststelle7508@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J407">
+        <f>"Schule("&amp;B407&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="408">
       <c r="B408" t="n">
@@ -20699,6 +22174,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>poststelle7607@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J408">
+        <f>"Schule("&amp;B408&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="409">
       <c r="B409" t="n">
@@ -20714,6 +22198,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>poststelle7308@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J409">
+        <f>"Schule("&amp;B409&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="410">
       <c r="B410" t="n">
@@ -20729,6 +22222,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>poststelle7330@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J410">
+        <f>"Schule("&amp;B410&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="411">
       <c r="B411" t="n">
@@ -20744,6 +22246,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>poststelle7146@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J411">
+        <f>"Schule("&amp;B411&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="412">
       <c r="B412" t="n">
@@ -20759,6 +22270,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>poststelle7579@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J412">
+        <f>"Schule("&amp;B412&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="413">
       <c r="B413" t="n">
@@ -20774,6 +22294,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>poststelle7510@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J413">
+        <f>"Schule("&amp;B413&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="414">
       <c r="B414" t="n">
@@ -20789,6 +22318,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>poststelle7331@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J414">
+        <f>"Schule("&amp;B414&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="415">
       <c r="B415" t="n">
@@ -20804,6 +22342,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>poststelle7524@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J415">
+        <f>"Schule("&amp;B415&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="416">
       <c r="B416" t="n">
@@ -20819,6 +22366,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>poststelle7583@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J416">
+        <f>"Schule("&amp;B416&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="417">
       <c r="B417" t="n">
@@ -20834,6 +22390,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>poststelle7158@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J417">
+        <f>"Schule("&amp;B417&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="418">
       <c r="B418" t="n">
@@ -20849,6 +22414,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>poststelle7334@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J418">
+        <f>"Schule("&amp;B418&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="419">
       <c r="B419" t="n">
@@ -20864,6 +22438,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>poststelle7300@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J419">
+        <f>"Schule("&amp;B419&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="420">
       <c r="B420" t="n">
@@ -20879,6 +22462,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>poststelle7485@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J420">
+        <f>"Schule("&amp;B420&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="421">
       <c r="B421" t="n">
@@ -20894,6 +22486,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>poststelle7582@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J421">
+        <f>"Schule("&amp;B421&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="422">
       <c r="B422" t="n">
@@ -20909,6 +22510,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>poststelle7299@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J422">
+        <f>"Schule("&amp;B422&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="423">
       <c r="B423" t="n">
@@ -20924,6 +22534,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>poststelle7658@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J423">
+        <f>"Schule("&amp;B423&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="424">
       <c r="B424" t="n">
@@ -20939,6 +22558,15 @@
           <t>HRWM</t>
         </is>
       </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>poststelle7148@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J424">
+        <f>"Schule("&amp;B424&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="425">
       <c r="B425" t="n">
@@ -20954,6 +22582,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>poststelle3454@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J425">
+        <f>"Schule("&amp;B425&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="426">
       <c r="B426" t="n">
@@ -20969,6 +22606,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>poststelle4871@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J426">
+        <f>"Schule("&amp;B426&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="427">
       <c r="B427" t="n">
@@ -20984,6 +22630,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>poststelle3650@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J427">
+        <f>"Schule("&amp;B427&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="428">
       <c r="B428" t="n">
@@ -20999,6 +22654,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>poststelle4873@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J428">
+        <f>"Schule("&amp;B428&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="429">
       <c r="B429" t="n">
@@ -21014,6 +22678,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>poststelle3440@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J429">
+        <f>"Schule("&amp;B429&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="430">
       <c r="B430" t="n">
@@ -21029,6 +22702,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>poststelle3660@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J430">
+        <f>"Schule("&amp;B430&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="431">
       <c r="B431" t="n">
@@ -21044,6 +22726,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>poststelle3439@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J431">
+        <f>"Schule("&amp;B431&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="432">
       <c r="B432" t="n">
@@ -21059,6 +22750,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>poststelle3628@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J432">
+        <f>"Schule("&amp;B432&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="433">
       <c r="B433" t="n">
@@ -21074,6 +22774,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>poststelle4014@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J433">
+        <f>"Schule("&amp;B433&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="434">
       <c r="B434" t="n">
@@ -21089,6 +22798,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>poststelle4009@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J434">
+        <f>"Schule("&amp;B434&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="435">
       <c r="B435" t="n">
@@ -21104,6 +22822,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>poststelle3672@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J435">
+        <f>"Schule("&amp;B435&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="436">
       <c r="B436" t="n">
@@ -21119,6 +22846,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>poststelle4000@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J436">
+        <f>"Schule("&amp;B436&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="437">
       <c r="B437" t="n">
@@ -21134,6 +22870,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>poststelle4282@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J437">
+        <f>"Schule("&amp;B437&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="438">
       <c r="B438" t="n">
@@ -21149,6 +22894,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>poststelle3630@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J438">
+        <f>"Schule("&amp;B438&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="439">
       <c r="B439" t="n">
@@ -21164,6 +22918,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>poststelle3671@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J439">
+        <f>"Schule("&amp;B439&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="440">
       <c r="B440" t="n">
@@ -21179,6 +22942,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>poststelle4261@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J440">
+        <f>"Schule("&amp;B440&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="441">
       <c r="B441" t="n">
@@ -21194,6 +22966,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>poststelle4246@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J441">
+        <f>"Schule("&amp;B441&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="442">
       <c r="B442" t="n">
@@ -21209,6 +22990,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>poststelle3998@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J442">
+        <f>"Schule("&amp;B442&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="443">
       <c r="B443" t="n">
@@ -21224,6 +23014,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>poststelle3631@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J443">
+        <f>"Schule("&amp;B443&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="444">
       <c r="B444" t="n">
@@ -21239,6 +23038,15 @@
           <t>HTW</t>
         </is>
       </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>poststelle4013@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J444">
+        <f>"Schule("&amp;B444&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="445">
       <c r="B445" t="n">
@@ -21254,6 +23062,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>poststelle7354@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J445">
+        <f>"Schule("&amp;B445&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="446">
       <c r="B446" t="n">
@@ -21269,6 +23086,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>poststelle7350@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J446">
+        <f>"Schule("&amp;B446&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="447">
       <c r="B447" t="n">
@@ -21284,6 +23110,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>poststelle7340@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J447">
+        <f>"Schule("&amp;B447&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="448">
       <c r="B448" t="n">
@@ -21299,6 +23134,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>poststelle7403@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J448">
+        <f>"Schule("&amp;B448&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="449">
       <c r="B449" t="n">
@@ -21314,6 +23158,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>poststelle7355@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J449">
+        <f>"Schule("&amp;B449&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="450">
       <c r="B450" t="n">
@@ -21329,6 +23182,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>poststelle7593@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J450">
+        <f>"Schule("&amp;B450&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="451">
       <c r="B451" t="n">
@@ -21344,6 +23206,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>poststelle7351@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J451">
+        <f>"Schule("&amp;B451&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="452">
       <c r="B452" t="n">
@@ -21359,6 +23230,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>poststelle7588@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J452">
+        <f>"Schule("&amp;B452&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="453">
       <c r="B453" t="n">
@@ -21374,6 +23254,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>poststelle7404@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J453">
+        <f>"Schule("&amp;B453&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="454">
       <c r="B454" t="n">
@@ -21389,6 +23278,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>poststelle7406@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J454">
+        <f>"Schule("&amp;B454&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="455">
       <c r="B455" t="n">
@@ -21404,6 +23302,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>poststelle7646@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J455">
+        <f>"Schule("&amp;B455&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="456">
       <c r="B456" t="n">
@@ -21419,6 +23326,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>poststelle7388@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J456">
+        <f>"Schule("&amp;B456&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="457">
       <c r="B457" t="n">
@@ -21434,6 +23350,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>poststelle7660@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J457">
+        <f>"Schule("&amp;B457&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="458">
       <c r="B458" t="n">
@@ -21449,6 +23374,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>poststelle7650@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J458">
+        <f>"Schule("&amp;B458&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="459">
       <c r="B459" t="n">
@@ -21464,6 +23398,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>poststelle7109@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J459">
+        <f>"Schule("&amp;B459&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="460">
       <c r="B460" t="n">
@@ -21479,6 +23422,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>poststelle7135@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J460">
+        <f>"Schule("&amp;B460&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="461">
       <c r="B461" t="n">
@@ -21494,6 +23446,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>poststelle7132@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J461">
+        <f>"Schule("&amp;B461&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="462">
       <c r="B462" t="n">
@@ -21509,6 +23470,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>poststelle7112@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J462">
+        <f>"Schule("&amp;B462&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="463">
       <c r="B463" t="n">
@@ -21524,6 +23494,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>poststelle7382@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J463">
+        <f>"Schule("&amp;B463&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="464">
       <c r="B464" t="n">
@@ -21539,6 +23518,15 @@
           <t>KS</t>
         </is>
       </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>poststelle7662@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J464">
+        <f>"Schule("&amp;B464&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="465">
       <c r="B465" t="n">
@@ -21554,6 +23542,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>poststelle3592@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J465">
+        <f>"Schule("&amp;B465&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="466">
       <c r="B466" t="n">
@@ -21569,6 +23566,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>poststelle4143@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J466">
+        <f>"Schule("&amp;B466&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="467">
       <c r="B467" t="n">
@@ -21584,6 +23590,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>poststelle3980@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J467">
+        <f>"Schule("&amp;B467&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="468">
       <c r="B468" t="n">
@@ -21599,6 +23614,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>poststelle4158@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J468">
+        <f>"Schule("&amp;B468&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="469">
       <c r="B469" t="n">
@@ -21614,6 +23638,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>poststelle4161@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J469">
+        <f>"Schule("&amp;B469&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="470">
       <c r="B470" t="n">
@@ -21629,6 +23662,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>poststelle3912@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J470">
+        <f>"Schule("&amp;B470&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="471">
       <c r="B471" t="n">
@@ -21644,6 +23686,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>poststelle4155@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J471">
+        <f>"Schule("&amp;B471&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="472">
       <c r="B472" t="n">
@@ -21659,6 +23710,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>poststelle4148@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J472">
+        <f>"Schule("&amp;B472&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="473">
       <c r="B473" t="n">
@@ -21674,6 +23734,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>poststelle3897@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J473">
+        <f>"Schule("&amp;B473&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="474">
       <c r="B474" t="n">
@@ -21689,6 +23758,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>poststelle4142@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J474">
+        <f>"Schule("&amp;B474&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="475">
       <c r="B475" t="n">
@@ -21704,6 +23782,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>poststelle3551@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J475">
+        <f>"Schule("&amp;B475&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="476">
       <c r="B476" t="n">
@@ -21719,6 +23806,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>poststelle3993@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J476">
+        <f>"Schule("&amp;B476&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="477">
       <c r="B477" t="n">
@@ -21734,6 +23830,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>poststelle3961@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J477">
+        <f>"Schule("&amp;B477&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="478">
       <c r="B478" t="n">
@@ -21749,6 +23854,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>poststelle3558@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J478">
+        <f>"Schule("&amp;B478&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="479">
       <c r="B479" t="n">
@@ -21764,6 +23878,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>poststelle4160@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J479">
+        <f>"Schule("&amp;B479&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="480">
       <c r="B480" t="n">
@@ -21779,6 +23902,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>poststelle3891@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J480">
+        <f>"Schule("&amp;B480&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="481">
       <c r="B481" t="n">
@@ -21794,6 +23926,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>poststelle4173@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J481">
+        <f>"Schule("&amp;B481&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="482">
       <c r="B482" t="n">
@@ -21809,6 +23950,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>poststelle4162@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J482">
+        <f>"Schule("&amp;B482&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="483">
       <c r="B483" t="n">
@@ -21824,6 +23974,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>poststelle3572@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J483">
+        <f>"Schule("&amp;B483&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="484">
       <c r="B484" t="n">
@@ -21839,6 +23998,15 @@
           <t>LDLM</t>
         </is>
       </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>poststelle3578@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J484">
+        <f>"Schule("&amp;B484&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="485">
       <c r="B485" t="n">
@@ -21854,6 +24022,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>poststelle4088@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J485">
+        <f>"Schule("&amp;B485&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="486">
       <c r="B486" t="n">
@@ -21869,6 +24046,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>poststelle3722@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J486">
+        <f>"Schule("&amp;B486&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="487">
       <c r="B487" t="n">
@@ -21884,6 +24070,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>poststelle3698@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J487">
+        <f>"Schule("&amp;B487&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="488">
       <c r="B488" t="n">
@@ -21899,6 +24094,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>poststelle3697@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J488">
+        <f>"Schule("&amp;B488&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="489">
       <c r="B489" t="n">
@@ -21914,6 +24118,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>poststelle3708@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J489">
+        <f>"Schule("&amp;B489&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="490">
       <c r="B490" t="n">
@@ -21929,6 +24142,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>poststelle3714@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J490">
+        <f>"Schule("&amp;B490&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="491">
       <c r="B491" t="n">
@@ -21944,6 +24166,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>poststelle4936@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J491">
+        <f>"Schule("&amp;B491&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="492">
       <c r="B492" t="n">
@@ -21959,6 +24190,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>poststelle4931@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J492">
+        <f>"Schule("&amp;B492&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="493">
       <c r="B493" t="n">
@@ -21974,6 +24214,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>poststelle3710@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J493">
+        <f>"Schule("&amp;B493&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="494">
       <c r="B494" t="n">
@@ -21989,6 +24238,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>poststelle3703@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J494">
+        <f>"Schule("&amp;B494&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="495">
       <c r="B495" t="n">
@@ -22004,6 +24262,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>poststelle3834@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J495">
+        <f>"Schule("&amp;B495&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="496">
       <c r="B496" t="n">
@@ -22019,6 +24286,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>poststelle3849@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J496">
+        <f>"Schule("&amp;B496&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="497">
       <c r="B497" t="n">
@@ -22034,6 +24310,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>poststelle3845@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J497">
+        <f>"Schule("&amp;B497&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="498">
       <c r="B498" t="n">
@@ -22049,6 +24334,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>poststelle4939@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J498">
+        <f>"Schule("&amp;B498&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="499">
       <c r="B499" t="n">
@@ -22064,6 +24358,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>poststelle3236@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J499">
+        <f>"Schule("&amp;B499&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="500">
       <c r="B500" t="n">
@@ -22079,6 +24382,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>poststelle3843@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J500">
+        <f>"Schule("&amp;B500&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="501">
       <c r="B501" t="n">
@@ -22094,6 +24406,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>poststelle3840@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J501">
+        <f>"Schule("&amp;B501&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="502">
       <c r="B502" t="n">
@@ -22109,6 +24430,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>poststelle4212@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J502">
+        <f>"Schule("&amp;B502&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="503">
       <c r="B503" t="n">
@@ -22124,6 +24454,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>poststelle3826@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J503">
+        <f>"Schule("&amp;B503&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="504">
       <c r="B504" t="n">
@@ -22139,6 +24478,15 @@
           <t>MKK</t>
         </is>
       </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>poststelle3239@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J504">
+        <f>"Schule("&amp;B504&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="505">
       <c r="B505" t="n">
@@ -22154,6 +24502,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>poststelle7419@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J505">
+        <f>"Schule("&amp;B505&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="506">
       <c r="B506" t="n">
@@ -22169,6 +24526,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>poststelle7411@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J506">
+        <f>"Schule("&amp;B506&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="507">
       <c r="B507" t="n">
@@ -22184,6 +24550,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>poststelle3411@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J507">
+        <f>"Schule("&amp;B507&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="508">
       <c r="B508" t="n">
@@ -22199,6 +24574,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>poststelle3416@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J508">
+        <f>"Schule("&amp;B508&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="509">
       <c r="B509" t="n">
@@ -22214,6 +24598,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>poststelle3400@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J509">
+        <f>"Schule("&amp;B509&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="510">
       <c r="B510" t="n">
@@ -22229,6 +24622,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>poststelle7430@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J510">
+        <f>"Schule("&amp;B510&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="511">
       <c r="B511" t="n">
@@ -22244,6 +24646,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>poststelle7470@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J511">
+        <f>"Schule("&amp;B511&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="512">
       <c r="B512" t="n">
@@ -22259,6 +24670,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>poststelle7442@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J512">
+        <f>"Schule("&amp;B512&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="513">
       <c r="B513" t="n">
@@ -22274,6 +24694,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>poststelle7418@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J513">
+        <f>"Schule("&amp;B513&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="514">
       <c r="B514" t="n">
@@ -22289,6 +24718,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>poststelle3393@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J514">
+        <f>"Schule("&amp;B514&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="515">
       <c r="B515" t="n">
@@ -22304,6 +24742,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>poststelle3401@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J515">
+        <f>"Schule("&amp;B515&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="516">
       <c r="B516" t="n">
@@ -22319,6 +24766,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>poststelle7427@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J516">
+        <f>"Schule("&amp;B516&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="517">
       <c r="B517" t="n">
@@ -22334,6 +24790,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>poststelle7422@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J517">
+        <f>"Schule("&amp;B517&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="518">
       <c r="B518" t="n">
@@ -22349,6 +24814,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>poststelle7443@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J518">
+        <f>"Schule("&amp;B518&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="519">
       <c r="B519" t="n">
@@ -22364,6 +24838,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>poststelle7138@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J519">
+        <f>"Schule("&amp;B519&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="520">
       <c r="B520" t="n">
@@ -22379,6 +24862,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>poststelle3414@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J520">
+        <f>"Schule("&amp;B520&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="521">
       <c r="B521" t="n">
@@ -22394,6 +24886,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>poststelle7464@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J521">
+        <f>"Schule("&amp;B521&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="522">
       <c r="B522" t="n">
@@ -22409,6 +24910,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>poststelle7417@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J522">
+        <f>"Schule("&amp;B522&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="523">
       <c r="B523" t="n">
@@ -22424,6 +24934,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>poststelle7457@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J523">
+        <f>"Schule("&amp;B523&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="524">
       <c r="B524" t="n">
@@ -22439,6 +24958,15 @@
           <t>MR</t>
         </is>
       </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>poststelle7426@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J524">
+        <f>"Schule("&amp;B524&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="525">
       <c r="B525" t="n">
@@ -22454,6 +24982,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>poststelle4442@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J525">
+        <f>"Schule("&amp;B525&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="526">
       <c r="B526" t="n">
@@ -22469,6 +25006,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>poststelle4026@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J526">
+        <f>"Schule("&amp;B526&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="527">
       <c r="B527" t="n">
@@ -22484,6 +25030,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>poststelle4201@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J527">
+        <f>"Schule("&amp;B527&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="528">
       <c r="B528" t="n">
@@ -22499,6 +25054,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>poststelle4040@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J528">
+        <f>"Schule("&amp;B528&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="529">
       <c r="B529" t="n">
@@ -22514,6 +25078,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>poststelle4249@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J529">
+        <f>"Schule("&amp;B529&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="530">
       <c r="B530" t="n">
@@ -22529,6 +25102,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>poststelle4027@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J530">
+        <f>"Schule("&amp;B530&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="531">
       <c r="B531" t="n">
@@ -22544,6 +25126,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>poststelle4060@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J531">
+        <f>"Schule("&amp;B531&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="532">
       <c r="B532" t="n">
@@ -22559,6 +25150,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>poststelle3537@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J532">
+        <f>"Schule("&amp;B532&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="533">
       <c r="B533" t="n">
@@ -22574,6 +25174,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>poststelle4036@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J533">
+        <f>"Schule("&amp;B533&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="534">
       <c r="B534" t="n">
@@ -22589,6 +25198,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>poststelle4023@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J534">
+        <f>"Schule("&amp;B534&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="535">
       <c r="B535" t="n">
@@ -22604,6 +25222,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>poststelle4209@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J535">
+        <f>"Schule("&amp;B535&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="536">
       <c r="B536" t="n">
@@ -22619,6 +25246,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>poststelle4056@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J536">
+        <f>"Schule("&amp;B536&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="537">
       <c r="B537" t="n">
@@ -22634,6 +25270,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>poststelle3255@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J537">
+        <f>"Schule("&amp;B537&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="538">
       <c r="B538" t="n">
@@ -22649,6 +25294,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>poststelle3242@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J538">
+        <f>"Schule("&amp;B538&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="539">
       <c r="B539" t="n">
@@ -22664,6 +25318,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>poststelle3246@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J539">
+        <f>"Schule("&amp;B539&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="540">
       <c r="B540" t="n">
@@ -22679,6 +25342,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>poststelle4032@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J540">
+        <f>"Schule("&amp;B540&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="541">
       <c r="B541" t="n">
@@ -22694,6 +25366,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>poststelle4251@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J541">
+        <f>"Schule("&amp;B541&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="542">
       <c r="B542" t="n">
@@ -22709,6 +25390,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>poststelle3243@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J542">
+        <f>"Schule("&amp;B542&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="543">
       <c r="B543" t="n">
@@ -22724,6 +25414,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>poststelle4278@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J543">
+        <f>"Schule("&amp;B543&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="544">
       <c r="B544" t="n">
@@ -22739,6 +25438,15 @@
           <t>OF</t>
         </is>
       </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>poststelle4030@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J544">
+        <f>"Schule("&amp;B544&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="545">
       <c r="B545" t="n">
@@ -22754,6 +25462,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>poststelle4110@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J545">
+        <f>"Schule("&amp;B545&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="546">
       <c r="B546" t="n">
@@ -22769,6 +25486,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>poststelle3196@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J546">
+        <f>"Schule("&amp;B546&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="547">
       <c r="B547" t="n">
@@ -22784,6 +25510,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>poststelle3188@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J547">
+        <f>"Schule("&amp;B547&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="548">
       <c r="B548" t="n">
@@ -22799,6 +25534,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>poststelle3187@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J548">
+        <f>"Schule("&amp;B548&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="549">
       <c r="B549" t="n">
@@ -22814,6 +25558,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>poststelle3293@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J549">
+        <f>"Schule("&amp;B549&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="550">
       <c r="B550" t="n">
@@ -22829,6 +25582,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>poststelle4109@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J550">
+        <f>"Schule("&amp;B550&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="551">
       <c r="B551" t="n">
@@ -22844,6 +25606,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>poststelle4111@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J551">
+        <f>"Schule("&amp;B551&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="552">
       <c r="B552" t="n">
@@ -22859,6 +25630,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>poststelle4116@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J552">
+        <f>"Schule("&amp;B552&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="553">
       <c r="B553" t="n">
@@ -22874,6 +25654,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>poststelle3184@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J553">
+        <f>"Schule("&amp;B553&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="554">
       <c r="B554" t="n">
@@ -22889,6 +25678,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>poststelle4256@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J554">
+        <f>"Schule("&amp;B554&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="555">
       <c r="B555" t="n">
@@ -22904,6 +25702,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>poststelle3286@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J555">
+        <f>"Schule("&amp;B555&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="556">
       <c r="B556" t="n">
@@ -22919,6 +25726,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>poststelle3259@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J556">
+        <f>"Schule("&amp;B556&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="557">
       <c r="B557" t="n">
@@ -22934,6 +25750,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>poststelle4125@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J557">
+        <f>"Schule("&amp;B557&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="558">
       <c r="B558" t="n">
@@ -22949,6 +25774,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>poststelle3186@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J558">
+        <f>"Schule("&amp;B558&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="559">
       <c r="B559" t="n">
@@ -22964,6 +25798,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>poststelle3285@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J559">
+        <f>"Schule("&amp;B559&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="560">
       <c r="B560" t="n">
@@ -22979,6 +25822,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>poststelle3282@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J560">
+        <f>"Schule("&amp;B560&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="561">
       <c r="B561" t="n">
@@ -22994,6 +25846,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>poststelle3277@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J561">
+        <f>"Schule("&amp;B561&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="562">
       <c r="B562" t="n">
@@ -23009,6 +25870,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>poststelle3266@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J562">
+        <f>"Schule("&amp;B562&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="563">
       <c r="B563" t="n">
@@ -23024,6 +25894,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>poststelle3294@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J563">
+        <f>"Schule("&amp;B563&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="564">
       <c r="B564" t="n">
@@ -23039,6 +25918,15 @@
           <t>RTWI</t>
         </is>
       </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>poststelle3271@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J564">
+        <f>"Schule("&amp;B564&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="565">
       <c r="B565" t="n">
@@ -23054,6 +25942,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>poststelle7516@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J565">
+        <f>"Schule("&amp;B565&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="566">
       <c r="B566" t="n">
@@ -23069,6 +25966,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>poststelle7490@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J566">
+        <f>"Schule("&amp;B566&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="567">
       <c r="B567" t="n">
@@ -23084,6 +25990,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>poststelle7218@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J567">
+        <f>"Schule("&amp;B567&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="568">
       <c r="B568" t="n">
@@ -23099,6 +26014,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>poststelle7196@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J568">
+        <f>"Schule("&amp;B568&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="569">
       <c r="B569" t="n">
@@ -23114,6 +26038,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>poststelle7475@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J569">
+        <f>"Schule("&amp;B569&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="570">
       <c r="B570" t="n">
@@ -23129,6 +26062,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>poststelle7630@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J570">
+        <f>"Schule("&amp;B570&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="571">
       <c r="B571" t="n">
@@ -23144,6 +26086,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>poststelle7184@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J571">
+        <f>"Schule("&amp;B571&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="572">
       <c r="B572" t="n">
@@ -23159,6 +26110,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>poststelle7232@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J572">
+        <f>"Schule("&amp;B572&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="573">
       <c r="B573" t="n">
@@ -23174,6 +26134,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>poststelle7186@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J573">
+        <f>"Schule("&amp;B573&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="574">
       <c r="B574" t="n">
@@ -23189,6 +26158,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>poststelle7621@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J574">
+        <f>"Schule("&amp;B574&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="575">
       <c r="B575" t="n">
@@ -23204,6 +26182,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>poststelle7221@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J575">
+        <f>"Schule("&amp;B575&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="576">
       <c r="B576" t="n">
@@ -23219,6 +26206,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>poststelle7568@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J576">
+        <f>"Schule("&amp;B576&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="577">
       <c r="B577" t="n">
@@ -23234,6 +26230,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>poststelle7173@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J577">
+        <f>"Schule("&amp;B577&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="578">
       <c r="B578" t="n">
@@ -23249,6 +26254,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>poststelle7679@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J578">
+        <f>"Schule("&amp;B578&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="579">
       <c r="B579" t="n">
@@ -23264,6 +26278,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>poststelle7664@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J579">
+        <f>"Schule("&amp;B579&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="580">
       <c r="B580" t="n">
@@ -23279,6 +26302,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>poststelle7670@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J580">
+        <f>"Schule("&amp;B580&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="581">
       <c r="B581" t="n">
@@ -23294,6 +26326,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>poststelle7556@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J581">
+        <f>"Schule("&amp;B581&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="582">
       <c r="B582" t="n">
@@ -23309,6 +26350,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>poststelle7205@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J582">
+        <f>"Schule("&amp;B582&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="583">
       <c r="B583" t="n">
@@ -23324,6 +26374,15 @@
           <t>SEWF</t>
         </is>
       </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>poststelle7216@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J583">
+        <f>"Schule("&amp;B583&amp;")@schule.hessen.de"</f>
+        <v/>
+      </c>
     </row>
     <row r="584">
       <c r="B584" t="n">
@@ -23338,6 +26397,15 @@
         <is>
           <t>SEWF</t>
         </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>poststelle7482@schule.hessen.de</t>
+        </is>
+      </c>
+      <c r="J584">
+        <f>"Schule("&amp;B584&amp;")@schule.hessen.de"</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Schulauswahl/Adressen_Rollout_Umfrage_erweitert_300_reine_Grundschulen.xlsx
+++ b/Schulauswahl/Adressen_Rollout_Umfrage_erweitert_300_reine_Grundschulen.xlsx
@@ -517,9 +517,10 @@
           <t>poststelle3105@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J1" s="9">
-        <f>"Schule("&amp;B1&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3105)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K1" t="n">
         <v>18</v>
@@ -594,9 +595,10 @@
           <t>poststelle3106@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J2" s="9">
-        <f>"Schule("&amp;B2&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3106)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K2" t="n">
         <v>23</v>
@@ -666,9 +668,10 @@
           <t>poststelle3115@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J3" s="9">
-        <f>"Schule("&amp;B3&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3115)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -710,9 +713,10 @@
           <t>poststelle3117@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J4" s="9">
-        <f>"Schule("&amp;B4&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3117)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K4" t="n">
         <v>9</v>
@@ -787,9 +791,10 @@
           <t>poststelle3123@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J5" s="9">
-        <f>"Schule("&amp;B5&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3123)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K5" t="n">
         <v>16</v>
@@ -864,9 +869,10 @@
           <t>poststelle3127@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J6" s="9">
-        <f>"Schule("&amp;B6&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3127)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K6" t="n">
         <v>13</v>
@@ -936,9 +942,10 @@
           <t>poststelle3135@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J7" s="9">
-        <f>"Schule("&amp;B7&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3135)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -980,9 +987,10 @@
           <t>poststelle3137@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J8" s="9">
-        <f>"Schule("&amp;B8&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3137)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K8" t="n">
         <v>17</v>
@@ -1057,9 +1065,10 @@
           <t>poststelle3150@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J9" s="9">
-        <f>"Schule("&amp;B9&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3150)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K9" t="n">
         <v>13</v>
@@ -1134,9 +1143,10 @@
           <t>poststelle3152@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J10" s="9">
-        <f>"Schule("&amp;B10&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3152)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K10" t="n">
         <v>16</v>
@@ -1206,9 +1216,10 @@
           <t>poststelle3158@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J11" s="9">
-        <f>"Schule("&amp;B11&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3158)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1250,9 +1261,10 @@
           <t>poststelle3170@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J12" s="9">
-        <f>"Schule("&amp;B12&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3170)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K12" t="n">
         <v>19</v>
@@ -1327,9 +1339,10 @@
           <t>poststelle3171@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J13" s="9">
-        <f>"Schule("&amp;B13&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3171)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1371,9 +1384,10 @@
           <t>poststelle3174@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J14" s="9">
-        <f>"Schule("&amp;B14&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3174)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K14" t="n">
         <v>16</v>
@@ -1448,9 +1462,10 @@
           <t>poststelle3176@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J15" s="9">
-        <f>"Schule("&amp;B15&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3176)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K15" t="n">
         <v>6</v>
@@ -1525,9 +1540,10 @@
           <t>poststelle3177@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J16" s="9">
-        <f>"Schule("&amp;B16&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3177)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K16" t="n">
         <v>4</v>
@@ -1602,9 +1618,10 @@
           <t>poststelle3189@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J17" s="9">
-        <f>"Schule("&amp;B17&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3189)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K17" t="n">
         <v>12</v>
@@ -1679,9 +1696,10 @@
           <t>poststelle3191@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J18" s="9">
-        <f>"Schule("&amp;B18&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3191)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K18" t="n">
         <v>5</v>
@@ -1756,9 +1774,10 @@
           <t>poststelle3205@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J19" s="9">
-        <f>"Schule("&amp;B19&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3205)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K19" t="n">
         <v>24</v>
@@ -1833,9 +1852,10 @@
           <t>poststelle3209@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J20" s="9">
-        <f>"Schule("&amp;B20&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3209)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K20" t="n">
         <v>13</v>
@@ -1910,9 +1930,10 @@
           <t>poststelle3211@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J21" s="9">
-        <f>"Schule("&amp;B21&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3211)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K21" t="n">
         <v>16</v>
@@ -1987,9 +2008,10 @@
           <t>poststelle3212@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J22" s="9">
-        <f>"Schule("&amp;B22&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3212)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K22" t="n">
         <v>14</v>
@@ -2064,9 +2086,10 @@
           <t>poststelle3213@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J23" s="9">
-        <f>"Schule("&amp;B23&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3213)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K23" t="n">
         <v>13</v>
@@ -2141,9 +2164,10 @@
           <t>poststelle3215@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J24" s="9">
-        <f>"Schule("&amp;B24&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3215)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2185,9 +2209,10 @@
           <t>poststelle3217@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J25" s="9">
-        <f>"Schule("&amp;B25&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3217)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K25" t="n">
         <v>12</v>
@@ -2262,9 +2287,10 @@
           <t>poststelle3221@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J26" s="9">
-        <f>"Schule("&amp;B26&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3221)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K26" t="n">
         <v>18</v>
@@ -2339,9 +2365,10 @@
           <t>poststelle3227@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J27" s="9">
-        <f>"Schule("&amp;B27&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3227)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2378,9 +2405,10 @@
           <t>poststelle3230@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J28" s="9">
-        <f>"Schule("&amp;B28&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3230)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2417,9 +2445,10 @@
           <t>poststelle3231@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J29" s="9">
-        <f>"Schule("&amp;B29&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3231)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2456,9 +2485,10 @@
           <t>poststelle3232@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J30" s="9">
-        <f>"Schule("&amp;B30&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3232)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2500,9 +2530,10 @@
           <t>poststelle3240@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J31" s="9">
-        <f>"Schule("&amp;B31&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3240)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2539,9 +2570,10 @@
           <t>poststelle3244@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J32" s="9">
-        <f>"Schule("&amp;B32&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3244)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2578,9 +2610,10 @@
           <t>poststelle3256@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J33" s="9">
-        <f>"Schule("&amp;B33&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3256)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2622,9 +2655,10 @@
           <t>poststelle3263@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J34" s="9">
-        <f>"Schule("&amp;B34&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3263)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K34" t="n">
         <v>21</v>
@@ -2694,9 +2728,10 @@
           <t>poststelle3264@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J35" s="9">
-        <f>"Schule("&amp;B35&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3264)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2738,9 +2773,10 @@
           <t>poststelle3270@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J36" s="9">
-        <f>"Schule("&amp;B36&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3270)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K36" t="n">
         <v>16</v>
@@ -2810,9 +2846,10 @@
           <t>poststelle3275@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J37" s="9">
-        <f>"Schule("&amp;B37&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3275)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2854,9 +2891,10 @@
           <t>poststelle3276@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J38" s="9">
-        <f>"Schule("&amp;B38&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3276)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K38" t="n">
         <v>16</v>
@@ -2931,9 +2969,10 @@
           <t>poststelle3288@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J39" s="9">
-        <f>"Schule("&amp;B39&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3288)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K39" t="n">
         <v>12</v>
@@ -3008,9 +3047,10 @@
           <t>poststelle3291@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J40" s="9">
-        <f>"Schule("&amp;B40&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3291)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K40" t="n">
         <v>8</v>
@@ -3085,9 +3125,10 @@
           <t>poststelle3292@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J41" s="9">
-        <f>"Schule("&amp;B41&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3292)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K41" t="n">
         <v>6</v>
@@ -3162,9 +3203,10 @@
           <t>poststelle3321@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J42" s="9">
-        <f>"Schule("&amp;B42&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3321)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K42" t="n">
         <v>14</v>
@@ -3234,9 +3276,10 @@
           <t>poststelle3322@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J43" s="9">
-        <f>"Schule("&amp;B43&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3322)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3278,9 +3321,10 @@
           <t>poststelle3332@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J44" s="9">
-        <f>"Schule("&amp;B44&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3332)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K44" t="n">
         <v>23</v>
@@ -3355,9 +3399,10 @@
           <t>poststelle3351@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J45" s="9">
-        <f>"Schule("&amp;B45&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3351)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -3399,9 +3444,10 @@
           <t>poststelle3354@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J46" s="9">
-        <f>"Schule("&amp;B46&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3354)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K46" t="n">
         <v>13</v>
@@ -3476,9 +3522,10 @@
           <t>poststelle3357@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J47" s="9">
-        <f>"Schule("&amp;B47&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3357)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K47" t="n">
         <v>6</v>
@@ -3553,9 +3600,10 @@
           <t>poststelle3363@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J48" s="9">
-        <f>"Schule("&amp;B48&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3363)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K48" t="n">
         <v>31</v>
@@ -3630,9 +3678,10 @@
           <t>poststelle3364@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J49" s="9">
-        <f>"Schule("&amp;B49&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3364)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3669,9 +3718,10 @@
           <t>poststelle3366@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J50" s="9">
-        <f>"Schule("&amp;B50&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3366)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3713,9 +3763,10 @@
           <t>poststelle3397@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J51" s="9">
-        <f>"Schule("&amp;B51&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3397)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K51" t="n">
         <v>3</v>
@@ -3790,9 +3841,10 @@
           <t>poststelle3408@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J52" s="9">
-        <f>"Schule("&amp;B52&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3408)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K52" t="n">
         <v>5</v>
@@ -3867,9 +3919,10 @@
           <t>poststelle3409@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J53" s="9">
-        <f>"Schule("&amp;B53&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3409)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K53" t="n">
         <v>4</v>
@@ -3944,9 +3997,10 @@
           <t>poststelle3413@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J54" s="9">
-        <f>"Schule("&amp;B54&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3413)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K54" t="n">
         <v>66</v>
@@ -4016,9 +4070,10 @@
           <t>poststelle3426@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J55" s="9">
-        <f>"Schule("&amp;B55&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3426)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -4060,9 +4115,10 @@
           <t>poststelle3433@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J56" s="9">
-        <f>"Schule("&amp;B56&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3433)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K56" t="n">
         <v>8</v>
@@ -4137,9 +4193,10 @@
           <t>poststelle3435@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J57" s="9">
-        <f>"Schule("&amp;B57&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3435)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K57" t="n">
         <v>3</v>
@@ -4209,9 +4266,10 @@
           <t>poststelle3521@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J58" s="9">
-        <f>"Schule("&amp;B58&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3521)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -4253,9 +4311,10 @@
           <t>poststelle3530@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J59" s="9">
-        <f>"Schule("&amp;B59&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3530)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K59" t="n">
         <v>8</v>
@@ -4330,9 +4389,10 @@
           <t>poststelle3534@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J60" s="9">
-        <f>"Schule("&amp;B60&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3534)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K60" t="n">
         <v>6</v>
@@ -4407,9 +4467,10 @@
           <t>poststelle3538@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J61" s="9">
-        <f>"Schule("&amp;B61&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3538)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K61" t="n">
         <v>31</v>
@@ -4484,9 +4545,10 @@
           <t>poststelle3542@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J62" s="9">
-        <f>"Schule("&amp;B62&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3542)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -4523,9 +4585,10 @@
           <t>poststelle3553@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J63" s="9">
-        <f>"Schule("&amp;B63&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3553)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -4567,9 +4630,10 @@
           <t>poststelle3561@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J64" s="9">
-        <f>"Schule("&amp;B64&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3561)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K64" t="n">
         <v>2</v>
@@ -4644,9 +4708,10 @@
           <t>poststelle3563@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J65" s="9">
-        <f>"Schule("&amp;B65&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3563)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K65" t="n">
         <v>3</v>
@@ -4721,9 +4786,10 @@
           <t>poststelle3579@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J66" s="9">
-        <f>"Schule("&amp;B66&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3579)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K66" t="n">
         <v>8</v>
@@ -4798,9 +4864,10 @@
           <t>poststelle3591@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J67" s="9">
-        <f>"Schule("&amp;B67&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3591)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K67" t="n">
         <v>6</v>
@@ -4870,9 +4937,10 @@
           <t>poststelle3591@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J68" s="9">
-        <f>"Schule("&amp;B68&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3591)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4914,9 +4982,10 @@
           <t>poststelle3603@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J69" s="9">
-        <f>"Schule("&amp;B69&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3603)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K69" t="n">
         <v>12</v>
@@ -4991,9 +5060,10 @@
           <t>poststelle3606@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J70" s="9">
-        <f>"Schule("&amp;B70&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3606)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K70" t="n">
         <v>8</v>
@@ -5068,9 +5138,10 @@
           <t>poststelle3617@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J71" s="9">
-        <f>"Schule("&amp;B71&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3617)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K71" t="n">
         <v>12</v>
@@ -5145,9 +5216,10 @@
           <t>poststelle3622@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J72" s="9">
-        <f>"Schule("&amp;B72&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3622)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K72" t="n">
         <v>16</v>
@@ -5222,9 +5294,10 @@
           <t>poststelle3624@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J73" s="9">
-        <f>"Schule("&amp;B73&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3624)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K73" t="n">
         <v>4</v>
@@ -5294,9 +5367,10 @@
           <t>poststelle3629@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J74" s="9">
-        <f>"Schule("&amp;B74&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3629)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="75" s="10">
@@ -5338,9 +5412,10 @@
           <t>poststelle3635@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J75" s="9">
-        <f>"Schule("&amp;B75&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3635)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K75" t="n">
         <v>10</v>
@@ -5415,9 +5490,10 @@
           <t>poststelle3638@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J76" s="9">
-        <f>"Schule("&amp;B76&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3638)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K76" t="n">
         <v>8</v>
@@ -5492,9 +5568,10 @@
           <t>poststelle3644@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J77" s="9">
-        <f>"Schule("&amp;B77&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3644)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K77" t="n">
         <v>28</v>
@@ -5569,9 +5646,10 @@
           <t>poststelle3648@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J78" s="9">
-        <f>"Schule("&amp;B78&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3648)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -5613,9 +5691,10 @@
           <t>poststelle3656@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J79" s="9">
-        <f>"Schule("&amp;B79&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3656)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K79" t="n">
         <v>12</v>
@@ -5690,9 +5769,10 @@
           <t>poststelle3659@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J80" s="9">
-        <f>"Schule("&amp;B80&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3659)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K80" t="n">
         <v>5</v>
@@ -5767,9 +5847,10 @@
           <t>poststelle3688@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J81" s="9">
-        <f>"Schule("&amp;B81&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3688)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K81" t="n">
         <v>7</v>
@@ -5839,9 +5920,10 @@
           <t>poststelle3690@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J82" s="9">
-        <f>"Schule("&amp;B82&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3690)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -5883,9 +5965,10 @@
           <t>poststelle3696@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J83" s="9">
-        <f>"Schule("&amp;B83&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3696)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K83" t="n">
         <v>4</v>
@@ -5955,9 +6038,10 @@
           <t>poststelle3700@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J84" s="9">
-        <f>"Schule("&amp;B84&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3700)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -5999,9 +6083,10 @@
           <t>poststelle3702@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J85" s="9">
-        <f>"Schule("&amp;B85&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3702)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K85" t="n">
         <v>4</v>
@@ -6076,9 +6161,10 @@
           <t>poststelle3730@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J86" s="9">
-        <f>"Schule("&amp;B86&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3730)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K86" t="n">
         <v>8</v>
@@ -6153,9 +6239,10 @@
           <t>poststelle3743@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J87" s="9">
-        <f>"Schule("&amp;B87&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3743)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K87" t="n">
         <v>12</v>
@@ -6225,9 +6312,10 @@
           <t>poststelle3744@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J88" s="9">
-        <f>"Schule("&amp;B88&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3744)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -6269,9 +6357,10 @@
           <t>poststelle3745@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J89" s="9">
-        <f>"Schule("&amp;B89&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3745)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K89" t="n">
         <v>17</v>
@@ -6341,9 +6430,10 @@
           <t>poststelle3761@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J90" s="9">
-        <f>"Schule("&amp;B90&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3761)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -6385,9 +6475,10 @@
           <t>poststelle3766@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J91" s="9">
-        <f>"Schule("&amp;B91&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3766)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K91" t="n">
         <v>4</v>
@@ -6462,9 +6553,10 @@
           <t>poststelle3778@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J92" s="9">
-        <f>"Schule("&amp;B92&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3778)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K92" t="n">
         <v>13</v>
@@ -6539,9 +6631,10 @@
           <t>poststelle3809@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J93" s="9">
-        <f>"Schule("&amp;B93&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3809)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K93" t="n">
         <v>18</v>
@@ -6616,9 +6709,10 @@
           <t>poststelle3810@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J94" s="9">
-        <f>"Schule("&amp;B94&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3810)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K94" t="n">
         <v>10</v>
@@ -6693,9 +6787,10 @@
           <t>poststelle3811@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J95" s="9">
-        <f>"Schule("&amp;B95&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3811)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K95" t="n">
         <v>16</v>
@@ -6770,9 +6865,10 @@
           <t>poststelle3820@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J96" s="9">
-        <f>"Schule("&amp;B96&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3820)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K96" t="n">
         <v>9</v>
@@ -6847,9 +6943,10 @@
           <t>poststelle3825@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J97" s="9">
-        <f>"Schule("&amp;B97&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3825)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -6886,9 +6983,10 @@
           <t>poststelle3828@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J98" s="9">
-        <f>"Schule("&amp;B98&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3828)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -6930,9 +7028,10 @@
           <t>poststelle3830@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J99" s="9">
-        <f>"Schule("&amp;B99&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3830)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -6974,9 +7073,10 @@
           <t>poststelle3831@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J100" s="9">
-        <f>"Schule("&amp;B100&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3831)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -7018,9 +7118,10 @@
           <t>poststelle3835@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J101" s="9">
-        <f>"Schule("&amp;B101&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3835)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K101" t="n">
         <v>13</v>
@@ -7095,9 +7196,10 @@
           <t>poststelle3844@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J102" s="9">
-        <f>"Schule("&amp;B102&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3844)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K102" t="n">
         <v>6</v>
@@ -7167,9 +7269,10 @@
           <t>poststelle3850@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J103" s="9">
-        <f>"Schule("&amp;B103&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3850)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -7206,9 +7309,10 @@
           <t>poststelle3851@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J104" s="9">
-        <f>"Schule("&amp;B104&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3851)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -7250,9 +7354,10 @@
           <t>poststelle3861@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J105" s="9">
-        <f>"Schule("&amp;B105&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3861)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -7294,9 +7399,10 @@
           <t>poststelle3877@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J106" s="9">
-        <f>"Schule("&amp;B106&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3877)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K106" t="n">
         <v>13</v>
@@ -7371,9 +7477,10 @@
           <t>poststelle3885@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J107" s="9">
-        <f>"Schule("&amp;B107&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3885)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K107" t="n">
         <v>5</v>
@@ -7443,9 +7550,10 @@
           <t>poststelle3886@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J108" s="9">
-        <f>"Schule("&amp;B108&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3886)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -7487,9 +7595,10 @@
           <t>poststelle3888@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J109" s="9">
-        <f>"Schule("&amp;B109&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3888)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K109" t="n">
         <v>8</v>
@@ -7564,9 +7673,10 @@
           <t>poststelle3894@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J110" s="9">
-        <f>"Schule("&amp;B110&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3894)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K110" t="n">
         <v>16</v>
@@ -7636,9 +7746,10 @@
           <t>poststelle3894@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J111" s="9">
-        <f>"Schule("&amp;B111&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3894)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -7680,9 +7791,10 @@
           <t>poststelle3913@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J112" s="9">
-        <f>"Schule("&amp;B112&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3913)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K112" t="n">
         <v>4</v>
@@ -7757,9 +7869,10 @@
           <t>poststelle3914@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J113" s="9">
-        <f>"Schule("&amp;B113&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J113" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3914)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K113" t="n">
         <v>8</v>
@@ -7834,9 +7947,10 @@
           <t>poststelle3918@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J114" s="9">
-        <f>"Schule("&amp;B114&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3918)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K114" t="n">
         <v>15</v>
@@ -7911,9 +8025,10 @@
           <t>poststelle3926@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J115" s="9">
-        <f>"Schule("&amp;B115&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3926)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K115" t="n">
         <v>9</v>
@@ -7988,9 +8103,10 @@
           <t>poststelle3937@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J116" s="9">
-        <f>"Schule("&amp;B116&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3937)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K116" t="n">
         <v>9</v>
@@ -8065,9 +8181,10 @@
           <t>poststelle3948@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J117" s="9">
-        <f>"Schule("&amp;B117&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3948)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K117" t="n">
         <v>19</v>
@@ -8142,9 +8259,10 @@
           <t>poststelle3949@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J118" s="9">
-        <f>"Schule("&amp;B118&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3949)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K118" t="n">
         <v>15</v>
@@ -8219,9 +8337,10 @@
           <t>poststelle3954@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J119" s="9">
-        <f>"Schule("&amp;B119&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3954)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K119" t="n">
         <v>5</v>
@@ -8296,9 +8415,10 @@
           <t>poststelle3955@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J120" s="9">
-        <f>"Schule("&amp;B120&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3955)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K120" t="n">
         <v>15</v>
@@ -8373,9 +8493,10 @@
           <t>poststelle3959@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J121" s="9">
-        <f>"Schule("&amp;B121&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3959)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K121" t="n">
         <v>16</v>
@@ -8450,9 +8571,10 @@
           <t>poststelle3982@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J122" s="9">
-        <f>"Schule("&amp;B122&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>Schule(3982)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K122" t="n">
         <v>11</v>
@@ -8522,9 +8644,10 @@
           <t>poststelle4001@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J123" s="9">
-        <f>"Schule("&amp;B123&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4001)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -8566,9 +8689,10 @@
           <t>poststelle4005@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J124" s="9">
-        <f>"Schule("&amp;B124&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4005)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K124" t="n">
         <v>10</v>
@@ -8643,9 +8767,10 @@
           <t>poststelle4006@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J125" s="9">
-        <f>"Schule("&amp;B125&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4006)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K125" t="n">
         <v>16</v>
@@ -8720,9 +8845,10 @@
           <t>poststelle4007@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J126" s="9">
-        <f>"Schule("&amp;B126&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4007)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K126" t="n">
         <v>14</v>
@@ -8792,9 +8918,10 @@
           <t>poststelle4008@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J127" s="9">
-        <f>"Schule("&amp;B127&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4008)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -8831,9 +8958,10 @@
           <t>poststelle4012@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J128" s="9">
-        <f>"Schule("&amp;B128&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4012)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -8870,9 +8998,10 @@
           <t>poststelle4018@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J129" s="9">
-        <f>"Schule("&amp;B129&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4018)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -8914,9 +9043,10 @@
           <t>poststelle4020@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J130" s="9">
-        <f>"Schule("&amp;B130&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4020)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -8953,9 +9083,10 @@
           <t>poststelle4022@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J131" s="9">
-        <f>"Schule("&amp;B131&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4022)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -8997,9 +9128,10 @@
           <t>poststelle4042@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J132" s="9">
-        <f>"Schule("&amp;B132&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4042)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K132" t="n">
         <v>18</v>
@@ -9074,9 +9206,10 @@
           <t>poststelle4045@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J133" s="9">
-        <f>"Schule("&amp;B133&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4045)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K133" t="n">
         <v>9</v>
@@ -9146,9 +9279,10 @@
           <t>poststelle4047@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J134" s="9">
-        <f>"Schule("&amp;B134&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4047)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -9190,9 +9324,10 @@
           <t>poststelle4050@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J135" s="9">
-        <f>"Schule("&amp;B135&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4050)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K135" t="n">
         <v>15</v>
@@ -9262,9 +9397,10 @@
           <t>poststelle4052@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J136" s="9">
-        <f>"Schule("&amp;B136&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4052)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -9306,9 +9442,10 @@
           <t>poststelle4053@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J137" s="9">
-        <f>"Schule("&amp;B137&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4053)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K137" t="n">
         <v>16</v>
@@ -9383,9 +9520,10 @@
           <t>poststelle4054@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J138" s="9">
-        <f>"Schule("&amp;B138&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4054)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K138" t="n">
         <v>14</v>
@@ -9460,9 +9598,10 @@
           <t>poststelle4054@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J139" s="9">
-        <f>"Schule("&amp;B139&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J139" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4054)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -9504,9 +9643,10 @@
           <t>poststelle4059@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J140" s="9">
-        <f>"Schule("&amp;B140&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4059)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K140" t="n">
         <v>12</v>
@@ -9576,9 +9716,10 @@
           <t>poststelle4061@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J141" s="9">
-        <f>"Schule("&amp;B141&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J141" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4061)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -9620,9 +9761,10 @@
           <t>poststelle4074@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J142" s="9">
-        <f>"Schule("&amp;B142&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4074)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K142" t="n">
         <v>13</v>
@@ -9692,9 +9834,10 @@
           <t>poststelle4075@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J143" s="9">
-        <f>"Schule("&amp;B143&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J143" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4075)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -9736,9 +9879,10 @@
           <t>poststelle4090@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J144" s="9">
-        <f>"Schule("&amp;B144&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4090)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K144" t="n">
         <v>2</v>
@@ -9813,9 +9957,10 @@
           <t>poststelle4097@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J145" s="9">
-        <f>"Schule("&amp;B145&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4097)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K145" t="n">
         <v>14</v>
@@ -9890,9 +10035,10 @@
           <t>poststelle4101@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J146" s="9">
-        <f>"Schule("&amp;B146&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4101)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K146" t="n">
         <v>3</v>
@@ -9967,9 +10113,10 @@
           <t>poststelle4133@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J147" s="9">
-        <f>"Schule("&amp;B147&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4133)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K147" t="n">
         <v>22</v>
@@ -10044,9 +10191,10 @@
           <t>poststelle4140@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J148" s="9">
-        <f>"Schule("&amp;B148&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4140)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K148" t="n">
         <v>11</v>
@@ -10121,9 +10269,10 @@
           <t>poststelle4141@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J149" s="9">
-        <f>"Schule("&amp;B149&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4141)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K149" t="n">
         <v>7</v>
@@ -10198,9 +10347,10 @@
           <t>poststelle4146@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J150" s="9">
-        <f>"Schule("&amp;B150&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4146)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K150" t="n">
         <v>5</v>
@@ -10275,9 +10425,10 @@
           <t>poststelle4151@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J151" s="9">
-        <f>"Schule("&amp;B151&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4151)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K151" t="n">
         <v>8</v>
@@ -10352,9 +10503,10 @@
           <t>poststelle4154@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J152" s="9">
-        <f>"Schule("&amp;B152&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J152" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4154)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K152" t="n">
         <v>6</v>
@@ -10429,9 +10581,10 @@
           <t>poststelle4159@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J153" s="9">
-        <f>"Schule("&amp;B153&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4159)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K153" t="n">
         <v>25</v>
@@ -10506,9 +10659,10 @@
           <t>poststelle4176@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J154" s="9">
-        <f>"Schule("&amp;B154&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4176)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -10550,9 +10704,10 @@
           <t>poststelle4183@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J155" s="9">
-        <f>"Schule("&amp;B155&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J155" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4183)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K155" t="n">
         <v>18</v>
@@ -10627,9 +10782,10 @@
           <t>poststelle4190@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J156" s="9">
-        <f>"Schule("&amp;B156&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J156" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4190)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K156" t="n">
         <v>13</v>
@@ -10704,9 +10860,10 @@
           <t>poststelle4199@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J157" s="9">
-        <f>"Schule("&amp;B157&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J157" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4199)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K157" t="n">
         <v>15</v>
@@ -10781,9 +10938,10 @@
           <t>poststelle4203@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J158" s="9">
-        <f>"Schule("&amp;B158&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J158" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4203)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K158" t="n">
         <v>20</v>
@@ -10853,9 +11011,10 @@
           <t>poststelle4211@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J159" s="9">
-        <f>"Schule("&amp;B159&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J159" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4211)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -10892,9 +11051,10 @@
           <t>poststelle4211@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J160" s="9">
-        <f>"Schule("&amp;B160&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J160" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4211)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -10936,9 +11096,10 @@
           <t>poststelle4213@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J161" s="9">
-        <f>"Schule("&amp;B161&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J161" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4213)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K161" t="n">
         <v>13</v>
@@ -11013,9 +11174,10 @@
           <t>poststelle4220@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J162" s="9">
-        <f>"Schule("&amp;B162&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J162" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4220)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -11057,9 +11219,10 @@
           <t>poststelle4221@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J163" s="9">
-        <f>"Schule("&amp;B163&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J163" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4221)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K163" t="n">
         <v>14</v>
@@ -11129,9 +11292,10 @@
           <t>poststelle4226@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J164" s="9">
-        <f>"Schule("&amp;B164&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J164" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4226)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -11173,9 +11337,10 @@
           <t>poststelle4234@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J165" s="9">
-        <f>"Schule("&amp;B165&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J165" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4234)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K165" t="n">
         <v>9</v>
@@ -11245,9 +11410,10 @@
           <t>poststelle4243@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J166" s="9">
-        <f>"Schule("&amp;B166&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J166" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4243)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="167" s="10">
@@ -11289,9 +11455,10 @@
           <t>poststelle4248@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J167" s="9">
-        <f>"Schule("&amp;B167&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J167" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4248)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K167" t="n">
         <v>12</v>
@@ -11366,9 +11533,10 @@
           <t>poststelle4250@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J168" s="9">
-        <f>"Schule("&amp;B168&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J168" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4250)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -11410,9 +11578,10 @@
           <t>poststelle4266@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J169" s="9">
-        <f>"Schule("&amp;B169&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J169" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4266)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K169" t="n">
         <v>2</v>
@@ -11487,9 +11656,10 @@
           <t>poststelle4272@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J170" s="9">
-        <f>"Schule("&amp;B170&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J170" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4272)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K170" t="n">
         <v>5</v>
@@ -11564,9 +11734,10 @@
           <t>poststelle4277@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J171" s="9">
-        <f>"Schule("&amp;B171&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J171" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4277)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K171" t="n">
         <v>8</v>
@@ -11641,9 +11812,10 @@
           <t>poststelle4293@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J172" s="9">
-        <f>"Schule("&amp;B172&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J172" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4293)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K172" t="n">
         <v>7</v>
@@ -11718,9 +11890,10 @@
           <t>poststelle4295@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J173" s="9">
-        <f>"Schule("&amp;B173&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J173" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4295)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K173" t="n">
         <v>12</v>
@@ -11795,9 +11968,10 @@
           <t>poststelle4299@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J174" s="9">
-        <f>"Schule("&amp;B174&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J174" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4299)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K174" t="n">
         <v>10</v>
@@ -11872,9 +12046,10 @@
           <t>poststelle4304@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J175" s="9">
-        <f>"Schule("&amp;B175&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J175" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4304)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K175" t="n">
         <v>33</v>
@@ -11949,9 +12124,10 @@
           <t>poststelle4311@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J176" s="9">
-        <f>"Schule("&amp;B176&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J176" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4311)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K176" t="n">
         <v>4</v>
@@ -12021,9 +12197,10 @@
           <t>poststelle4312@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J177" s="9">
-        <f>"Schule("&amp;B177&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J177" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4312)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -12065,9 +12242,10 @@
           <t>poststelle4314@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J178" s="9">
-        <f>"Schule("&amp;B178&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J178" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4314)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K178" t="n">
         <v>9</v>
@@ -12142,9 +12320,10 @@
           <t>poststelle4316@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J179" s="9">
-        <f>"Schule("&amp;B179&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J179" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4316)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K179" t="n">
         <v>5</v>
@@ -12219,9 +12398,10 @@
           <t>poststelle4319@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J180" s="9">
-        <f>"Schule("&amp;B180&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J180" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4319)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K180" t="n">
         <v>6</v>
@@ -12296,9 +12476,10 @@
           <t>poststelle4333@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J181" s="9">
-        <f>"Schule("&amp;B181&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J181" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4333)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K181" t="n">
         <v>6</v>
@@ -12373,9 +12554,10 @@
           <t>poststelle4343@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J182" s="9">
-        <f>"Schule("&amp;B182&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J182" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4343)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K182" t="n">
         <v>5</v>
@@ -12450,9 +12632,10 @@
           <t>poststelle4380@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J183" s="9">
-        <f>"Schule("&amp;B183&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J183" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4380)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K183" t="n">
         <v>18</v>
@@ -12522,9 +12705,10 @@
           <t>poststelle4384@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J184" s="9">
-        <f>"Schule("&amp;B184&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J184" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4384)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -12561,9 +12745,10 @@
           <t>poststelle4384@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J185" s="9">
-        <f>"Schule("&amp;B185&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J185" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4384)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -12605,9 +12790,10 @@
           <t>poststelle4392@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J186" s="9">
-        <f>"Schule("&amp;B186&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J186" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4392)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K186" t="n">
         <v>3</v>
@@ -12682,9 +12868,10 @@
           <t>poststelle4434@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J187" s="9">
-        <f>"Schule("&amp;B187&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J187" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4434)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K187" t="n">
         <v>18</v>
@@ -12759,9 +12946,10 @@
           <t>poststelle4435@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J188" s="9">
-        <f>"Schule("&amp;B188&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J188" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4435)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K188" t="n">
         <v>13</v>
@@ -12836,9 +13024,10 @@
           <t>poststelle4436@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J189" s="9">
-        <f>"Schule("&amp;B189&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J189" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4436)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K189" t="n">
         <v>4</v>
@@ -12913,9 +13102,10 @@
           <t>poststelle4437@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J190" s="9">
-        <f>"Schule("&amp;B190&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J190" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4437)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K190" t="n">
         <v>6</v>
@@ -12990,9 +13180,10 @@
           <t>poststelle4483@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J191" s="9">
-        <f>"Schule("&amp;B191&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J191" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4483)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K191" t="n">
         <v>10</v>
@@ -13067,9 +13258,10 @@
           <t>poststelle4484@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J192" s="9">
-        <f>"Schule("&amp;B192&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J192" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4484)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K192" t="n">
         <v>14</v>
@@ -13144,9 +13336,10 @@
           <t>poststelle4535@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J193" s="9">
-        <f>"Schule("&amp;B193&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J193" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4535)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K193" t="n">
         <v>8</v>
@@ -13221,9 +13414,10 @@
           <t>poststelle4647@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J194" s="9">
-        <f>"Schule("&amp;B194&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J194" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4647)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K194" t="n">
         <v>4</v>
@@ -13298,9 +13492,10 @@
           <t>poststelle4795@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J195" s="9">
-        <f>"Schule("&amp;B195&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J195" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4795)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K195" t="n">
         <v>5</v>
@@ -13375,9 +13570,10 @@
           <t>poststelle4797@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J196" s="9">
-        <f>"Schule("&amp;B196&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J196" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4797)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K196" t="n">
         <v>17</v>
@@ -13447,9 +13643,10 @@
           <t>poststelle4800@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J197" s="9">
-        <f>"Schule("&amp;B197&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J197" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4800)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -13486,9 +13683,10 @@
           <t>poststelle4801@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J198" s="9">
-        <f>"Schule("&amp;B198&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J198" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4801)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -13530,9 +13728,10 @@
           <t>poststelle4862@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J199" s="9">
-        <f>"Schule("&amp;B199&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J199" s="9" t="inlineStr">
+        <is>
+          <t>Schule(4862)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K199" t="n">
         <v>8</v>
@@ -13607,9 +13806,10 @@
           <t>poststelle5024@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J200" s="9">
-        <f>"Schule("&amp;B200&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J200" s="9" t="inlineStr">
+        <is>
+          <t>Schule(5024)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K200" t="n">
         <v>36</v>
@@ -13684,9 +13884,10 @@
           <t>poststelle5039@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J201" s="9">
-        <f>"Schule("&amp;B201&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J201" s="9" t="inlineStr">
+        <is>
+          <t>Schule(5039)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K201" t="n">
         <v>8</v>
@@ -13761,9 +13962,10 @@
           <t>poststelle5040@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J202" s="9">
-        <f>"Schule("&amp;B202&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J202" s="9" t="inlineStr">
+        <is>
+          <t>Schule(5040)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K202" t="n">
         <v>14</v>
@@ -13838,9 +14040,10 @@
           <t>poststelle5393@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J203" s="9">
-        <f>"Schule("&amp;B203&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J203" s="9" t="inlineStr">
+        <is>
+          <t>Schule(5393)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K203" t="n">
         <v>4</v>
@@ -13915,9 +14118,10 @@
           <t>poststelle5440@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J204" s="9">
-        <f>"Schule("&amp;B204&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J204" s="9" t="inlineStr">
+        <is>
+          <t>Schule(5440)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K204" t="n">
         <v>4</v>
@@ -13992,9 +14196,10 @@
           <t>poststelle7103@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J205" s="9">
-        <f>"Schule("&amp;B205&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J205" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7103)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K205" t="n">
         <v>18</v>
@@ -14064,9 +14269,10 @@
           <t>poststelle7104@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J206" s="9">
-        <f>"Schule("&amp;B206&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J206" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7104)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -14108,9 +14314,10 @@
           <t>poststelle7105@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J207" s="9">
-        <f>"Schule("&amp;B207&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J207" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7105)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -14152,9 +14359,10 @@
           <t>poststelle7106@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J208" s="9">
-        <f>"Schule("&amp;B208&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J208" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7106)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -14191,9 +14399,10 @@
           <t>poststelle7113@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J209" s="9">
-        <f>"Schule("&amp;B209&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J209" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7113)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -14235,9 +14444,10 @@
           <t>poststelle7121@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J210" s="9">
-        <f>"Schule("&amp;B210&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J210" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7121)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -14274,9 +14484,10 @@
           <t>poststelle7124@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J211" s="9">
-        <f>"Schule("&amp;B211&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J211" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7124)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -14313,9 +14524,10 @@
           <t>poststelle7125@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J212" s="9">
-        <f>"Schule("&amp;B212&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J212" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7125)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -14352,9 +14564,10 @@
           <t>poststelle7127@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J213" s="9">
-        <f>"Schule("&amp;B213&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J213" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7127)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -14396,9 +14609,10 @@
           <t>poststelle7129@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J214" s="9">
-        <f>"Schule("&amp;B214&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J214" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7129)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K214" t="n">
         <v>19</v>
@@ -14473,9 +14687,10 @@
           <t>poststelle7130@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J215" s="9">
-        <f>"Schule("&amp;B215&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J215" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7130)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K215" t="n">
         <v>10</v>
@@ -14550,9 +14765,10 @@
           <t>poststelle7134@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J216" s="9">
-        <f>"Schule("&amp;B216&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J216" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7134)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K216" t="n">
         <v>15</v>
@@ -14627,9 +14843,10 @@
           <t>poststelle7137@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J217" s="9">
-        <f>"Schule("&amp;B217&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J217" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7137)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K217" t="n">
         <v>10</v>
@@ -14704,9 +14921,10 @@
           <t>poststelle7142@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J218" s="9">
-        <f>"Schule("&amp;B218&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J218" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7142)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K218" t="n">
         <v>8</v>
@@ -14781,9 +14999,10 @@
           <t>poststelle7143@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J219" s="9">
-        <f>"Schule("&amp;B219&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J219" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7143)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K219" t="n">
         <v>14</v>
@@ -14858,9 +15077,10 @@
           <t>poststelle7144@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J220" s="9">
-        <f>"Schule("&amp;B220&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J220" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7144)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K220" t="n">
         <v>23</v>
@@ -14935,9 +15155,10 @@
           <t>poststelle7150@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J221" s="9">
-        <f>"Schule("&amp;B221&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J221" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7150)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -14979,9 +15200,10 @@
           <t>poststelle7151@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J222" s="9">
-        <f>"Schule("&amp;B222&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J222" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7151)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K222" t="n">
         <v>12</v>
@@ -15056,9 +15278,10 @@
           <t>poststelle7161@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J223" s="9">
-        <f>"Schule("&amp;B223&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J223" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7161)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K223" t="n">
         <v>8</v>
@@ -15128,9 +15351,10 @@
           <t>poststelle7162@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J224" s="9">
-        <f>"Schule("&amp;B224&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J224" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7162)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -15172,9 +15396,10 @@
           <t>poststelle7190@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J225" s="9">
-        <f>"Schule("&amp;B225&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J225" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7190)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K225" t="n">
         <v>4</v>
@@ -15249,9 +15474,10 @@
           <t>poststelle7199@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J226" s="9">
-        <f>"Schule("&amp;B226&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J226" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7199)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K226" t="n">
         <v>8</v>
@@ -15326,9 +15552,10 @@
           <t>poststelle7204@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J227" s="9">
-        <f>"Schule("&amp;B227&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J227" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7204)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K227" t="n">
         <v>9</v>
@@ -15398,9 +15625,10 @@
           <t>poststelle7215@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J228" s="9">
-        <f>"Schule("&amp;B228&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J228" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7215)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -15442,9 +15670,10 @@
           <t>poststelle7220@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J229" s="9">
-        <f>"Schule("&amp;B229&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J229" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7220)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K229" t="n">
         <v>7</v>
@@ -15514,9 +15743,10 @@
           <t>poststelle7233@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J230" s="9">
-        <f>"Schule("&amp;B230&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J230" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7233)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -15558,9 +15788,10 @@
           <t>poststelle7240@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J231" s="9">
-        <f>"Schule("&amp;B231&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J231" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7240)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K231" t="n">
         <v>6</v>
@@ -15630,9 +15861,10 @@
           <t>poststelle7244@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J232" s="9">
-        <f>"Schule("&amp;B232&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J232" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7244)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -15674,9 +15906,10 @@
           <t>poststelle7249@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J233" s="9">
-        <f>"Schule("&amp;B233&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J233" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7249)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K233" t="n">
         <v>4</v>
@@ -15751,9 +15984,10 @@
           <t>poststelle7260@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J234" s="9">
-        <f>"Schule("&amp;B234&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J234" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7260)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -15795,9 +16029,10 @@
           <t>poststelle7267@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J235" s="9">
-        <f>"Schule("&amp;B235&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J235" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7267)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K235" t="n">
         <v>6</v>
@@ -15872,9 +16107,10 @@
           <t>poststelle7271@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J236" s="9">
-        <f>"Schule("&amp;B236&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J236" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7271)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K236" t="n">
         <v>27</v>
@@ -15949,9 +16185,10 @@
           <t>poststelle7292@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J237" s="9">
-        <f>"Schule("&amp;B237&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J237" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7292)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K237" t="n">
         <v>4</v>
@@ -16026,9 +16263,10 @@
           <t>poststelle7305@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J238" s="9">
-        <f>"Schule("&amp;B238&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J238" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7305)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K238" t="n">
         <v>7</v>
@@ -16103,9 +16341,10 @@
           <t>poststelle7306@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J239" s="9">
-        <f>"Schule("&amp;B239&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J239" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7306)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -16147,9 +16386,10 @@
           <t>poststelle7316@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J240" s="9">
-        <f>"Schule("&amp;B240&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J240" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7316)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K240" t="n">
         <v>6</v>
@@ -16224,9 +16464,10 @@
           <t>poststelle7322@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J241" s="9">
-        <f>"Schule("&amp;B241&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J241" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7322)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K241" t="n">
         <v>10</v>
@@ -16301,9 +16542,10 @@
           <t>poststelle7344@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J242" s="9">
-        <f>"Schule("&amp;B242&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J242" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7344)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K242" t="n">
         <v>15</v>
@@ -16378,9 +16620,10 @@
           <t>poststelle7357@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J243" s="9">
-        <f>"Schule("&amp;B243&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J243" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7357)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K243" t="n">
         <v>10</v>
@@ -16455,9 +16698,10 @@
           <t>poststelle7376@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J244" s="9">
-        <f>"Schule("&amp;B244&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J244" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7376)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K244" t="n">
         <v>8</v>
@@ -16532,9 +16776,10 @@
           <t>poststelle7392@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J245" s="9">
-        <f>"Schule("&amp;B245&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J245" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7392)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K245" t="n">
         <v>12</v>
@@ -16604,9 +16849,10 @@
           <t>poststelle7395@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J246" s="9">
-        <f>"Schule("&amp;B246&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J246" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7395)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="247">
@@ -16648,9 +16894,10 @@
           <t>poststelle7400@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J247" s="9">
-        <f>"Schule("&amp;B247&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J247" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7400)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K247" t="n">
         <v>11</v>
@@ -16725,9 +16972,10 @@
           <t>poststelle7401@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J248" s="9">
-        <f>"Schule("&amp;B248&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J248" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7401)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K248" t="n">
         <v>11</v>
@@ -16802,9 +17050,10 @@
           <t>poststelle7405@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J249" s="9">
-        <f>"Schule("&amp;B249&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J249" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7405)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K249" t="n">
         <v>8</v>
@@ -16874,9 +17123,10 @@
           <t>poststelle7409@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J250" s="9">
-        <f>"Schule("&amp;B250&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J250" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7409)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -16918,9 +17168,10 @@
           <t>poststelle7439@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J251" s="9">
-        <f>"Schule("&amp;B251&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J251" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7439)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K251" t="n">
         <v>12</v>
@@ -16995,9 +17246,10 @@
           <t>poststelle7440@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J252" s="9">
-        <f>"Schule("&amp;B252&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J252" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7440)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K252" t="n">
         <v>8</v>
@@ -17072,9 +17324,10 @@
           <t>poststelle7446@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J253" s="9">
-        <f>"Schule("&amp;B253&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J253" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7446)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K253" t="n">
         <v>4</v>
@@ -17149,9 +17402,10 @@
           <t>poststelle7455@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J254" s="9">
-        <f>"Schule("&amp;B254&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J254" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7455)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K254" t="n">
         <v>8</v>
@@ -17226,9 +17480,10 @@
           <t>poststelle7469@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J255" s="9">
-        <f>"Schule("&amp;B255&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J255" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7469)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -17270,9 +17525,10 @@
           <t>poststelle7473@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J256" s="9">
-        <f>"Schule("&amp;B256&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J256" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7473)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K256" t="n">
         <v>15</v>
@@ -17347,9 +17603,10 @@
           <t>poststelle7479@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J257" s="9">
-        <f>"Schule("&amp;B257&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J257" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7479)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K257" t="n">
         <v>7</v>
@@ -17424,9 +17681,10 @@
           <t>poststelle7503@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J258" s="9">
-        <f>"Schule("&amp;B258&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J258" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7503)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K258" t="n">
         <v>20</v>
@@ -17496,9 +17754,10 @@
           <t>poststelle7517@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J259" s="9">
-        <f>"Schule("&amp;B259&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J259" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7517)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -17535,9 +17794,10 @@
           <t>poststelle7519@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J260" s="9">
-        <f>"Schule("&amp;B260&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J260" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7519)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -17579,9 +17839,10 @@
           <t>poststelle7526@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J261" s="9">
-        <f>"Schule("&amp;B261&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J261" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7526)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K261" t="n">
         <v>2</v>
@@ -17656,9 +17917,10 @@
           <t>poststelle7537@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J262" s="9">
-        <f>"Schule("&amp;B262&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J262" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7537)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="263">
@@ -17695,9 +17957,10 @@
           <t>poststelle7542@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J263" s="9">
-        <f>"Schule("&amp;B263&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J263" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7542)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -17739,9 +18002,10 @@
           <t>poststelle7567@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J264" s="9">
-        <f>"Schule("&amp;B264&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J264" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7567)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K264" t="n">
         <v>4</v>
@@ -17816,9 +18080,10 @@
           <t>poststelle7577@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J265" s="9">
-        <f>"Schule("&amp;B265&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J265" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7577)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K265" t="n">
         <v>6</v>
@@ -17893,9 +18158,10 @@
           <t>poststelle7581@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J266" s="9">
-        <f>"Schule("&amp;B266&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J266" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7581)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K266" t="n">
         <v>8</v>
@@ -17970,9 +18236,10 @@
           <t>poststelle7584@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J267" s="9">
-        <f>"Schule("&amp;B267&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J267" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7584)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K267" t="n">
         <v>8</v>
@@ -18047,9 +18314,10 @@
           <t>poststelle7586@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J268" s="9">
-        <f>"Schule("&amp;B268&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J268" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7586)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K268" t="n">
         <v>8</v>
@@ -18124,9 +18392,10 @@
           <t>poststelle7591@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J269" s="9">
-        <f>"Schule("&amp;B269&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J269" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7591)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K269" t="n">
         <v>6</v>
@@ -18201,9 +18470,10 @@
           <t>poststelle7616@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J270" s="9">
-        <f>"Schule("&amp;B270&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J270" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7616)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K270" t="n">
         <v>7</v>
@@ -18278,9 +18548,10 @@
           <t>poststelle7629@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J271" s="9">
-        <f>"Schule("&amp;B271&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J271" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7629)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K271" t="n">
         <v>8</v>
@@ -18355,9 +18626,10 @@
           <t>poststelle7649@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J272" s="9">
-        <f>"Schule("&amp;B272&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J272" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7649)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K272" t="n">
         <v>19</v>
@@ -18432,9 +18704,10 @@
           <t>poststelle7651@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J273" s="9">
-        <f>"Schule("&amp;B273&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J273" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7651)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K273" t="n">
         <v>23</v>
@@ -18504,9 +18777,10 @@
           <t>poststelle7652@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J274" s="9">
-        <f>"Schule("&amp;B274&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J274" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7652)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -18548,9 +18822,10 @@
           <t>poststelle7655@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J275" s="9">
-        <f>"Schule("&amp;B275&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J275" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7655)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K275" t="n">
         <v>10</v>
@@ -18625,9 +18900,10 @@
           <t>poststelle7656@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J276" s="9">
-        <f>"Schule("&amp;B276&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J276" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7656)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="277">
@@ -18669,9 +18945,10 @@
           <t>poststelle7657@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J277" s="9">
-        <f>"Schule("&amp;B277&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J277" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7657)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K277" t="n">
         <v>14</v>
@@ -18741,9 +19018,10 @@
           <t>poststelle7663@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J278" s="9">
-        <f>"Schule("&amp;B278&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J278" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7663)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -18785,9 +19063,10 @@
           <t>poststelle7665@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J279" s="9">
-        <f>"Schule("&amp;B279&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J279" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7665)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K279" t="n">
         <v>16</v>
@@ -18862,9 +19141,10 @@
           <t>poststelle7672@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J280" s="9">
-        <f>"Schule("&amp;B280&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J280" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7672)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K280" t="n">
         <v>10</v>
@@ -18939,9 +19219,10 @@
           <t>poststelle7674@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J281" s="9">
-        <f>"Schule("&amp;B281&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J281" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7674)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K281" t="n">
         <v>4</v>
@@ -19016,9 +19297,10 @@
           <t>poststelle7677@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J282" s="9">
-        <f>"Schule("&amp;B282&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J282" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7677)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K282" t="n">
         <v>4</v>
@@ -19093,9 +19375,10 @@
           <t>poststelle7678@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J283" s="9">
-        <f>"Schule("&amp;B283&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J283" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7678)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K283" t="n">
         <v>16</v>
@@ -19170,9 +19453,10 @@
           <t>poststelle7683@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J284" s="9">
-        <f>"Schule("&amp;B284&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J284" s="9" t="inlineStr">
+        <is>
+          <t>Schule(7683)@schule.hessen.de</t>
+        </is>
       </c>
       <c r="K284" t="n">
         <v>12</v>
@@ -19227,9 +19511,10 @@
           <t>poststelle3333@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J285">
-        <f>"Schule("&amp;B285&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Schule(3333)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -19251,9 +19536,10 @@
           <t>poststelle3386@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J286">
-        <f>"Schule("&amp;B286&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Schule(3386)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="287">
@@ -19275,9 +19561,10 @@
           <t>poststelle4230@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J287">
-        <f>"Schule("&amp;B287&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Schule(4230)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -19299,9 +19586,10 @@
           <t>poststelle3602@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J288">
-        <f>"Schule("&amp;B288&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Schule(3602)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="289">
@@ -19323,9 +19611,10 @@
           <t>poststelle3334@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J289">
-        <f>"Schule("&amp;B289&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Schule(3334)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="290">
@@ -19347,9 +19636,10 @@
           <t>poststelle3384@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J290">
-        <f>"Schule("&amp;B290&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Schule(3384)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -19371,9 +19661,10 @@
           <t>poststelle3510@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J291">
-        <f>"Schule("&amp;B291&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Schule(3510)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -19395,9 +19686,10 @@
           <t>poststelle3325@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J292">
-        <f>"Schule("&amp;B292&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Schule(3325)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -19419,9 +19711,10 @@
           <t>poststelle3344@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J293">
-        <f>"Schule("&amp;B293&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Schule(3344)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="294">
@@ -19443,9 +19736,10 @@
           <t>poststelle3379@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J294">
-        <f>"Schule("&amp;B294&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Schule(3379)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -19467,9 +19761,10 @@
           <t>poststelle3605@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J295">
-        <f>"Schule("&amp;B295&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Schule(3605)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -19491,9 +19786,10 @@
           <t>poststelle3385@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J296">
-        <f>"Schule("&amp;B296&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Schule(3385)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -19515,9 +19811,10 @@
           <t>poststelle4237@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J297">
-        <f>"Schule("&amp;B297&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Schule(4237)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -19539,9 +19836,10 @@
           <t>poststelle3370@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J298">
-        <f>"Schule("&amp;B298&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Schule(3370)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -19563,9 +19861,10 @@
           <t>poststelle3348@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J299">
-        <f>"Schule("&amp;B299&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Schule(3348)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="300">
@@ -19587,9 +19886,10 @@
           <t>poststelle3614@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J300">
-        <f>"Schule("&amp;B300&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Schule(3614)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="301">
@@ -19611,9 +19911,10 @@
           <t>poststelle3599@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J301">
-        <f>"Schule("&amp;B301&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Schule(3599)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="302">
@@ -19635,9 +19936,10 @@
           <t>poststelle3323@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J302">
-        <f>"Schule("&amp;B302&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Schule(3323)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -19659,9 +19961,10 @@
           <t>poststelle3390@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J303">
-        <f>"Schule("&amp;B303&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Schule(3390)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -19683,9 +19986,10 @@
           <t>poststelle3608@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J304">
-        <f>"Schule("&amp;B304&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Schule(3608)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -19707,9 +20011,10 @@
           <t>poststelle3539@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J305">
-        <f>"Schule("&amp;B305&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Schule(3539)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -19731,9 +20036,10 @@
           <t>poststelle3509@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J306">
-        <f>"Schule("&amp;B306&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Schule(3509)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -19755,9 +20061,10 @@
           <t>poststelle3482@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J307">
-        <f>"Schule("&amp;B307&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Schule(3482)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="308">
@@ -19779,9 +20086,10 @@
           <t>poststelle3525@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J308">
-        <f>"Schule("&amp;B308&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Schule(3525)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="309">
@@ -19803,9 +20111,10 @@
           <t>poststelle3502@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J309">
-        <f>"Schule("&amp;B309&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Schule(3502)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="310">
@@ -19827,9 +20136,10 @@
           <t>poststelle3201@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J310">
-        <f>"Schule("&amp;B310&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Schule(3201)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="311">
@@ -19851,9 +20161,10 @@
           <t>poststelle3489@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J311">
-        <f>"Schule("&amp;B311&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Schule(3489)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="312">
@@ -19875,9 +20186,10 @@
           <t>poststelle4338@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J312">
-        <f>"Schule("&amp;B312&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>Schule(4338)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="313">
@@ -19899,9 +20211,10 @@
           <t>poststelle3224@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J313">
-        <f>"Schule("&amp;B313&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Schule(3224)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="314">
@@ -19923,9 +20236,10 @@
           <t>poststelle4253@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J314">
-        <f>"Schule("&amp;B314&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Schule(4253)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="315">
@@ -19947,9 +20261,10 @@
           <t>poststelle3511@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J315">
-        <f>"Schule("&amp;B315&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Schule(3511)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="316">
@@ -19971,9 +20286,10 @@
           <t>poststelle4188@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J316">
-        <f>"Schule("&amp;B316&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Schule(4188)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="317">
@@ -19995,9 +20311,10 @@
           <t>poststelle3481@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J317">
-        <f>"Schule("&amp;B317&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Schule(3481)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="318">
@@ -20019,9 +20336,10 @@
           <t>poststelle3480@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J318">
-        <f>"Schule("&amp;B318&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Schule(3480)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -20043,9 +20361,10 @@
           <t>poststelle4284@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J319">
-        <f>"Schule("&amp;B319&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Schule(4284)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="320">
@@ -20067,9 +20386,10 @@
           <t>poststelle4336@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J320">
-        <f>"Schule("&amp;B320&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Schule(4336)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="321">
@@ -20091,9 +20411,10 @@
           <t>poststelle3523@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J321">
-        <f>"Schule("&amp;B321&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Schule(3523)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="322">
@@ -20115,9 +20436,10 @@
           <t>poststelle3528@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J322">
-        <f>"Schule("&amp;B322&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Schule(3528)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="323">
@@ -20139,9 +20461,10 @@
           <t>poststelle4191@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J323">
-        <f>"Schule("&amp;B323&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>Schule(4191)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="324">
@@ -20163,9 +20486,10 @@
           <t>poststelle4231@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J324">
-        <f>"Schule("&amp;B324&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Schule(4231)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="325">
@@ -20187,9 +20511,10 @@
           <t>poststelle3172@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J325">
-        <f>"Schule("&amp;B325&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Schule(3172)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="326">
@@ -20211,9 +20536,10 @@
           <t>poststelle4262@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J326">
-        <f>"Schule("&amp;B326&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Schule(4262)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="327">
@@ -20235,9 +20561,10 @@
           <t>poststelle3666@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J327">
-        <f>"Schule("&amp;B327&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Schule(3666)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="328">
@@ -20259,9 +20586,10 @@
           <t>poststelle3166@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J328">
-        <f>"Schule("&amp;B328&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Schule(3166)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="329">
@@ -20283,9 +20611,10 @@
           <t>poststelle3131@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J329">
-        <f>"Schule("&amp;B329&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Schule(3131)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="330">
@@ -20307,9 +20636,10 @@
           <t>poststelle3167@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J330">
-        <f>"Schule("&amp;B330&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Schule(3167)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="331">
@@ -20331,9 +20661,10 @@
           <t>poststelle3104@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J331">
-        <f>"Schule("&amp;B331&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Schule(3104)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="332">
@@ -20355,9 +20686,10 @@
           <t>poststelle3168@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J332">
-        <f>"Schule("&amp;B332&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Schule(3168)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="333">
@@ -20379,9 +20711,10 @@
           <t>poststelle3154@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J333">
-        <f>"Schule("&amp;B333&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Schule(3154)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="334">
@@ -20403,9 +20736,10 @@
           <t>poststelle3118@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J334">
-        <f>"Schule("&amp;B334&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Schule(3118)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="335">
@@ -20427,9 +20761,10 @@
           <t>poststelle4381@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J335">
-        <f>"Schule("&amp;B335&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Schule(4381)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="336">
@@ -20451,9 +20786,10 @@
           <t>poststelle3153@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J336">
-        <f>"Schule("&amp;B336&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Schule(3153)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="337">
@@ -20475,9 +20811,10 @@
           <t>poststelle4396@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J337">
-        <f>"Schule("&amp;B337&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Schule(4396)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -20499,9 +20836,10 @@
           <t>poststelle3107@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J338">
-        <f>"Schule("&amp;B338&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Schule(3107)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="339">
@@ -20523,9 +20861,10 @@
           <t>poststelle4301@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J339">
-        <f>"Schule("&amp;B339&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>Schule(4301)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="340">
@@ -20547,9 +20886,10 @@
           <t>poststelle3165@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J340">
-        <f>"Schule("&amp;B340&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Schule(3165)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="341">
@@ -20571,9 +20911,10 @@
           <t>poststelle3122@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J341">
-        <f>"Schule("&amp;B341&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>Schule(3122)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="342">
@@ -20595,9 +20936,10 @@
           <t>poststelle3111@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J342">
-        <f>"Schule("&amp;B342&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Schule(3111)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="343">
@@ -20619,9 +20961,10 @@
           <t>poststelle3155@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J343">
-        <f>"Schule("&amp;B343&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>Schule(3155)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="344">
@@ -20643,9 +20986,10 @@
           <t>poststelle3116@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J344">
-        <f>"Schule("&amp;B344&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>Schule(3116)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="345">
@@ -20667,9 +21011,10 @@
           <t>poststelle7356@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J345">
-        <f>"Schule("&amp;B345&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>Schule(7356)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="346">
@@ -20691,9 +21036,10 @@
           <t>poststelle7258@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J346">
-        <f>"Schule("&amp;B346&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>Schule(7258)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="347">
@@ -20715,9 +21061,10 @@
           <t>poststelle7254@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J347">
-        <f>"Schule("&amp;B347&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>Schule(7254)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="348">
@@ -20739,9 +21086,10 @@
           <t>poststelle7263@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J348">
-        <f>"Schule("&amp;B348&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Schule(7263)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="349">
@@ -20763,9 +21111,10 @@
           <t>poststelle7238@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J349">
-        <f>"Schule("&amp;B349&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>Schule(7238)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="350">
@@ -20787,9 +21136,10 @@
           <t>poststelle7237@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J350">
-        <f>"Schule("&amp;B350&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>Schule(7237)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="351">
@@ -20811,9 +21161,10 @@
           <t>poststelle7367@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J351">
-        <f>"Schule("&amp;B351&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Schule(7367)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="352">
@@ -20835,9 +21186,10 @@
           <t>poststelle7283@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J352">
-        <f>"Schule("&amp;B352&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Schule(7283)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="353">
@@ -20859,9 +21211,10 @@
           <t>poststelle7285@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J353">
-        <f>"Schule("&amp;B353&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>Schule(7285)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="354">
@@ -20883,9 +21236,10 @@
           <t>poststelle7234@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J354">
-        <f>"Schule("&amp;B354&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>Schule(7234)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="355">
@@ -20907,9 +21261,10 @@
           <t>poststelle7245@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J355">
-        <f>"Schule("&amp;B355&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>Schule(7245)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="356">
@@ -20931,9 +21286,10 @@
           <t>poststelle7290@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J356">
-        <f>"Schule("&amp;B356&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>Schule(7290)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="357">
@@ -20955,9 +21311,10 @@
           <t>poststelle7100@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J357">
-        <f>"Schule("&amp;B357&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Schule(7100)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="358">
@@ -20979,9 +21336,10 @@
           <t>poststelle7236@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J358">
-        <f>"Schule("&amp;B358&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>Schule(7236)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="359">
@@ -21003,9 +21361,10 @@
           <t>poststelle7288@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J359">
-        <f>"Schule("&amp;B359&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Schule(7288)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="360">
@@ -21027,9 +21386,10 @@
           <t>poststelle7294@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J360">
-        <f>"Schule("&amp;B360&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>Schule(7294)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="361">
@@ -21051,9 +21411,10 @@
           <t>poststelle7373@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J361">
-        <f>"Schule("&amp;B361&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Schule(7373)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="362">
@@ -21075,9 +21436,10 @@
           <t>poststelle7661@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J362">
-        <f>"Schule("&amp;B362&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>Schule(7661)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="363">
@@ -21099,9 +21461,10 @@
           <t>poststelle7281@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J363">
-        <f>"Schule("&amp;B363&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>Schule(7281)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="364">
@@ -21123,9 +21486,10 @@
           <t>poststelle7248@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J364">
-        <f>"Schule("&amp;B364&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Schule(7248)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="365">
@@ -21147,9 +21511,10 @@
           <t>poststelle3782@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J365">
-        <f>"Schule("&amp;B365&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Schule(3782)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="366">
@@ -21171,9 +21536,10 @@
           <t>poststelle3932@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J366">
-        <f>"Schule("&amp;B366&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Schule(3932)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="367">
@@ -21195,9 +21561,10 @@
           <t>poststelle3934@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J367">
-        <f>"Schule("&amp;B367&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>Schule(3934)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="368">
@@ -21219,9 +21586,10 @@
           <t>poststelle3796@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J368">
-        <f>"Schule("&amp;B368&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Schule(3796)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="369">
@@ -21243,9 +21611,10 @@
           <t>poststelle3813@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J369">
-        <f>"Schule("&amp;B369&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Schule(3813)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="370">
@@ -21267,9 +21636,10 @@
           <t>poststelle3933@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J370">
-        <f>"Schule("&amp;B370&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>Schule(3933)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="371">
@@ -21291,9 +21661,10 @@
           <t>poststelle3936@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J371">
-        <f>"Schule("&amp;B371&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>Schule(3936)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="372">
@@ -21315,9 +21686,10 @@
           <t>poststelle4196@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J372">
-        <f>"Schule("&amp;B372&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>Schule(4196)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="373">
@@ -21339,9 +21711,10 @@
           <t>poststelle3780@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J373">
-        <f>"Schule("&amp;B373&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Schule(3780)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="374">
@@ -21363,9 +21736,10 @@
           <t>poststelle3956@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J374">
-        <f>"Schule("&amp;B374&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Schule(3956)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="375">
@@ -21387,9 +21761,10 @@
           <t>poststelle3787@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J375">
-        <f>"Schule("&amp;B375&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>Schule(3787)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="376">
@@ -21411,9 +21786,10 @@
           <t>poststelle3794@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J376">
-        <f>"Schule("&amp;B376&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Schule(3794)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="377">
@@ -21435,9 +21811,10 @@
           <t>poststelle3921@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J377">
-        <f>"Schule("&amp;B377&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Schule(3921)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="378">
@@ -21459,9 +21836,10 @@
           <t>poststelle3789@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J378">
-        <f>"Schule("&amp;B378&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Schule(3789)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="379">
@@ -21483,9 +21861,10 @@
           <t>poststelle3812@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J379">
-        <f>"Schule("&amp;B379&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Schule(3812)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="380">
@@ -21507,9 +21886,10 @@
           <t>poststelle4308@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J380">
-        <f>"Schule("&amp;B380&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Schule(4308)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="381">
@@ -21531,9 +21911,10 @@
           <t>poststelle3930@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J381">
-        <f>"Schule("&amp;B381&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Schule(3930)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="382">
@@ -21555,9 +21936,10 @@
           <t>poststelle3795@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J382">
-        <f>"Schule("&amp;B382&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>Schule(3795)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="383">
@@ -21579,9 +21961,10 @@
           <t>poststelle3792@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J383">
-        <f>"Schule("&amp;B383&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>Schule(3792)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="384">
@@ -21603,9 +21986,10 @@
           <t>poststelle3776@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J384">
-        <f>"Schule("&amp;B384&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>Schule(3776)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="385">
@@ -21627,9 +22011,10 @@
           <t>poststelle3869@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J385">
-        <f>"Schule("&amp;B385&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>Schule(3869)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="386">
@@ -21651,9 +22036,10 @@
           <t>poststelle3862@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J386">
-        <f>"Schule("&amp;B386&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>Schule(3862)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="387">
@@ -21675,9 +22061,10 @@
           <t>poststelle3767@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J387">
-        <f>"Schule("&amp;B387&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>Schule(3767)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="388">
@@ -21699,9 +22086,10 @@
           <t>poststelle3772@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J388">
-        <f>"Schule("&amp;B388&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Schule(3772)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="389">
@@ -21723,9 +22111,10 @@
           <t>poststelle4285@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J389">
-        <f>"Schule("&amp;B389&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>Schule(4285)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="390">
@@ -21747,9 +22136,10 @@
           <t>poststelle4157@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J390">
-        <f>"Schule("&amp;B390&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Schule(4157)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="391">
@@ -21771,9 +22161,10 @@
           <t>poststelle3304@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J391">
-        <f>"Schule("&amp;B391&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Schule(3304)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="392">
@@ -21795,9 +22186,10 @@
           <t>poststelle3301@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J392">
-        <f>"Schule("&amp;B392&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>Schule(3301)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="393">
@@ -21819,9 +22211,10 @@
           <t>poststelle3764@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J393">
-        <f>"Schule("&amp;B393&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>Schule(3764)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="394">
@@ -21843,9 +22236,10 @@
           <t>poststelle3724@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J394">
-        <f>"Schule("&amp;B394&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Schule(3724)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="395">
@@ -21867,9 +22261,10 @@
           <t>poststelle4178@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J395">
-        <f>"Schule("&amp;B395&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>Schule(4178)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="396">
@@ -21891,9 +22286,10 @@
           <t>poststelle3228@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J396">
-        <f>"Schule("&amp;B396&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>Schule(3228)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="397">
@@ -21915,9 +22311,10 @@
           <t>poststelle4222@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J397">
-        <f>"Schule("&amp;B397&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>Schule(4222)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="398">
@@ -21939,9 +22336,10 @@
           <t>poststelle3311@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J398">
-        <f>"Schule("&amp;B398&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>Schule(3311)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="399">
@@ -21963,9 +22361,10 @@
           <t>poststelle3733@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J399">
-        <f>"Schule("&amp;B399&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>Schule(3733)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="400">
@@ -21987,9 +22386,10 @@
           <t>poststelle4181@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J400">
-        <f>"Schule("&amp;B400&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>Schule(4181)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="401">
@@ -22011,9 +22411,10 @@
           <t>poststelle3229@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J401">
-        <f>"Schule("&amp;B401&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>Schule(3229)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="402">
@@ -22035,9 +22436,10 @@
           <t>poststelle3735@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J402">
-        <f>"Schule("&amp;B402&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>Schule(3735)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="403">
@@ -22059,9 +22461,10 @@
           <t>poststelle3740@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J403">
-        <f>"Schule("&amp;B403&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Schule(3740)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="404">
@@ -22083,9 +22486,10 @@
           <t>poststelle3758@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J404">
-        <f>"Schule("&amp;B404&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Schule(3758)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="405">
@@ -22107,9 +22511,10 @@
           <t>poststelle7522@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J405">
-        <f>"Schule("&amp;B405&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>Schule(7522)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="406">
@@ -22131,9 +22536,10 @@
           <t>poststelle7512@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J406">
-        <f>"Schule("&amp;B406&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>Schule(7512)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="407">
@@ -22155,9 +22561,10 @@
           <t>poststelle7508@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J407">
-        <f>"Schule("&amp;B407&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>Schule(7508)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="408">
@@ -22179,9 +22586,10 @@
           <t>poststelle7607@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J408">
-        <f>"Schule("&amp;B408&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>Schule(7607)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="409">
@@ -22203,9 +22611,10 @@
           <t>poststelle7308@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J409">
-        <f>"Schule("&amp;B409&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>Schule(7308)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="410">
@@ -22227,9 +22636,10 @@
           <t>poststelle7330@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J410">
-        <f>"Schule("&amp;B410&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>Schule(7330)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="411">
@@ -22251,9 +22661,10 @@
           <t>poststelle7146@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J411">
-        <f>"Schule("&amp;B411&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>Schule(7146)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="412">
@@ -22275,9 +22686,10 @@
           <t>poststelle7579@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J412">
-        <f>"Schule("&amp;B412&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>Schule(7579)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="413">
@@ -22299,9 +22711,10 @@
           <t>poststelle7510@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J413">
-        <f>"Schule("&amp;B413&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>Schule(7510)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="414">
@@ -22323,9 +22736,10 @@
           <t>poststelle7331@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J414">
-        <f>"Schule("&amp;B414&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>Schule(7331)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="415">
@@ -22347,9 +22761,10 @@
           <t>poststelle7524@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J415">
-        <f>"Schule("&amp;B415&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>Schule(7524)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="416">
@@ -22371,9 +22786,10 @@
           <t>poststelle7583@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J416">
-        <f>"Schule("&amp;B416&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>Schule(7583)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="417">
@@ -22395,9 +22811,10 @@
           <t>poststelle7158@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J417">
-        <f>"Schule("&amp;B417&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>Schule(7158)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="418">
@@ -22419,9 +22836,10 @@
           <t>poststelle7334@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J418">
-        <f>"Schule("&amp;B418&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Schule(7334)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="419">
@@ -22443,9 +22861,10 @@
           <t>poststelle7300@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J419">
-        <f>"Schule("&amp;B419&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>Schule(7300)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="420">
@@ -22467,9 +22886,10 @@
           <t>poststelle7485@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J420">
-        <f>"Schule("&amp;B420&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>Schule(7485)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="421">
@@ -22491,9 +22911,10 @@
           <t>poststelle7582@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J421">
-        <f>"Schule("&amp;B421&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>Schule(7582)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="422">
@@ -22515,9 +22936,10 @@
           <t>poststelle7299@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J422">
-        <f>"Schule("&amp;B422&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>Schule(7299)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="423">
@@ -22539,9 +22961,10 @@
           <t>poststelle7658@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J423">
-        <f>"Schule("&amp;B423&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>Schule(7658)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="424">
@@ -22563,9 +22986,10 @@
           <t>poststelle7148@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J424">
-        <f>"Schule("&amp;B424&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>Schule(7148)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="425">
@@ -22587,9 +23011,10 @@
           <t>poststelle3454@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J425">
-        <f>"Schule("&amp;B425&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>Schule(3454)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="426">
@@ -22611,9 +23036,10 @@
           <t>poststelle4871@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J426">
-        <f>"Schule("&amp;B426&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Schule(4871)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="427">
@@ -22635,9 +23061,10 @@
           <t>poststelle3650@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J427">
-        <f>"Schule("&amp;B427&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>Schule(3650)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="428">
@@ -22659,9 +23086,10 @@
           <t>poststelle4873@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J428">
-        <f>"Schule("&amp;B428&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>Schule(4873)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="429">
@@ -22683,9 +23111,10 @@
           <t>poststelle3440@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J429">
-        <f>"Schule("&amp;B429&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>Schule(3440)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="430">
@@ -22707,9 +23136,10 @@
           <t>poststelle3660@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J430">
-        <f>"Schule("&amp;B430&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Schule(3660)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="431">
@@ -22731,9 +23161,10 @@
           <t>poststelle3439@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J431">
-        <f>"Schule("&amp;B431&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Schule(3439)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="432">
@@ -22755,9 +23186,10 @@
           <t>poststelle3628@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J432">
-        <f>"Schule("&amp;B432&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>Schule(3628)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="433">
@@ -22779,9 +23211,10 @@
           <t>poststelle4014@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J433">
-        <f>"Schule("&amp;B433&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>Schule(4014)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="434">
@@ -22803,9 +23236,10 @@
           <t>poststelle4009@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J434">
-        <f>"Schule("&amp;B434&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>Schule(4009)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="435">
@@ -22827,9 +23261,10 @@
           <t>poststelle3672@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J435">
-        <f>"Schule("&amp;B435&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>Schule(3672)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="436">
@@ -22851,9 +23286,10 @@
           <t>poststelle4000@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J436">
-        <f>"Schule("&amp;B436&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>Schule(4000)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="437">
@@ -22875,9 +23311,10 @@
           <t>poststelle4282@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J437">
-        <f>"Schule("&amp;B437&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Schule(4282)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="438">
@@ -22899,9 +23336,10 @@
           <t>poststelle3630@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J438">
-        <f>"Schule("&amp;B438&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Schule(3630)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="439">
@@ -22923,9 +23361,10 @@
           <t>poststelle3671@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J439">
-        <f>"Schule("&amp;B439&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Schule(3671)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="440">
@@ -22947,9 +23386,10 @@
           <t>poststelle4261@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J440">
-        <f>"Schule("&amp;B440&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Schule(4261)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="441">
@@ -22971,9 +23411,10 @@
           <t>poststelle4246@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J441">
-        <f>"Schule("&amp;B441&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>Schule(4246)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="442">
@@ -22995,9 +23436,10 @@
           <t>poststelle3998@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J442">
-        <f>"Schule("&amp;B442&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Schule(3998)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="443">
@@ -23019,9 +23461,10 @@
           <t>poststelle3631@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J443">
-        <f>"Schule("&amp;B443&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>Schule(3631)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="444">
@@ -23043,9 +23486,10 @@
           <t>poststelle4013@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J444">
-        <f>"Schule("&amp;B444&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Schule(4013)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="445">
@@ -23067,9 +23511,10 @@
           <t>poststelle7354@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J445">
-        <f>"Schule("&amp;B445&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>Schule(7354)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="446">
@@ -23091,9 +23536,10 @@
           <t>poststelle7350@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J446">
-        <f>"Schule("&amp;B446&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Schule(7350)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="447">
@@ -23115,9 +23561,10 @@
           <t>poststelle7340@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J447">
-        <f>"Schule("&amp;B447&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Schule(7340)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="448">
@@ -23139,9 +23586,10 @@
           <t>poststelle7403@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J448">
-        <f>"Schule("&amp;B448&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Schule(7403)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="449">
@@ -23163,9 +23611,10 @@
           <t>poststelle7355@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J449">
-        <f>"Schule("&amp;B449&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Schule(7355)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="450">
@@ -23187,9 +23636,10 @@
           <t>poststelle7593@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J450">
-        <f>"Schule("&amp;B450&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>Schule(7593)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="451">
@@ -23211,9 +23661,10 @@
           <t>poststelle7351@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J451">
-        <f>"Schule("&amp;B451&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>Schule(7351)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="452">
@@ -23235,9 +23686,10 @@
           <t>poststelle7588@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J452">
-        <f>"Schule("&amp;B452&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>Schule(7588)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="453">
@@ -23259,9 +23711,10 @@
           <t>poststelle7404@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J453">
-        <f>"Schule("&amp;B453&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>Schule(7404)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="454">
@@ -23283,9 +23736,10 @@
           <t>poststelle7406@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J454">
-        <f>"Schule("&amp;B454&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>Schule(7406)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="455">
@@ -23307,9 +23761,10 @@
           <t>poststelle7646@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J455">
-        <f>"Schule("&amp;B455&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>Schule(7646)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="456">
@@ -23331,9 +23786,10 @@
           <t>poststelle7388@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J456">
-        <f>"Schule("&amp;B456&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>Schule(7388)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="457">
@@ -23355,9 +23811,10 @@
           <t>poststelle7660@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J457">
-        <f>"Schule("&amp;B457&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>Schule(7660)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="458">
@@ -23379,9 +23836,10 @@
           <t>poststelle7650@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J458">
-        <f>"Schule("&amp;B458&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>Schule(7650)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="459">
@@ -23403,9 +23861,10 @@
           <t>poststelle7109@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J459">
-        <f>"Schule("&amp;B459&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>Schule(7109)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="460">
@@ -23427,9 +23886,10 @@
           <t>poststelle7135@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J460">
-        <f>"Schule("&amp;B460&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>Schule(7135)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="461">
@@ -23451,9 +23911,10 @@
           <t>poststelle7132@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J461">
-        <f>"Schule("&amp;B461&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>Schule(7132)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="462">
@@ -23475,9 +23936,10 @@
           <t>poststelle7112@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J462">
-        <f>"Schule("&amp;B462&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>Schule(7112)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="463">
@@ -23499,9 +23961,10 @@
           <t>poststelle7382@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J463">
-        <f>"Schule("&amp;B463&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>Schule(7382)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="464">
@@ -23523,9 +23986,10 @@
           <t>poststelle7662@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J464">
-        <f>"Schule("&amp;B464&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>Schule(7662)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="465">
@@ -23547,9 +24011,10 @@
           <t>poststelle3592@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J465">
-        <f>"Schule("&amp;B465&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>Schule(3592)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="466">
@@ -23571,9 +24036,10 @@
           <t>poststelle4143@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J466">
-        <f>"Schule("&amp;B466&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>Schule(4143)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="467">
@@ -23595,9 +24061,10 @@
           <t>poststelle3980@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J467">
-        <f>"Schule("&amp;B467&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>Schule(3980)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="468">
@@ -23619,9 +24086,10 @@
           <t>poststelle4158@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J468">
-        <f>"Schule("&amp;B468&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>Schule(4158)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="469">
@@ -23643,9 +24111,10 @@
           <t>poststelle4161@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J469">
-        <f>"Schule("&amp;B469&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>Schule(4161)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="470">
@@ -23667,9 +24136,10 @@
           <t>poststelle3912@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J470">
-        <f>"Schule("&amp;B470&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>Schule(3912)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="471">
@@ -23691,9 +24161,10 @@
           <t>poststelle4155@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J471">
-        <f>"Schule("&amp;B471&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>Schule(4155)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="472">
@@ -23715,9 +24186,10 @@
           <t>poststelle4148@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J472">
-        <f>"Schule("&amp;B472&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>Schule(4148)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="473">
@@ -23739,9 +24211,10 @@
           <t>poststelle3897@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J473">
-        <f>"Schule("&amp;B473&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>Schule(3897)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="474">
@@ -23763,9 +24236,10 @@
           <t>poststelle4142@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J474">
-        <f>"Schule("&amp;B474&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>Schule(4142)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="475">
@@ -23787,9 +24261,10 @@
           <t>poststelle3551@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J475">
-        <f>"Schule("&amp;B475&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>Schule(3551)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="476">
@@ -23811,9 +24286,10 @@
           <t>poststelle3993@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J476">
-        <f>"Schule("&amp;B476&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>Schule(3993)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="477">
@@ -23835,9 +24311,10 @@
           <t>poststelle3961@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J477">
-        <f>"Schule("&amp;B477&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>Schule(3961)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="478">
@@ -23859,9 +24336,10 @@
           <t>poststelle3558@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J478">
-        <f>"Schule("&amp;B478&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>Schule(3558)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="479">
@@ -23883,9 +24361,10 @@
           <t>poststelle4160@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J479">
-        <f>"Schule("&amp;B479&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>Schule(4160)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="480">
@@ -23907,9 +24386,10 @@
           <t>poststelle3891@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J480">
-        <f>"Schule("&amp;B480&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>Schule(3891)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="481">
@@ -23931,9 +24411,10 @@
           <t>poststelle4173@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J481">
-        <f>"Schule("&amp;B481&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>Schule(4173)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="482">
@@ -23955,9 +24436,10 @@
           <t>poststelle4162@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J482">
-        <f>"Schule("&amp;B482&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>Schule(4162)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="483">
@@ -23979,9 +24461,10 @@
           <t>poststelle3572@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J483">
-        <f>"Schule("&amp;B483&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>Schule(3572)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="484">
@@ -24003,9 +24486,10 @@
           <t>poststelle3578@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J484">
-        <f>"Schule("&amp;B484&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>Schule(3578)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="485">
@@ -24027,9 +24511,10 @@
           <t>poststelle4088@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J485">
-        <f>"Schule("&amp;B485&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>Schule(4088)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="486">
@@ -24051,9 +24536,10 @@
           <t>poststelle3722@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J486">
-        <f>"Schule("&amp;B486&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>Schule(3722)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="487">
@@ -24075,9 +24561,10 @@
           <t>poststelle3698@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J487">
-        <f>"Schule("&amp;B487&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>Schule(3698)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="488">
@@ -24099,9 +24586,10 @@
           <t>poststelle3697@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J488">
-        <f>"Schule("&amp;B488&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>Schule(3697)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="489">
@@ -24123,9 +24611,10 @@
           <t>poststelle3708@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J489">
-        <f>"Schule("&amp;B489&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>Schule(3708)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="490">
@@ -24147,9 +24636,10 @@
           <t>poststelle3714@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J490">
-        <f>"Schule("&amp;B490&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>Schule(3714)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="491">
@@ -24171,9 +24661,10 @@
           <t>poststelle4936@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J491">
-        <f>"Schule("&amp;B491&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>Schule(4936)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="492">
@@ -24195,9 +24686,10 @@
           <t>poststelle4931@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J492">
-        <f>"Schule("&amp;B492&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>Schule(4931)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="493">
@@ -24219,9 +24711,10 @@
           <t>poststelle3710@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J493">
-        <f>"Schule("&amp;B493&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>Schule(3710)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="494">
@@ -24243,9 +24736,10 @@
           <t>poststelle3703@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J494">
-        <f>"Schule("&amp;B494&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>Schule(3703)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="495">
@@ -24267,9 +24761,10 @@
           <t>poststelle3834@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J495">
-        <f>"Schule("&amp;B495&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>Schule(3834)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="496">
@@ -24291,9 +24786,10 @@
           <t>poststelle3849@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J496">
-        <f>"Schule("&amp;B496&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>Schule(3849)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="497">
@@ -24315,9 +24811,10 @@
           <t>poststelle3845@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J497">
-        <f>"Schule("&amp;B497&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>Schule(3845)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="498">
@@ -24339,9 +24836,10 @@
           <t>poststelle4939@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J498">
-        <f>"Schule("&amp;B498&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>Schule(4939)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="499">
@@ -24363,9 +24861,10 @@
           <t>poststelle3236@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J499">
-        <f>"Schule("&amp;B499&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>Schule(3236)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="500">
@@ -24387,9 +24886,10 @@
           <t>poststelle3843@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J500">
-        <f>"Schule("&amp;B500&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>Schule(3843)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="501">
@@ -24411,9 +24911,10 @@
           <t>poststelle3840@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J501">
-        <f>"Schule("&amp;B501&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>Schule(3840)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="502">
@@ -24435,9 +24936,10 @@
           <t>poststelle4212@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J502">
-        <f>"Schule("&amp;B502&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Schule(4212)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="503">
@@ -24459,9 +24961,10 @@
           <t>poststelle3826@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J503">
-        <f>"Schule("&amp;B503&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Schule(3826)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="504">
@@ -24483,9 +24986,10 @@
           <t>poststelle3239@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J504">
-        <f>"Schule("&amp;B504&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Schule(3239)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="505">
@@ -24507,9 +25011,10 @@
           <t>poststelle7419@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J505">
-        <f>"Schule("&amp;B505&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Schule(7419)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="506">
@@ -24531,9 +25036,10 @@
           <t>poststelle7411@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J506">
-        <f>"Schule("&amp;B506&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>Schule(7411)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="507">
@@ -24555,9 +25061,10 @@
           <t>poststelle3411@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J507">
-        <f>"Schule("&amp;B507&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>Schule(3411)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="508">
@@ -24579,9 +25086,10 @@
           <t>poststelle3416@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J508">
-        <f>"Schule("&amp;B508&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Schule(3416)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="509">
@@ -24603,9 +25111,10 @@
           <t>poststelle3400@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J509">
-        <f>"Schule("&amp;B509&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Schule(3400)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="510">
@@ -24627,9 +25136,10 @@
           <t>poststelle7430@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J510">
-        <f>"Schule("&amp;B510&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>Schule(7430)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="511">
@@ -24651,9 +25161,10 @@
           <t>poststelle7470@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J511">
-        <f>"Schule("&amp;B511&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>Schule(7470)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="512">
@@ -24675,9 +25186,10 @@
           <t>poststelle7442@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J512">
-        <f>"Schule("&amp;B512&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>Schule(7442)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="513">
@@ -24699,9 +25211,10 @@
           <t>poststelle7418@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J513">
-        <f>"Schule("&amp;B513&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>Schule(7418)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="514">
@@ -24723,9 +25236,10 @@
           <t>poststelle3393@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J514">
-        <f>"Schule("&amp;B514&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>Schule(3393)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="515">
@@ -24747,9 +25261,10 @@
           <t>poststelle3401@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J515">
-        <f>"Schule("&amp;B515&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>Schule(3401)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="516">
@@ -24771,9 +25286,10 @@
           <t>poststelle7427@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J516">
-        <f>"Schule("&amp;B516&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>Schule(7427)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="517">
@@ -24795,9 +25311,10 @@
           <t>poststelle7422@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J517">
-        <f>"Schule("&amp;B517&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>Schule(7422)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="518">
@@ -24819,9 +25336,10 @@
           <t>poststelle7443@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J518">
-        <f>"Schule("&amp;B518&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>Schule(7443)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="519">
@@ -24843,9 +25361,10 @@
           <t>poststelle7138@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J519">
-        <f>"Schule("&amp;B519&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>Schule(7138)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="520">
@@ -24867,9 +25386,10 @@
           <t>poststelle3414@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J520">
-        <f>"Schule("&amp;B520&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>Schule(3414)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="521">
@@ -24891,9 +25411,10 @@
           <t>poststelle7464@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J521">
-        <f>"Schule("&amp;B521&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Schule(7464)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="522">
@@ -24915,9 +25436,10 @@
           <t>poststelle7417@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J522">
-        <f>"Schule("&amp;B522&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>Schule(7417)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="523">
@@ -24939,9 +25461,10 @@
           <t>poststelle7457@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J523">
-        <f>"Schule("&amp;B523&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>Schule(7457)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="524">
@@ -24963,9 +25486,10 @@
           <t>poststelle7426@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J524">
-        <f>"Schule("&amp;B524&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>Schule(7426)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="525">
@@ -24987,9 +25511,10 @@
           <t>poststelle4442@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J525">
-        <f>"Schule("&amp;B525&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>Schule(4442)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="526">
@@ -25011,9 +25536,10 @@
           <t>poststelle4026@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J526">
-        <f>"Schule("&amp;B526&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>Schule(4026)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="527">
@@ -25035,9 +25561,10 @@
           <t>poststelle4201@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J527">
-        <f>"Schule("&amp;B527&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>Schule(4201)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="528">
@@ -25059,9 +25586,10 @@
           <t>poststelle4040@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J528">
-        <f>"Schule("&amp;B528&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>Schule(4040)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="529">
@@ -25083,9 +25611,10 @@
           <t>poststelle4249@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J529">
-        <f>"Schule("&amp;B529&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>Schule(4249)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="530">
@@ -25107,9 +25636,10 @@
           <t>poststelle4027@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J530">
-        <f>"Schule("&amp;B530&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>Schule(4027)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="531">
@@ -25131,9 +25661,10 @@
           <t>poststelle4060@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J531">
-        <f>"Schule("&amp;B531&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>Schule(4060)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="532">
@@ -25155,9 +25686,10 @@
           <t>poststelle3537@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J532">
-        <f>"Schule("&amp;B532&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>Schule(3537)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="533">
@@ -25179,9 +25711,10 @@
           <t>poststelle4036@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J533">
-        <f>"Schule("&amp;B533&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Schule(4036)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="534">
@@ -25203,9 +25736,10 @@
           <t>poststelle4023@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J534">
-        <f>"Schule("&amp;B534&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>Schule(4023)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="535">
@@ -25227,9 +25761,10 @@
           <t>poststelle4209@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J535">
-        <f>"Schule("&amp;B535&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>Schule(4209)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="536">
@@ -25251,9 +25786,10 @@
           <t>poststelle4056@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J536">
-        <f>"Schule("&amp;B536&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>Schule(4056)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="537">
@@ -25275,9 +25811,10 @@
           <t>poststelle3255@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J537">
-        <f>"Schule("&amp;B537&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>Schule(3255)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="538">
@@ -25299,9 +25836,10 @@
           <t>poststelle3242@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J538">
-        <f>"Schule("&amp;B538&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>Schule(3242)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="539">
@@ -25323,9 +25861,10 @@
           <t>poststelle3246@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J539">
-        <f>"Schule("&amp;B539&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>Schule(3246)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="540">
@@ -25347,9 +25886,10 @@
           <t>poststelle4032@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J540">
-        <f>"Schule("&amp;B540&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>Schule(4032)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="541">
@@ -25371,9 +25911,10 @@
           <t>poststelle4251@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J541">
-        <f>"Schule("&amp;B541&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>Schule(4251)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="542">
@@ -25395,9 +25936,10 @@
           <t>poststelle3243@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J542">
-        <f>"Schule("&amp;B542&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>Schule(3243)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="543">
@@ -25419,9 +25961,10 @@
           <t>poststelle4278@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J543">
-        <f>"Schule("&amp;B543&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>Schule(4278)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="544">
@@ -25443,9 +25986,10 @@
           <t>poststelle4030@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J544">
-        <f>"Schule("&amp;B544&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>Schule(4030)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="545">
@@ -25467,9 +26011,10 @@
           <t>poststelle4110@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J545">
-        <f>"Schule("&amp;B545&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>Schule(4110)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="546">
@@ -25491,9 +26036,10 @@
           <t>poststelle3196@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J546">
-        <f>"Schule("&amp;B546&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>Schule(3196)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="547">
@@ -25515,9 +26061,10 @@
           <t>poststelle3188@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J547">
-        <f>"Schule("&amp;B547&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>Schule(3188)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="548">
@@ -25539,9 +26086,10 @@
           <t>poststelle3187@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J548">
-        <f>"Schule("&amp;B548&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>Schule(3187)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="549">
@@ -25563,9 +26111,10 @@
           <t>poststelle3293@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J549">
-        <f>"Schule("&amp;B549&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>Schule(3293)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="550">
@@ -25587,9 +26136,10 @@
           <t>poststelle4109@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J550">
-        <f>"Schule("&amp;B550&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>Schule(4109)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="551">
@@ -25611,9 +26161,10 @@
           <t>poststelle4111@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J551">
-        <f>"Schule("&amp;B551&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>Schule(4111)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="552">
@@ -25635,9 +26186,10 @@
           <t>poststelle4116@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J552">
-        <f>"Schule("&amp;B552&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>Schule(4116)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="553">
@@ -25659,9 +26211,10 @@
           <t>poststelle3184@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J553">
-        <f>"Schule("&amp;B553&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>Schule(3184)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="554">
@@ -25683,9 +26236,10 @@
           <t>poststelle4256@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J554">
-        <f>"Schule("&amp;B554&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>Schule(4256)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="555">
@@ -25707,9 +26261,10 @@
           <t>poststelle3286@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J555">
-        <f>"Schule("&amp;B555&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>Schule(3286)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="556">
@@ -25731,9 +26286,10 @@
           <t>poststelle3259@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J556">
-        <f>"Schule("&amp;B556&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>Schule(3259)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="557">
@@ -25755,9 +26311,10 @@
           <t>poststelle4125@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J557">
-        <f>"Schule("&amp;B557&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>Schule(4125)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="558">
@@ -25779,9 +26336,10 @@
           <t>poststelle3186@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J558">
-        <f>"Schule("&amp;B558&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>Schule(3186)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="559">
@@ -25803,9 +26361,10 @@
           <t>poststelle3285@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J559">
-        <f>"Schule("&amp;B559&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>Schule(3285)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="560">
@@ -25827,9 +26386,10 @@
           <t>poststelle3282@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J560">
-        <f>"Schule("&amp;B560&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>Schule(3282)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="561">
@@ -25851,9 +26411,10 @@
           <t>poststelle3277@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J561">
-        <f>"Schule("&amp;B561&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>Schule(3277)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="562">
@@ -25875,9 +26436,10 @@
           <t>poststelle3266@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J562">
-        <f>"Schule("&amp;B562&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>Schule(3266)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="563">
@@ -25899,9 +26461,10 @@
           <t>poststelle3294@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J563">
-        <f>"Schule("&amp;B563&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>Schule(3294)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="564">
@@ -25923,9 +26486,10 @@
           <t>poststelle3271@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J564">
-        <f>"Schule("&amp;B564&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>Schule(3271)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="565">
@@ -25947,9 +26511,10 @@
           <t>poststelle7516@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J565">
-        <f>"Schule("&amp;B565&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>Schule(7516)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="566">
@@ -25971,9 +26536,10 @@
           <t>poststelle7490@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J566">
-        <f>"Schule("&amp;B566&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>Schule(7490)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="567">
@@ -25995,9 +26561,10 @@
           <t>poststelle7218@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J567">
-        <f>"Schule("&amp;B567&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>Schule(7218)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="568">
@@ -26019,9 +26586,10 @@
           <t>poststelle7196@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J568">
-        <f>"Schule("&amp;B568&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>Schule(7196)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="569">
@@ -26043,9 +26611,10 @@
           <t>poststelle7475@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J569">
-        <f>"Schule("&amp;B569&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>Schule(7475)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="570">
@@ -26067,9 +26636,10 @@
           <t>poststelle7630@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J570">
-        <f>"Schule("&amp;B570&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>Schule(7630)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="571">
@@ -26091,9 +26661,10 @@
           <t>poststelle7184@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J571">
-        <f>"Schule("&amp;B571&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>Schule(7184)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="572">
@@ -26115,9 +26686,10 @@
           <t>poststelle7232@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J572">
-        <f>"Schule("&amp;B572&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>Schule(7232)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="573">
@@ -26139,9 +26711,10 @@
           <t>poststelle7186@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J573">
-        <f>"Schule("&amp;B573&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>Schule(7186)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="574">
@@ -26163,9 +26736,10 @@
           <t>poststelle7621@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J574">
-        <f>"Schule("&amp;B574&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>Schule(7621)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="575">
@@ -26187,9 +26761,10 @@
           <t>poststelle7221@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J575">
-        <f>"Schule("&amp;B575&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>Schule(7221)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="576">
@@ -26211,9 +26786,10 @@
           <t>poststelle7568@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J576">
-        <f>"Schule("&amp;B576&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>Schule(7568)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="577">
@@ -26235,9 +26811,10 @@
           <t>poststelle7173@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J577">
-        <f>"Schule("&amp;B577&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>Schule(7173)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="578">
@@ -26259,9 +26836,10 @@
           <t>poststelle7679@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J578">
-        <f>"Schule("&amp;B578&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>Schule(7679)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="579">
@@ -26283,9 +26861,10 @@
           <t>poststelle7664@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J579">
-        <f>"Schule("&amp;B579&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>Schule(7664)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="580">
@@ -26307,9 +26886,10 @@
           <t>poststelle7670@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J580">
-        <f>"Schule("&amp;B580&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>Schule(7670)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="581">
@@ -26331,9 +26911,10 @@
           <t>poststelle7556@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J581">
-        <f>"Schule("&amp;B581&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>Schule(7556)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="582">
@@ -26355,9 +26936,10 @@
           <t>poststelle7205@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J582">
-        <f>"Schule("&amp;B582&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>Schule(7205)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="583">
@@ -26379,9 +26961,10 @@
           <t>poststelle7216@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J583">
-        <f>"Schule("&amp;B583&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>Schule(7216)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
     <row r="584">
@@ -26403,9 +26986,10 @@
           <t>poststelle7482@schule.hessen.de</t>
         </is>
       </c>
-      <c r="J584">
-        <f>"Schule("&amp;B584&amp;")@schule.hessen.de"</f>
-        <v/>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>Schule(7482)@schule.hessen.de</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Schulauswahl/Adressen_Rollout_Umfrage_erweitert_300_reine_Grundschulen.xlsx
+++ b/Schulauswahl/Adressen_Rollout_Umfrage_erweitert_300_reine_Grundschulen.xlsx
@@ -519,12 +519,12 @@
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>Schule(3105)@schule.hessen.de</t>
+          <t>Schule3105@schule.hessen.de</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Schulleitung(3105)@schule.hessen.de</t>
+          <t>Schulleitung3105@schule.hessen.de</t>
         </is>
       </c>
       <c r="L1" t="n">
@@ -602,12 +602,12 @@
       </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
-          <t>Schule(3106)@schule.hessen.de</t>
+          <t>Schule3106@schule.hessen.de</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Schulleitung(3106)@schule.hessen.de</t>
+          <t>Schulleitung3106@schule.hessen.de</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -680,12 +680,12 @@
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>Schule(3115)@schule.hessen.de</t>
+          <t>Schule3115@schule.hessen.de</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Schulleitung(3115)@schule.hessen.de</t>
+          <t>Schulleitung3115@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="J4" s="9" t="inlineStr">
         <is>
-          <t>Schule(3117)@schule.hessen.de</t>
+          <t>Schule3117@schule.hessen.de</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Schulleitung(3117)@schule.hessen.de</t>
+          <t>Schulleitung3117@schule.hessen.de</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -813,12 +813,12 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Schule(3123)@schule.hessen.de</t>
+          <t>Schule3123@schule.hessen.de</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Schulleitung(3123)@schule.hessen.de</t>
+          <t>Schulleitung3123@schule.hessen.de</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -896,12 +896,12 @@
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>Schule(3127)@schule.hessen.de</t>
+          <t>Schule3127@schule.hessen.de</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Schulleitung(3127)@schule.hessen.de</t>
+          <t>Schulleitung3127@schule.hessen.de</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -974,12 +974,12 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Schule(3135)@schule.hessen.de</t>
+          <t>Schule3135@schule.hessen.de</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Schulleitung(3135)@schule.hessen.de</t>
+          <t>Schulleitung3135@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>Schule(3137)@schule.hessen.de</t>
+          <t>Schule3137@schule.hessen.de</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Schulleitung(3137)@schule.hessen.de</t>
+          <t>Schulleitung3137@schule.hessen.de</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Schule(3150)@schule.hessen.de</t>
+          <t>Schule3150@schule.hessen.de</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Schulleitung(3150)@schule.hessen.de</t>
+          <t>Schulleitung3150@schule.hessen.de</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>Schule(3152)@schule.hessen.de</t>
+          <t>Schule3152@schule.hessen.de</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Schulleitung(3152)@schule.hessen.de</t>
+          <t>Schulleitung3152@schule.hessen.de</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Schule(3158)@schule.hessen.de</t>
+          <t>Schule3158@schule.hessen.de</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Schulleitung(3158)@schule.hessen.de</t>
+          <t>Schulleitung3158@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>Schule(3170)@schule.hessen.de</t>
+          <t>Schule3170@schule.hessen.de</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Schulleitung(3170)@schule.hessen.de</t>
+          <t>Schulleitung3170@schule.hessen.de</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Schule(3171)@schule.hessen.de</t>
+          <t>Schule3171@schule.hessen.de</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Schulleitung(3171)@schule.hessen.de</t>
+          <t>Schulleitung3171@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>Schule(3174)@schule.hessen.de</t>
+          <t>Schule3174@schule.hessen.de</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Schulleitung(3174)@schule.hessen.de</t>
+          <t>Schulleitung3174@schule.hessen.de</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Schule(3176)@schule.hessen.de</t>
+          <t>Schule3176@schule.hessen.de</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Schulleitung(3176)@schule.hessen.de</t>
+          <t>Schulleitung3176@schule.hessen.de</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Schule(3177)@schule.hessen.de</t>
+          <t>Schule3177@schule.hessen.de</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Schulleitung(3177)@schule.hessen.de</t>
+          <t>Schulleitung3177@schule.hessen.de</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Schule(3189)@schule.hessen.de</t>
+          <t>Schule3189@schule.hessen.de</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Schulleitung(3189)@schule.hessen.de</t>
+          <t>Schulleitung3189@schule.hessen.de</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Schule(3191)@schule.hessen.de</t>
+          <t>Schule3191@schule.hessen.de</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Schulleitung(3191)@schule.hessen.de</t>
+          <t>Schulleitung3191@schule.hessen.de</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Schule(3205)@schule.hessen.de</t>
+          <t>Schule3205@schule.hessen.de</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Schulleitung(3205)@schule.hessen.de</t>
+          <t>Schulleitung3205@schule.hessen.de</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>Schule(3209)@schule.hessen.de</t>
+          <t>Schule3209@schule.hessen.de</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Schulleitung(3209)@schule.hessen.de</t>
+          <t>Schulleitung3209@schule.hessen.de</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Schule(3211)@schule.hessen.de</t>
+          <t>Schule3211@schule.hessen.de</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Schulleitung(3211)@schule.hessen.de</t>
+          <t>Schulleitung3211@schule.hessen.de</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Schule(3212)@schule.hessen.de</t>
+          <t>Schule3212@schule.hessen.de</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Schulleitung(3212)@schule.hessen.de</t>
+          <t>Schulleitung3212@schule.hessen.de</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Schule(3213)@schule.hessen.de</t>
+          <t>Schule3213@schule.hessen.de</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Schulleitung(3213)@schule.hessen.de</t>
+          <t>Schulleitung3213@schule.hessen.de</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>Schule(3215)@schule.hessen.de</t>
+          <t>Schule3215@schule.hessen.de</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Schulleitung(3215)@schule.hessen.de</t>
+          <t>Schulleitung3215@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>Schule(3217)@schule.hessen.de</t>
+          <t>Schule3217@schule.hessen.de</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Schulleitung(3217)@schule.hessen.de</t>
+          <t>Schulleitung3217@schule.hessen.de</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>Schule(3221)@schule.hessen.de</t>
+          <t>Schule3221@schule.hessen.de</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Schulleitung(3221)@schule.hessen.de</t>
+          <t>Schulleitung3221@schule.hessen.de</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>Schule(3227)@schule.hessen.de</t>
+          <t>Schule3227@schule.hessen.de</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Schulleitung(3227)@schule.hessen.de</t>
+          <t>Schulleitung3227@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>Schule(3230)@schule.hessen.de</t>
+          <t>Schule3230@schule.hessen.de</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Schulleitung(3230)@schule.hessen.de</t>
+          <t>Schulleitung3230@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>Schule(3231)@schule.hessen.de</t>
+          <t>Schule3231@schule.hessen.de</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Schulleitung(3231)@schule.hessen.de</t>
+          <t>Schulleitung3231@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>Schule(3232)@schule.hessen.de</t>
+          <t>Schule3232@schule.hessen.de</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Schulleitung(3232)@schule.hessen.de</t>
+          <t>Schulleitung3232@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -2682,12 +2682,12 @@
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>Schule(3240)@schule.hessen.de</t>
+          <t>Schule3240@schule.hessen.de</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Schulleitung(3240)@schule.hessen.de</t>
+          <t>Schulleitung3240@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -2727,12 +2727,12 @@
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>Schule(3244)@schule.hessen.de</t>
+          <t>Schule3244@schule.hessen.de</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Schulleitung(3244)@schule.hessen.de</t>
+          <t>Schulleitung3244@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>Schule(3256)@schule.hessen.de</t>
+          <t>Schule3256@schule.hessen.de</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Schulleitung(3256)@schule.hessen.de</t>
+          <t>Schulleitung3256@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>Schule(3263)@schule.hessen.de</t>
+          <t>Schule3263@schule.hessen.de</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Schulleitung(3263)@schule.hessen.de</t>
+          <t>Schulleitung3263@schule.hessen.de</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>Schule(3264)@schule.hessen.de</t>
+          <t>Schule3264@schule.hessen.de</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Schulleitung(3264)@schule.hessen.de</t>
+          <t>Schulleitung3264@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>Schule(3270)@schule.hessen.de</t>
+          <t>Schule3270@schule.hessen.de</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Schulleitung(3270)@schule.hessen.de</t>
+          <t>Schulleitung3270@schule.hessen.de</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>Schule(3275)@schule.hessen.de</t>
+          <t>Schule3275@schule.hessen.de</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Schulleitung(3275)@schule.hessen.de</t>
+          <t>Schulleitung3275@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>Schule(3276)@schule.hessen.de</t>
+          <t>Schule3276@schule.hessen.de</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Schulleitung(3276)@schule.hessen.de</t>
+          <t>Schulleitung3276@schule.hessen.de</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>Schule(3288)@schule.hessen.de</t>
+          <t>Schule3288@schule.hessen.de</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Schulleitung(3288)@schule.hessen.de</t>
+          <t>Schulleitung3288@schule.hessen.de</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>Schule(3291)@schule.hessen.de</t>
+          <t>Schule3291@schule.hessen.de</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Schulleitung(3291)@schule.hessen.de</t>
+          <t>Schulleitung3291@schule.hessen.de</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>Schule(3292)@schule.hessen.de</t>
+          <t>Schule3292@schule.hessen.de</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Schulleitung(3292)@schule.hessen.de</t>
+          <t>Schulleitung3292@schule.hessen.de</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>Schule(3321)@schule.hessen.de</t>
+          <t>Schule3321@schule.hessen.de</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Schulleitung(3321)@schule.hessen.de</t>
+          <t>Schulleitung3321@schule.hessen.de</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>Schule(3322)@schule.hessen.de</t>
+          <t>Schule3322@schule.hessen.de</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Schulleitung(3322)@schule.hessen.de</t>
+          <t>Schulleitung3322@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -3538,12 +3538,12 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>Schule(3332)@schule.hessen.de</t>
+          <t>Schule3332@schule.hessen.de</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Schulleitung(3332)@schule.hessen.de</t>
+          <t>Schulleitung3332@schule.hessen.de</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>Schule(3351)@schule.hessen.de</t>
+          <t>Schule3351@schule.hessen.de</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Schulleitung(3351)@schule.hessen.de</t>
+          <t>Schulleitung3351@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3671,12 @@
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>Schule(3354)@schule.hessen.de</t>
+          <t>Schule3354@schule.hessen.de</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Schulleitung(3354)@schule.hessen.de</t>
+          <t>Schulleitung3354@schule.hessen.de</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>Schule(3357)@schule.hessen.de</t>
+          <t>Schule3357@schule.hessen.de</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Schulleitung(3357)@schule.hessen.de</t>
+          <t>Schulleitung3357@schule.hessen.de</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>Schule(3363)@schule.hessen.de</t>
+          <t>Schule3363@schule.hessen.de</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Schulleitung(3363)@schule.hessen.de</t>
+          <t>Schulleitung3363@schule.hessen.de</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>Schule(3364)@schule.hessen.de</t>
+          <t>Schule3364@schule.hessen.de</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Schulleitung(3364)@schule.hessen.de</t>
+          <t>Schulleitung3364@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>Schule(3366)@schule.hessen.de</t>
+          <t>Schule3366@schule.hessen.de</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Schulleitung(3366)@schule.hessen.de</t>
+          <t>Schulleitung3366@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>Schule(3397)@schule.hessen.de</t>
+          <t>Schule3397@schule.hessen.de</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Schulleitung(3397)@schule.hessen.de</t>
+          <t>Schulleitung3397@schule.hessen.de</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>Schule(3408)@schule.hessen.de</t>
+          <t>Schule3408@schule.hessen.de</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Schulleitung(3408)@schule.hessen.de</t>
+          <t>Schulleitung3408@schule.hessen.de</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>Schule(3409)@schule.hessen.de</t>
+          <t>Schule3409@schule.hessen.de</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Schulleitung(3409)@schule.hessen.de</t>
+          <t>Schulleitung3409@schule.hessen.de</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>Schule(3413)@schule.hessen.de</t>
+          <t>Schule3413@schule.hessen.de</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Schulleitung(3413)@schule.hessen.de</t>
+          <t>Schulleitung3413@schule.hessen.de</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>Schule(3426)@schule.hessen.de</t>
+          <t>Schule3426@schule.hessen.de</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Schulleitung(3426)@schule.hessen.de</t>
+          <t>Schulleitung3426@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -4392,12 +4392,12 @@
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>Schule(3433)@schule.hessen.de</t>
+          <t>Schule3433@schule.hessen.de</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Schulleitung(3433)@schule.hessen.de</t>
+          <t>Schulleitung3433@schule.hessen.de</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>Schule(3435)@schule.hessen.de</t>
+          <t>Schule3435@schule.hessen.de</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Schulleitung(3435)@schule.hessen.de</t>
+          <t>Schulleitung3435@schule.hessen.de</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>Schule(3521)@schule.hessen.de</t>
+          <t>Schule3521@schule.hessen.de</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Schulleitung(3521)@schule.hessen.de</t>
+          <t>Schulleitung3521@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>Schule(3530)@schule.hessen.de</t>
+          <t>Schule3530@schule.hessen.de</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Schulleitung(3530)@schule.hessen.de</t>
+          <t>Schulleitung3530@schule.hessen.de</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>Schule(3534)@schule.hessen.de</t>
+          <t>Schule3534@schule.hessen.de</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Schulleitung(3534)@schule.hessen.de</t>
+          <t>Schulleitung3534@schule.hessen.de</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>Schule(3538)@schule.hessen.de</t>
+          <t>Schule3538@schule.hessen.de</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Schulleitung(3538)@schule.hessen.de</t>
+          <t>Schulleitung3538@schule.hessen.de</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>Schule(3542)@schule.hessen.de</t>
+          <t>Schule3542@schule.hessen.de</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Schulleitung(3542)@schule.hessen.de</t>
+          <t>Schulleitung3542@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -4897,12 +4897,12 @@
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>Schule(3553)@schule.hessen.de</t>
+          <t>Schule3553@schule.hessen.de</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Schulleitung(3553)@schule.hessen.de</t>
+          <t>Schulleitung3553@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>Schule(3561)@schule.hessen.de</t>
+          <t>Schule3561@schule.hessen.de</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Schulleitung(3561)@schule.hessen.de</t>
+          <t>Schulleitung3561@schule.hessen.de</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>Schule(3563)@schule.hessen.de</t>
+          <t>Schule3563@schule.hessen.de</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Schulleitung(3563)@schule.hessen.de</t>
+          <t>Schulleitung3563@schule.hessen.de</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>Schule(3579)@schule.hessen.de</t>
+          <t>Schule3579@schule.hessen.de</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Schulleitung(3579)@schule.hessen.de</t>
+          <t>Schulleitung3579@schule.hessen.de</t>
         </is>
       </c>
       <c r="L66" t="n">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>Schule(3591)@schule.hessen.de</t>
+          <t>Schule3591@schule.hessen.de</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Schulleitung(3591)@schule.hessen.de</t>
+          <t>Schulleitung3591@schule.hessen.de</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>Schule(3591)@schule.hessen.de</t>
+          <t>Schule3591@schule.hessen.de</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Schulleitung(3591)@schule.hessen.de</t>
+          <t>Schulleitung3591@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>Schule(3603)@schule.hessen.de</t>
+          <t>Schule3603@schule.hessen.de</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Schulleitung(3603)@schule.hessen.de</t>
+          <t>Schulleitung3603@schule.hessen.de</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>Schule(3606)@schule.hessen.de</t>
+          <t>Schule3606@schule.hessen.de</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Schulleitung(3606)@schule.hessen.de</t>
+          <t>Schulleitung3606@schule.hessen.de</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>Schule(3617)@schule.hessen.de</t>
+          <t>Schule3617@schule.hessen.de</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Schulleitung(3617)@schule.hessen.de</t>
+          <t>Schulleitung3617@schule.hessen.de</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>Schule(3622)@schule.hessen.de</t>
+          <t>Schule3622@schule.hessen.de</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Schulleitung(3622)@schule.hessen.de</t>
+          <t>Schulleitung3622@schule.hessen.de</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>Schule(3624)@schule.hessen.de</t>
+          <t>Schule3624@schule.hessen.de</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Schulleitung(3624)@schule.hessen.de</t>
+          <t>Schulleitung3624@schule.hessen.de</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>Schule(3629)@schule.hessen.de</t>
+          <t>Schule3629@schule.hessen.de</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Schulleitung(3629)@schule.hessen.de</t>
+          <t>Schulleitung3629@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -5784,12 +5784,12 @@
       </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>Schule(3635)@schule.hessen.de</t>
+          <t>Schule3635@schule.hessen.de</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Schulleitung(3635)@schule.hessen.de</t>
+          <t>Schulleitung3635@schule.hessen.de</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>Schule(3638)@schule.hessen.de</t>
+          <t>Schule3638@schule.hessen.de</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Schulleitung(3638)@schule.hessen.de</t>
+          <t>Schulleitung3638@schule.hessen.de</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>Schule(3644)@schule.hessen.de</t>
+          <t>Schule3644@schule.hessen.de</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Schulleitung(3644)@schule.hessen.de</t>
+          <t>Schulleitung3644@schule.hessen.de</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>Schule(3648)@schule.hessen.de</t>
+          <t>Schule3648@schule.hessen.de</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Schulleitung(3648)@schule.hessen.de</t>
+          <t>Schulleitung3648@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -6083,12 +6083,12 @@
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>Schule(3656)@schule.hessen.de</t>
+          <t>Schule3656@schule.hessen.de</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Schulleitung(3656)@schule.hessen.de</t>
+          <t>Schulleitung3656@schule.hessen.de</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>Schule(3659)@schule.hessen.de</t>
+          <t>Schule3659@schule.hessen.de</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Schulleitung(3659)@schule.hessen.de</t>
+          <t>Schulleitung3659@schule.hessen.de</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>Schule(3688)@schule.hessen.de</t>
+          <t>Schule3688@schule.hessen.de</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Schulleitung(3688)@schule.hessen.de</t>
+          <t>Schulleitung3688@schule.hessen.de</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>Schule(3690)@schule.hessen.de</t>
+          <t>Schule3690@schule.hessen.de</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Schulleitung(3690)@schule.hessen.de</t>
+          <t>Schulleitung3690@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -6377,12 +6377,12 @@
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>Schule(3696)@schule.hessen.de</t>
+          <t>Schule3696@schule.hessen.de</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Schulleitung(3696)@schule.hessen.de</t>
+          <t>Schulleitung3696@schule.hessen.de</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>Schule(3700)@schule.hessen.de</t>
+          <t>Schule3700@schule.hessen.de</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Schulleitung(3700)@schule.hessen.de</t>
+          <t>Schulleitung3700@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6505,12 @@
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>Schule(3702)@schule.hessen.de</t>
+          <t>Schule3702@schule.hessen.de</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Schulleitung(3702)@schule.hessen.de</t>
+          <t>Schulleitung3702@schule.hessen.de</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>Schule(3730)@schule.hessen.de</t>
+          <t>Schule3730@schule.hessen.de</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Schulleitung(3730)@schule.hessen.de</t>
+          <t>Schulleitung3730@schule.hessen.de</t>
         </is>
       </c>
       <c r="L86" t="n">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>Schule(3743)@schule.hessen.de</t>
+          <t>Schule3743@schule.hessen.de</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Schulleitung(3743)@schule.hessen.de</t>
+          <t>Schulleitung3743@schule.hessen.de</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>Schule(3744)@schule.hessen.de</t>
+          <t>Schule3744@schule.hessen.de</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Schulleitung(3744)@schule.hessen.de</t>
+          <t>Schulleitung3744@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>Schule(3745)@schule.hessen.de</t>
+          <t>Schule3745@schule.hessen.de</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Schulleitung(3745)@schule.hessen.de</t>
+          <t>Schulleitung3745@schule.hessen.de</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>Schule(3761)@schule.hessen.de</t>
+          <t>Schule3761@schule.hessen.de</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Schulleitung(3761)@schule.hessen.de</t>
+          <t>Schulleitung3761@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -6927,12 +6927,12 @@
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>Schule(3766)@schule.hessen.de</t>
+          <t>Schule3766@schule.hessen.de</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Schulleitung(3766)@schule.hessen.de</t>
+          <t>Schulleitung3766@schule.hessen.de</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>Schule(3778)@schule.hessen.de</t>
+          <t>Schule3778@schule.hessen.de</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Schulleitung(3778)@schule.hessen.de</t>
+          <t>Schulleitung3778@schule.hessen.de</t>
         </is>
       </c>
       <c r="L92" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>Schule(3809)@schule.hessen.de</t>
+          <t>Schule3809@schule.hessen.de</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Schulleitung(3809)@schule.hessen.de</t>
+          <t>Schulleitung3809@schule.hessen.de</t>
         </is>
       </c>
       <c r="L93" t="n">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>Schule(3810)@schule.hessen.de</t>
+          <t>Schule3810@schule.hessen.de</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Schulleitung(3810)@schule.hessen.de</t>
+          <t>Schulleitung3810@schule.hessen.de</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>Schule(3811)@schule.hessen.de</t>
+          <t>Schule3811@schule.hessen.de</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Schulleitung(3811)@schule.hessen.de</t>
+          <t>Schulleitung3811@schule.hessen.de</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>Schule(3820)@schule.hessen.de</t>
+          <t>Schule3820@schule.hessen.de</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Schulleitung(3820)@schule.hessen.de</t>
+          <t>Schulleitung3820@schule.hessen.de</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>Schule(3825)@schule.hessen.de</t>
+          <t>Schule3825@schule.hessen.de</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Schulleitung(3825)@schule.hessen.de</t>
+          <t>Schulleitung3825@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>Schule(3828)@schule.hessen.de</t>
+          <t>Schule3828@schule.hessen.de</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Schulleitung(3828)@schule.hessen.de</t>
+          <t>Schulleitung3828@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -7520,12 +7520,12 @@
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>Schule(3830)@schule.hessen.de</t>
+          <t>Schule3830@schule.hessen.de</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Schulleitung(3830)@schule.hessen.de</t>
+          <t>Schulleitung3830@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -7570,12 +7570,12 @@
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>Schule(3831)@schule.hessen.de</t>
+          <t>Schule3831@schule.hessen.de</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Schulleitung(3831)@schule.hessen.de</t>
+          <t>Schulleitung3831@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -7620,12 +7620,12 @@
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>Schule(3835)@schule.hessen.de</t>
+          <t>Schule3835@schule.hessen.de</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Schulleitung(3835)@schule.hessen.de</t>
+          <t>Schulleitung3835@schule.hessen.de</t>
         </is>
       </c>
       <c r="L101" t="n">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>Schule(3844)@schule.hessen.de</t>
+          <t>Schule3844@schule.hessen.de</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Schulleitung(3844)@schule.hessen.de</t>
+          <t>Schulleitung3844@schule.hessen.de</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -7781,12 +7781,12 @@
       </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>Schule(3850)@schule.hessen.de</t>
+          <t>Schule3850@schule.hessen.de</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Schulleitung(3850)@schule.hessen.de</t>
+          <t>Schulleitung3850@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -7826,12 +7826,12 @@
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>Schule(3851)@schule.hessen.de</t>
+          <t>Schule3851@schule.hessen.de</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Schulleitung(3851)@schule.hessen.de</t>
+          <t>Schulleitung3851@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -7876,12 +7876,12 @@
       </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>Schule(3861)@schule.hessen.de</t>
+          <t>Schule3861@schule.hessen.de</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Schulleitung(3861)@schule.hessen.de</t>
+          <t>Schulleitung3861@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -7926,12 +7926,12 @@
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>Schule(3877)@schule.hessen.de</t>
+          <t>Schule3877@schule.hessen.de</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Schulleitung(3877)@schule.hessen.de</t>
+          <t>Schulleitung3877@schule.hessen.de</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>Schule(3885)@schule.hessen.de</t>
+          <t>Schule3885@schule.hessen.de</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Schulleitung(3885)@schule.hessen.de</t>
+          <t>Schulleitung3885@schule.hessen.de</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>Schule(3886)@schule.hessen.de</t>
+          <t>Schule3886@schule.hessen.de</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Schulleitung(3886)@schule.hessen.de</t>
+          <t>Schulleitung3886@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>Schule(3888)@schule.hessen.de</t>
+          <t>Schule3888@schule.hessen.de</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Schulleitung(3888)@schule.hessen.de</t>
+          <t>Schulleitung3888@schule.hessen.de</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>Schule(3894)@schule.hessen.de</t>
+          <t>Schule3894@schule.hessen.de</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Schulleitung(3894)@schule.hessen.de</t>
+          <t>Schulleitung3894@schule.hessen.de</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>Schule(3894)@schule.hessen.de</t>
+          <t>Schule3894@schule.hessen.de</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Schulleitung(3894)@schule.hessen.de</t>
+          <t>Schulleitung3894@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -8348,12 +8348,12 @@
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>Schule(3913)@schule.hessen.de</t>
+          <t>Schule3913@schule.hessen.de</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Schulleitung(3913)@schule.hessen.de</t>
+          <t>Schulleitung3913@schule.hessen.de</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>Schule(3914)@schule.hessen.de</t>
+          <t>Schule3914@schule.hessen.de</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Schulleitung(3914)@schule.hessen.de</t>
+          <t>Schulleitung3914@schule.hessen.de</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>Schule(3918)@schule.hessen.de</t>
+          <t>Schule3918@schule.hessen.de</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Schulleitung(3918)@schule.hessen.de</t>
+          <t>Schulleitung3918@schule.hessen.de</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>Schule(3926)@schule.hessen.de</t>
+          <t>Schule3926@schule.hessen.de</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Schulleitung(3926)@schule.hessen.de</t>
+          <t>Schulleitung3926@schule.hessen.de</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>Schule(3937)@schule.hessen.de</t>
+          <t>Schule3937@schule.hessen.de</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Schulleitung(3937)@schule.hessen.de</t>
+          <t>Schulleitung3937@schule.hessen.de</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>Schule(3948)@schule.hessen.de</t>
+          <t>Schule3948@schule.hessen.de</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Schulleitung(3948)@schule.hessen.de</t>
+          <t>Schulleitung3948@schule.hessen.de</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>Schule(3949)@schule.hessen.de</t>
+          <t>Schule3949@schule.hessen.de</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Schulleitung(3949)@schule.hessen.de</t>
+          <t>Schulleitung3949@schule.hessen.de</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>Schule(3954)@schule.hessen.de</t>
+          <t>Schule3954@schule.hessen.de</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Schulleitung(3954)@schule.hessen.de</t>
+          <t>Schulleitung3954@schule.hessen.de</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>Schule(3955)@schule.hessen.de</t>
+          <t>Schule3955@schule.hessen.de</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Schulleitung(3955)@schule.hessen.de</t>
+          <t>Schulleitung3955@schule.hessen.de</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="J121" s="9" t="inlineStr">
         <is>
-          <t>Schule(3959)@schule.hessen.de</t>
+          <t>Schule3959@schule.hessen.de</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Schulleitung(3959)@schule.hessen.de</t>
+          <t>Schulleitung3959@schule.hessen.de</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>Schule(3982)@schule.hessen.de</t>
+          <t>Schule3982@schule.hessen.de</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Schulleitung(3982)@schule.hessen.de</t>
+          <t>Schulleitung3982@schule.hessen.de</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="J123" s="9" t="inlineStr">
         <is>
-          <t>Schule(4001)@schule.hessen.de</t>
+          <t>Schule4001@schule.hessen.de</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Schulleitung(4001)@schule.hessen.de</t>
+          <t>Schulleitung4001@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -9306,12 +9306,12 @@
       </c>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>Schule(4005)@schule.hessen.de</t>
+          <t>Schule4005@schule.hessen.de</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Schulleitung(4005)@schule.hessen.de</t>
+          <t>Schulleitung4005@schule.hessen.de</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="J125" s="9" t="inlineStr">
         <is>
-          <t>Schule(4006)@schule.hessen.de</t>
+          <t>Schule4006@schule.hessen.de</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Schulleitung(4006)@schule.hessen.de</t>
+          <t>Schulleitung4006@schule.hessen.de</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>Schule(4007)@schule.hessen.de</t>
+          <t>Schule4007@schule.hessen.de</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Schulleitung(4007)@schule.hessen.de</t>
+          <t>Schulleitung4007@schule.hessen.de</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="J127" s="9" t="inlineStr">
         <is>
-          <t>Schule(4008)@schule.hessen.de</t>
+          <t>Schule4008@schule.hessen.de</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Schulleitung(4008)@schule.hessen.de</t>
+          <t>Schulleitung4008@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -9595,12 +9595,12 @@
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>Schule(4012)@schule.hessen.de</t>
+          <t>Schule4012@schule.hessen.de</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Schulleitung(4012)@schule.hessen.de</t>
+          <t>Schulleitung4012@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -9640,12 +9640,12 @@
       </c>
       <c r="J129" s="9" t="inlineStr">
         <is>
-          <t>Schule(4018)@schule.hessen.de</t>
+          <t>Schule4018@schule.hessen.de</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Schulleitung(4018)@schule.hessen.de</t>
+          <t>Schulleitung4018@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -9690,12 +9690,12 @@
       </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>Schule(4020)@schule.hessen.de</t>
+          <t>Schule4020@schule.hessen.de</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Schulleitung(4020)@schule.hessen.de</t>
+          <t>Schulleitung4020@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="J131" s="9" t="inlineStr">
         <is>
-          <t>Schule(4022)@schule.hessen.de</t>
+          <t>Schule4022@schule.hessen.de</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Schulleitung(4022)@schule.hessen.de</t>
+          <t>Schulleitung4022@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -9785,12 +9785,12 @@
       </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>Schule(4042)@schule.hessen.de</t>
+          <t>Schule4042@schule.hessen.de</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Schulleitung(4042)@schule.hessen.de</t>
+          <t>Schulleitung4042@schule.hessen.de</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="J133" s="9" t="inlineStr">
         <is>
-          <t>Schule(4045)@schule.hessen.de</t>
+          <t>Schule4045@schule.hessen.de</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Schulleitung(4045)@schule.hessen.de</t>
+          <t>Schulleitung4045@schule.hessen.de</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="J134" s="9" t="inlineStr">
         <is>
-          <t>Schule(4047)@schule.hessen.de</t>
+          <t>Schule4047@schule.hessen.de</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Schulleitung(4047)@schule.hessen.de</t>
+          <t>Schulleitung4047@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -9996,12 +9996,12 @@
       </c>
       <c r="J135" s="9" t="inlineStr">
         <is>
-          <t>Schule(4050)@schule.hessen.de</t>
+          <t>Schule4050@schule.hessen.de</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Schulleitung(4050)@schule.hessen.de</t>
+          <t>Schulleitung4050@schule.hessen.de</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>Schule(4052)@schule.hessen.de</t>
+          <t>Schule4052@schule.hessen.de</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Schulleitung(4052)@schule.hessen.de</t>
+          <t>Schulleitung4052@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -10124,12 +10124,12 @@
       </c>
       <c r="J137" s="9" t="inlineStr">
         <is>
-          <t>Schule(4053)@schule.hessen.de</t>
+          <t>Schule4053@schule.hessen.de</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Schulleitung(4053)@schule.hessen.de</t>
+          <t>Schulleitung4053@schule.hessen.de</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>Schule(4054)@schule.hessen.de</t>
+          <t>Schule4054@schule.hessen.de</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Schulleitung(4054)@schule.hessen.de</t>
+          <t>Schulleitung4054@schule.hessen.de</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="J139" s="9" t="inlineStr">
         <is>
-          <t>Schule(4054)@schule.hessen.de</t>
+          <t>Schule4054@schule.hessen.de</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Schulleitung(4054)@schule.hessen.de</t>
+          <t>Schulleitung4054@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -10340,12 +10340,12 @@
       </c>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>Schule(4059)@schule.hessen.de</t>
+          <t>Schule4059@schule.hessen.de</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Schulleitung(4059)@schule.hessen.de</t>
+          <t>Schulleitung4059@schule.hessen.de</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -10418,12 +10418,12 @@
       </c>
       <c r="J141" s="9" t="inlineStr">
         <is>
-          <t>Schule(4061)@schule.hessen.de</t>
+          <t>Schule4061@schule.hessen.de</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Schulleitung(4061)@schule.hessen.de</t>
+          <t>Schulleitung4061@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -10468,12 +10468,12 @@
       </c>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>Schule(4074)@schule.hessen.de</t>
+          <t>Schule4074@schule.hessen.de</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Schulleitung(4074)@schule.hessen.de</t>
+          <t>Schulleitung4074@schule.hessen.de</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="J143" s="9" t="inlineStr">
         <is>
-          <t>Schule(4075)@schule.hessen.de</t>
+          <t>Schule4075@schule.hessen.de</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Schulleitung(4075)@schule.hessen.de</t>
+          <t>Schulleitung4075@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -10596,12 +10596,12 @@
       </c>
       <c r="J144" s="9" t="inlineStr">
         <is>
-          <t>Schule(4090)@schule.hessen.de</t>
+          <t>Schule4090@schule.hessen.de</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Schulleitung(4090)@schule.hessen.de</t>
+          <t>Schulleitung4090@schule.hessen.de</t>
         </is>
       </c>
       <c r="L144" t="n">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="J145" s="9" t="inlineStr">
         <is>
-          <t>Schule(4097)@schule.hessen.de</t>
+          <t>Schule4097@schule.hessen.de</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Schulleitung(4097)@schule.hessen.de</t>
+          <t>Schulleitung4097@schule.hessen.de</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>Schule(4101)@schule.hessen.de</t>
+          <t>Schule4101@schule.hessen.de</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Schulleitung(4101)@schule.hessen.de</t>
+          <t>Schulleitung4101@schule.hessen.de</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="J147" s="9" t="inlineStr">
         <is>
-          <t>Schule(4133)@schule.hessen.de</t>
+          <t>Schule4133@schule.hessen.de</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Schulleitung(4133)@schule.hessen.de</t>
+          <t>Schulleitung4133@schule.hessen.de</t>
         </is>
       </c>
       <c r="L147" t="n">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="J148" s="9" t="inlineStr">
         <is>
-          <t>Schule(4140)@schule.hessen.de</t>
+          <t>Schule4140@schule.hessen.de</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Schulleitung(4140)@schule.hessen.de</t>
+          <t>Schulleitung4140@schule.hessen.de</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="J149" s="9" t="inlineStr">
         <is>
-          <t>Schule(4141)@schule.hessen.de</t>
+          <t>Schule4141@schule.hessen.de</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Schulleitung(4141)@schule.hessen.de</t>
+          <t>Schulleitung4141@schule.hessen.de</t>
         </is>
       </c>
       <c r="L149" t="n">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="J150" s="9" t="inlineStr">
         <is>
-          <t>Schule(4146)@schule.hessen.de</t>
+          <t>Schule4146@schule.hessen.de</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Schulleitung(4146)@schule.hessen.de</t>
+          <t>Schulleitung4146@schule.hessen.de</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -11177,12 +11177,12 @@
       </c>
       <c r="J151" s="9" t="inlineStr">
         <is>
-          <t>Schule(4151)@schule.hessen.de</t>
+          <t>Schule4151@schule.hessen.de</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Schulleitung(4151)@schule.hessen.de</t>
+          <t>Schulleitung4151@schule.hessen.de</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="J152" s="9" t="inlineStr">
         <is>
-          <t>Schule(4154)@schule.hessen.de</t>
+          <t>Schule4154@schule.hessen.de</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Schulleitung(4154)@schule.hessen.de</t>
+          <t>Schulleitung4154@schule.hessen.de</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="J153" s="9" t="inlineStr">
         <is>
-          <t>Schule(4159)@schule.hessen.de</t>
+          <t>Schule4159@schule.hessen.de</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Schulleitung(4159)@schule.hessen.de</t>
+          <t>Schulleitung4159@schule.hessen.de</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -11426,12 +11426,12 @@
       </c>
       <c r="J154" s="9" t="inlineStr">
         <is>
-          <t>Schule(4176)@schule.hessen.de</t>
+          <t>Schule4176@schule.hessen.de</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Schulleitung(4176)@schule.hessen.de</t>
+          <t>Schulleitung4176@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -11476,12 +11476,12 @@
       </c>
       <c r="J155" s="9" t="inlineStr">
         <is>
-          <t>Schule(4183)@schule.hessen.de</t>
+          <t>Schule4183@schule.hessen.de</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Schulleitung(4183)@schule.hessen.de</t>
+          <t>Schulleitung4183@schule.hessen.de</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="J156" s="9" t="inlineStr">
         <is>
-          <t>Schule(4190)@schule.hessen.de</t>
+          <t>Schule4190@schule.hessen.de</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Schulleitung(4190)@schule.hessen.de</t>
+          <t>Schulleitung4190@schule.hessen.de</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="J157" s="9" t="inlineStr">
         <is>
-          <t>Schule(4199)@schule.hessen.de</t>
+          <t>Schule4199@schule.hessen.de</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Schulleitung(4199)@schule.hessen.de</t>
+          <t>Schulleitung4199@schule.hessen.de</t>
         </is>
       </c>
       <c r="L157" t="n">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="J158" s="9" t="inlineStr">
         <is>
-          <t>Schule(4203)@schule.hessen.de</t>
+          <t>Schule4203@schule.hessen.de</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Schulleitung(4203)@schule.hessen.de</t>
+          <t>Schulleitung4203@schule.hessen.de</t>
         </is>
       </c>
       <c r="L158" t="n">
@@ -11803,12 +11803,12 @@
       </c>
       <c r="J159" s="9" t="inlineStr">
         <is>
-          <t>Schule(4211)@schule.hessen.de</t>
+          <t>Schule4211@schule.hessen.de</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Schulleitung(4211)@schule.hessen.de</t>
+          <t>Schulleitung4211@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -11848,12 +11848,12 @@
       </c>
       <c r="J160" s="9" t="inlineStr">
         <is>
-          <t>Schule(4211)@schule.hessen.de</t>
+          <t>Schule4211@schule.hessen.de</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Schulleitung(4211)@schule.hessen.de</t>
+          <t>Schulleitung4211@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -11898,12 +11898,12 @@
       </c>
       <c r="J161" s="9" t="inlineStr">
         <is>
-          <t>Schule(4213)@schule.hessen.de</t>
+          <t>Schule4213@schule.hessen.de</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Schulleitung(4213)@schule.hessen.de</t>
+          <t>Schulleitung4213@schule.hessen.de</t>
         </is>
       </c>
       <c r="L161" t="n">
@@ -11981,12 +11981,12 @@
       </c>
       <c r="J162" s="9" t="inlineStr">
         <is>
-          <t>Schule(4220)@schule.hessen.de</t>
+          <t>Schule4220@schule.hessen.de</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Schulleitung(4220)@schule.hessen.de</t>
+          <t>Schulleitung4220@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -12031,12 +12031,12 @@
       </c>
       <c r="J163" s="9" t="inlineStr">
         <is>
-          <t>Schule(4221)@schule.hessen.de</t>
+          <t>Schule4221@schule.hessen.de</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Schulleitung(4221)@schule.hessen.de</t>
+          <t>Schulleitung4221@schule.hessen.de</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="J164" s="9" t="inlineStr">
         <is>
-          <t>Schule(4226)@schule.hessen.de</t>
+          <t>Schule4226@schule.hessen.de</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Schulleitung(4226)@schule.hessen.de</t>
+          <t>Schulleitung4226@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -12159,12 +12159,12 @@
       </c>
       <c r="J165" s="9" t="inlineStr">
         <is>
-          <t>Schule(4234)@schule.hessen.de</t>
+          <t>Schule4234@schule.hessen.de</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Schulleitung(4234)@schule.hessen.de</t>
+          <t>Schulleitung4234@schule.hessen.de</t>
         </is>
       </c>
       <c r="L165" t="n">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="J166" s="9" t="inlineStr">
         <is>
-          <t>Schule(4243)@schule.hessen.de</t>
+          <t>Schule4243@schule.hessen.de</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Schulleitung(4243)@schule.hessen.de</t>
+          <t>Schulleitung4243@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -12287,12 +12287,12 @@
       </c>
       <c r="J167" s="9" t="inlineStr">
         <is>
-          <t>Schule(4248)@schule.hessen.de</t>
+          <t>Schule4248@schule.hessen.de</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Schulleitung(4248)@schule.hessen.de</t>
+          <t>Schulleitung4248@schule.hessen.de</t>
         </is>
       </c>
       <c r="L167" t="n">
@@ -12370,12 +12370,12 @@
       </c>
       <c r="J168" s="9" t="inlineStr">
         <is>
-          <t>Schule(4250)@schule.hessen.de</t>
+          <t>Schule4250@schule.hessen.de</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Schulleitung(4250)@schule.hessen.de</t>
+          <t>Schulleitung4250@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -12420,12 +12420,12 @@
       </c>
       <c r="J169" s="9" t="inlineStr">
         <is>
-          <t>Schule(4266)@schule.hessen.de</t>
+          <t>Schule4266@schule.hessen.de</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Schulleitung(4266)@schule.hessen.de</t>
+          <t>Schulleitung4266@schule.hessen.de</t>
         </is>
       </c>
       <c r="L169" t="n">
@@ -12503,12 +12503,12 @@
       </c>
       <c r="J170" s="9" t="inlineStr">
         <is>
-          <t>Schule(4272)@schule.hessen.de</t>
+          <t>Schule4272@schule.hessen.de</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Schulleitung(4272)@schule.hessen.de</t>
+          <t>Schulleitung4272@schule.hessen.de</t>
         </is>
       </c>
       <c r="L170" t="n">
@@ -12586,12 +12586,12 @@
       </c>
       <c r="J171" s="9" t="inlineStr">
         <is>
-          <t>Schule(4277)@schule.hessen.de</t>
+          <t>Schule4277@schule.hessen.de</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Schulleitung(4277)@schule.hessen.de</t>
+          <t>Schulleitung4277@schule.hessen.de</t>
         </is>
       </c>
       <c r="L171" t="n">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="J172" s="9" t="inlineStr">
         <is>
-          <t>Schule(4293)@schule.hessen.de</t>
+          <t>Schule4293@schule.hessen.de</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Schulleitung(4293)@schule.hessen.de</t>
+          <t>Schulleitung4293@schule.hessen.de</t>
         </is>
       </c>
       <c r="L172" t="n">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="J173" s="9" t="inlineStr">
         <is>
-          <t>Schule(4295)@schule.hessen.de</t>
+          <t>Schule4295@schule.hessen.de</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Schulleitung(4295)@schule.hessen.de</t>
+          <t>Schulleitung4295@schule.hessen.de</t>
         </is>
       </c>
       <c r="L173" t="n">
@@ -12835,12 +12835,12 @@
       </c>
       <c r="J174" s="9" t="inlineStr">
         <is>
-          <t>Schule(4299)@schule.hessen.de</t>
+          <t>Schule4299@schule.hessen.de</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Schulleitung(4299)@schule.hessen.de</t>
+          <t>Schulleitung4299@schule.hessen.de</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -12918,12 +12918,12 @@
       </c>
       <c r="J175" s="9" t="inlineStr">
         <is>
-          <t>Schule(4304)@schule.hessen.de</t>
+          <t>Schule4304@schule.hessen.de</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Schulleitung(4304)@schule.hessen.de</t>
+          <t>Schulleitung4304@schule.hessen.de</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="J176" s="9" t="inlineStr">
         <is>
-          <t>Schule(4311)@schule.hessen.de</t>
+          <t>Schule4311@schule.hessen.de</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Schulleitung(4311)@schule.hessen.de</t>
+          <t>Schulleitung4311@schule.hessen.de</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="J177" s="9" t="inlineStr">
         <is>
-          <t>Schule(4312)@schule.hessen.de</t>
+          <t>Schule4312@schule.hessen.de</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Schulleitung(4312)@schule.hessen.de</t>
+          <t>Schulleitung4312@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -13129,12 +13129,12 @@
       </c>
       <c r="J178" s="9" t="inlineStr">
         <is>
-          <t>Schule(4314)@schule.hessen.de</t>
+          <t>Schule4314@schule.hessen.de</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Schulleitung(4314)@schule.hessen.de</t>
+          <t>Schulleitung4314@schule.hessen.de</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="J179" s="9" t="inlineStr">
         <is>
-          <t>Schule(4316)@schule.hessen.de</t>
+          <t>Schule4316@schule.hessen.de</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Schulleitung(4316)@schule.hessen.de</t>
+          <t>Schulleitung4316@schule.hessen.de</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -13295,12 +13295,12 @@
       </c>
       <c r="J180" s="9" t="inlineStr">
         <is>
-          <t>Schule(4319)@schule.hessen.de</t>
+          <t>Schule4319@schule.hessen.de</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Schulleitung(4319)@schule.hessen.de</t>
+          <t>Schulleitung4319@schule.hessen.de</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -13378,12 +13378,12 @@
       </c>
       <c r="J181" s="9" t="inlineStr">
         <is>
-          <t>Schule(4333)@schule.hessen.de</t>
+          <t>Schule4333@schule.hessen.de</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Schulleitung(4333)@schule.hessen.de</t>
+          <t>Schulleitung4333@schule.hessen.de</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="J182" s="9" t="inlineStr">
         <is>
-          <t>Schule(4343)@schule.hessen.de</t>
+          <t>Schule4343@schule.hessen.de</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Schulleitung(4343)@schule.hessen.de</t>
+          <t>Schulleitung4343@schule.hessen.de</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -13544,12 +13544,12 @@
       </c>
       <c r="J183" s="9" t="inlineStr">
         <is>
-          <t>Schule(4380)@schule.hessen.de</t>
+          <t>Schule4380@schule.hessen.de</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Schulleitung(4380)@schule.hessen.de</t>
+          <t>Schulleitung4380@schule.hessen.de</t>
         </is>
       </c>
       <c r="L183" t="n">
@@ -13622,12 +13622,12 @@
       </c>
       <c r="J184" s="9" t="inlineStr">
         <is>
-          <t>Schule(4384)@schule.hessen.de</t>
+          <t>Schule4384@schule.hessen.de</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Schulleitung(4384)@schule.hessen.de</t>
+          <t>Schulleitung4384@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -13667,12 +13667,12 @@
       </c>
       <c r="J185" s="9" t="inlineStr">
         <is>
-          <t>Schule(4384)@schule.hessen.de</t>
+          <t>Schule4384@schule.hessen.de</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Schulleitung(4384)@schule.hessen.de</t>
+          <t>Schulleitung4384@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -13717,12 +13717,12 @@
       </c>
       <c r="J186" s="9" t="inlineStr">
         <is>
-          <t>Schule(4392)@schule.hessen.de</t>
+          <t>Schule4392@schule.hessen.de</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Schulleitung(4392)@schule.hessen.de</t>
+          <t>Schulleitung4392@schule.hessen.de</t>
         </is>
       </c>
       <c r="L186" t="n">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="J187" s="9" t="inlineStr">
         <is>
-          <t>Schule(4434)@schule.hessen.de</t>
+          <t>Schule4434@schule.hessen.de</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Schulleitung(4434)@schule.hessen.de</t>
+          <t>Schulleitung4434@schule.hessen.de</t>
         </is>
       </c>
       <c r="L187" t="n">
@@ -13883,12 +13883,12 @@
       </c>
       <c r="J188" s="9" t="inlineStr">
         <is>
-          <t>Schule(4435)@schule.hessen.de</t>
+          <t>Schule4435@schule.hessen.de</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Schulleitung(4435)@schule.hessen.de</t>
+          <t>Schulleitung4435@schule.hessen.de</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="J189" s="9" t="inlineStr">
         <is>
-          <t>Schule(4436)@schule.hessen.de</t>
+          <t>Schule4436@schule.hessen.de</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Schulleitung(4436)@schule.hessen.de</t>
+          <t>Schulleitung4436@schule.hessen.de</t>
         </is>
       </c>
       <c r="L189" t="n">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="J190" s="9" t="inlineStr">
         <is>
-          <t>Schule(4437)@schule.hessen.de</t>
+          <t>Schule4437@schule.hessen.de</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Schulleitung(4437)@schule.hessen.de</t>
+          <t>Schulleitung4437@schule.hessen.de</t>
         </is>
       </c>
       <c r="L190" t="n">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="J191" s="9" t="inlineStr">
         <is>
-          <t>Schule(4483)@schule.hessen.de</t>
+          <t>Schule4483@schule.hessen.de</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Schulleitung(4483)@schule.hessen.de</t>
+          <t>Schulleitung4483@schule.hessen.de</t>
         </is>
       </c>
       <c r="L191" t="n">
@@ -14215,12 +14215,12 @@
       </c>
       <c r="J192" s="9" t="inlineStr">
         <is>
-          <t>Schule(4484)@schule.hessen.de</t>
+          <t>Schule4484@schule.hessen.de</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Schulleitung(4484)@schule.hessen.de</t>
+          <t>Schulleitung4484@schule.hessen.de</t>
         </is>
       </c>
       <c r="L192" t="n">
@@ -14298,12 +14298,12 @@
       </c>
       <c r="J193" s="9" t="inlineStr">
         <is>
-          <t>Schule(4535)@schule.hessen.de</t>
+          <t>Schule4535@schule.hessen.de</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Schulleitung(4535)@schule.hessen.de</t>
+          <t>Schulleitung4535@schule.hessen.de</t>
         </is>
       </c>
       <c r="L193" t="n">
@@ -14381,12 +14381,12 @@
       </c>
       <c r="J194" s="9" t="inlineStr">
         <is>
-          <t>Schule(4647)@schule.hessen.de</t>
+          <t>Schule4647@schule.hessen.de</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Schulleitung(4647)@schule.hessen.de</t>
+          <t>Schulleitung4647@schule.hessen.de</t>
         </is>
       </c>
       <c r="L194" t="n">
@@ -14464,12 +14464,12 @@
       </c>
       <c r="J195" s="9" t="inlineStr">
         <is>
-          <t>Schule(4795)@schule.hessen.de</t>
+          <t>Schule4795@schule.hessen.de</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Schulleitung(4795)@schule.hessen.de</t>
+          <t>Schulleitung4795@schule.hessen.de</t>
         </is>
       </c>
       <c r="L195" t="n">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="J196" s="9" t="inlineStr">
         <is>
-          <t>Schule(4797)@schule.hessen.de</t>
+          <t>Schule4797@schule.hessen.de</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Schulleitung(4797)@schule.hessen.de</t>
+          <t>Schulleitung4797@schule.hessen.de</t>
         </is>
       </c>
       <c r="L196" t="n">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="J197" s="9" t="inlineStr">
         <is>
-          <t>Schule(4800)@schule.hessen.de</t>
+          <t>Schule4800@schule.hessen.de</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Schulleitung(4800)@schule.hessen.de</t>
+          <t>Schulleitung4800@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -14670,12 +14670,12 @@
       </c>
       <c r="J198" s="9" t="inlineStr">
         <is>
-          <t>Schule(4801)@schule.hessen.de</t>
+          <t>Schule4801@schule.hessen.de</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Schulleitung(4801)@schule.hessen.de</t>
+          <t>Schulleitung4801@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -14720,12 +14720,12 @@
       </c>
       <c r="J199" s="9" t="inlineStr">
         <is>
-          <t>Schule(4862)@schule.hessen.de</t>
+          <t>Schule4862@schule.hessen.de</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Schulleitung(4862)@schule.hessen.de</t>
+          <t>Schulleitung4862@schule.hessen.de</t>
         </is>
       </c>
       <c r="L199" t="n">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="J200" s="9" t="inlineStr">
         <is>
-          <t>Schule(5024)@schule.hessen.de</t>
+          <t>Schule5024@schule.hessen.de</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Schulleitung(5024)@schule.hessen.de</t>
+          <t>Schulleitung5024@schule.hessen.de</t>
         </is>
       </c>
       <c r="L200" t="n">
@@ -14886,12 +14886,12 @@
       </c>
       <c r="J201" s="9" t="inlineStr">
         <is>
-          <t>Schule(5039)@schule.hessen.de</t>
+          <t>Schule5039@schule.hessen.de</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Schulleitung(5039)@schule.hessen.de</t>
+          <t>Schulleitung5039@schule.hessen.de</t>
         </is>
       </c>
       <c r="L201" t="n">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="J202" s="9" t="inlineStr">
         <is>
-          <t>Schule(5040)@schule.hessen.de</t>
+          <t>Schule5040@schule.hessen.de</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Schulleitung(5040)@schule.hessen.de</t>
+          <t>Schulleitung5040@schule.hessen.de</t>
         </is>
       </c>
       <c r="L202" t="n">
@@ -15052,12 +15052,12 @@
       </c>
       <c r="J203" s="9" t="inlineStr">
         <is>
-          <t>Schule(5393)@schule.hessen.de</t>
+          <t>Schule5393@schule.hessen.de</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Schulleitung(5393)@schule.hessen.de</t>
+          <t>Schulleitung5393@schule.hessen.de</t>
         </is>
       </c>
       <c r="L203" t="n">
@@ -15135,12 +15135,12 @@
       </c>
       <c r="J204" s="9" t="inlineStr">
         <is>
-          <t>Schule(5440)@schule.hessen.de</t>
+          <t>Schule5440@schule.hessen.de</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Schulleitung(5440)@schule.hessen.de</t>
+          <t>Schulleitung5440@schule.hessen.de</t>
         </is>
       </c>
       <c r="L204" t="n">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="J205" s="9" t="inlineStr">
         <is>
-          <t>Schule(7103)@schule.hessen.de</t>
+          <t>Schule7103@schule.hessen.de</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Schulleitung(7103)@schule.hessen.de</t>
+          <t>Schulleitung7103@schule.hessen.de</t>
         </is>
       </c>
       <c r="L205" t="n">
@@ -15296,12 +15296,12 @@
       </c>
       <c r="J206" s="9" t="inlineStr">
         <is>
-          <t>Schule(7104)@schule.hessen.de</t>
+          <t>Schule7104@schule.hessen.de</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Schulleitung(7104)@schule.hessen.de</t>
+          <t>Schulleitung7104@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -15346,12 +15346,12 @@
       </c>
       <c r="J207" s="9" t="inlineStr">
         <is>
-          <t>Schule(7105)@schule.hessen.de</t>
+          <t>Schule7105@schule.hessen.de</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Schulleitung(7105)@schule.hessen.de</t>
+          <t>Schulleitung7105@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -15396,12 +15396,12 @@
       </c>
       <c r="J208" s="9" t="inlineStr">
         <is>
-          <t>Schule(7106)@schule.hessen.de</t>
+          <t>Schule7106@schule.hessen.de</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Schulleitung(7106)@schule.hessen.de</t>
+          <t>Schulleitung7106@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -15441,12 +15441,12 @@
       </c>
       <c r="J209" s="9" t="inlineStr">
         <is>
-          <t>Schule(7113)@schule.hessen.de</t>
+          <t>Schule7113@schule.hessen.de</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Schulleitung(7113)@schule.hessen.de</t>
+          <t>Schulleitung7113@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -15491,12 +15491,12 @@
       </c>
       <c r="J210" s="9" t="inlineStr">
         <is>
-          <t>Schule(7121)@schule.hessen.de</t>
+          <t>Schule7121@schule.hessen.de</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Schulleitung(7121)@schule.hessen.de</t>
+          <t>Schulleitung7121@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -15536,12 +15536,12 @@
       </c>
       <c r="J211" s="9" t="inlineStr">
         <is>
-          <t>Schule(7124)@schule.hessen.de</t>
+          <t>Schule7124@schule.hessen.de</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Schulleitung(7124)@schule.hessen.de</t>
+          <t>Schulleitung7124@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -15581,12 +15581,12 @@
       </c>
       <c r="J212" s="9" t="inlineStr">
         <is>
-          <t>Schule(7125)@schule.hessen.de</t>
+          <t>Schule7125@schule.hessen.de</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Schulleitung(7125)@schule.hessen.de</t>
+          <t>Schulleitung7125@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -15626,12 +15626,12 @@
       </c>
       <c r="J213" s="9" t="inlineStr">
         <is>
-          <t>Schule(7127)@schule.hessen.de</t>
+          <t>Schule7127@schule.hessen.de</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Schulleitung(7127)@schule.hessen.de</t>
+          <t>Schulleitung7127@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -15676,12 +15676,12 @@
       </c>
       <c r="J214" s="9" t="inlineStr">
         <is>
-          <t>Schule(7129)@schule.hessen.de</t>
+          <t>Schule7129@schule.hessen.de</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Schulleitung(7129)@schule.hessen.de</t>
+          <t>Schulleitung7129@schule.hessen.de</t>
         </is>
       </c>
       <c r="L214" t="n">
@@ -15759,12 +15759,12 @@
       </c>
       <c r="J215" s="9" t="inlineStr">
         <is>
-          <t>Schule(7130)@schule.hessen.de</t>
+          <t>Schule7130@schule.hessen.de</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Schulleitung(7130)@schule.hessen.de</t>
+          <t>Schulleitung7130@schule.hessen.de</t>
         </is>
       </c>
       <c r="L215" t="n">
@@ -15842,12 +15842,12 @@
       </c>
       <c r="J216" s="9" t="inlineStr">
         <is>
-          <t>Schule(7134)@schule.hessen.de</t>
+          <t>Schule7134@schule.hessen.de</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Schulleitung(7134)@schule.hessen.de</t>
+          <t>Schulleitung7134@schule.hessen.de</t>
         </is>
       </c>
       <c r="L216" t="n">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="J217" s="9" t="inlineStr">
         <is>
-          <t>Schule(7137)@schule.hessen.de</t>
+          <t>Schule7137@schule.hessen.de</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Schulleitung(7137)@schule.hessen.de</t>
+          <t>Schulleitung7137@schule.hessen.de</t>
         </is>
       </c>
       <c r="L217" t="n">
@@ -16008,12 +16008,12 @@
       </c>
       <c r="J218" s="9" t="inlineStr">
         <is>
-          <t>Schule(7142)@schule.hessen.de</t>
+          <t>Schule7142@schule.hessen.de</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Schulleitung(7142)@schule.hessen.de</t>
+          <t>Schulleitung7142@schule.hessen.de</t>
         </is>
       </c>
       <c r="L218" t="n">
@@ -16091,12 +16091,12 @@
       </c>
       <c r="J219" s="9" t="inlineStr">
         <is>
-          <t>Schule(7143)@schule.hessen.de</t>
+          <t>Schule7143@schule.hessen.de</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Schulleitung(7143)@schule.hessen.de</t>
+          <t>Schulleitung7143@schule.hessen.de</t>
         </is>
       </c>
       <c r="L219" t="n">
@@ -16174,12 +16174,12 @@
       </c>
       <c r="J220" s="9" t="inlineStr">
         <is>
-          <t>Schule(7144)@schule.hessen.de</t>
+          <t>Schule7144@schule.hessen.de</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Schulleitung(7144)@schule.hessen.de</t>
+          <t>Schulleitung7144@schule.hessen.de</t>
         </is>
       </c>
       <c r="L220" t="n">
@@ -16257,12 +16257,12 @@
       </c>
       <c r="J221" s="9" t="inlineStr">
         <is>
-          <t>Schule(7150)@schule.hessen.de</t>
+          <t>Schule7150@schule.hessen.de</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Schulleitung(7150)@schule.hessen.de</t>
+          <t>Schulleitung7150@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -16307,12 +16307,12 @@
       </c>
       <c r="J222" s="9" t="inlineStr">
         <is>
-          <t>Schule(7151)@schule.hessen.de</t>
+          <t>Schule7151@schule.hessen.de</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Schulleitung(7151)@schule.hessen.de</t>
+          <t>Schulleitung7151@schule.hessen.de</t>
         </is>
       </c>
       <c r="L222" t="n">
@@ -16390,12 +16390,12 @@
       </c>
       <c r="J223" s="9" t="inlineStr">
         <is>
-          <t>Schule(7161)@schule.hessen.de</t>
+          <t>Schule7161@schule.hessen.de</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Schulleitung(7161)@schule.hessen.de</t>
+          <t>Schulleitung7161@schule.hessen.de</t>
         </is>
       </c>
       <c r="L223" t="n">
@@ -16468,12 +16468,12 @@
       </c>
       <c r="J224" s="9" t="inlineStr">
         <is>
-          <t>Schule(7162)@schule.hessen.de</t>
+          <t>Schule7162@schule.hessen.de</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Schulleitung(7162)@schule.hessen.de</t>
+          <t>Schulleitung7162@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -16518,12 +16518,12 @@
       </c>
       <c r="J225" s="9" t="inlineStr">
         <is>
-          <t>Schule(7190)@schule.hessen.de</t>
+          <t>Schule7190@schule.hessen.de</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Schulleitung(7190)@schule.hessen.de</t>
+          <t>Schulleitung7190@schule.hessen.de</t>
         </is>
       </c>
       <c r="L225" t="n">
@@ -16601,12 +16601,12 @@
       </c>
       <c r="J226" s="9" t="inlineStr">
         <is>
-          <t>Schule(7199)@schule.hessen.de</t>
+          <t>Schule7199@schule.hessen.de</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Schulleitung(7199)@schule.hessen.de</t>
+          <t>Schulleitung7199@schule.hessen.de</t>
         </is>
       </c>
       <c r="L226" t="n">
@@ -16684,12 +16684,12 @@
       </c>
       <c r="J227" s="9" t="inlineStr">
         <is>
-          <t>Schule(7204)@schule.hessen.de</t>
+          <t>Schule7204@schule.hessen.de</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Schulleitung(7204)@schule.hessen.de</t>
+          <t>Schulleitung7204@schule.hessen.de</t>
         </is>
       </c>
       <c r="L227" t="n">
@@ -16762,12 +16762,12 @@
       </c>
       <c r="J228" s="9" t="inlineStr">
         <is>
-          <t>Schule(7215)@schule.hessen.de</t>
+          <t>Schule7215@schule.hessen.de</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Schulleitung(7215)@schule.hessen.de</t>
+          <t>Schulleitung7215@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -16812,12 +16812,12 @@
       </c>
       <c r="J229" s="9" t="inlineStr">
         <is>
-          <t>Schule(7220)@schule.hessen.de</t>
+          <t>Schule7220@schule.hessen.de</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Schulleitung(7220)@schule.hessen.de</t>
+          <t>Schulleitung7220@schule.hessen.de</t>
         </is>
       </c>
       <c r="L229" t="n">
@@ -16890,12 +16890,12 @@
       </c>
       <c r="J230" s="9" t="inlineStr">
         <is>
-          <t>Schule(7233)@schule.hessen.de</t>
+          <t>Schule7233@schule.hessen.de</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Schulleitung(7233)@schule.hessen.de</t>
+          <t>Schulleitung7233@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -16940,12 +16940,12 @@
       </c>
       <c r="J231" s="9" t="inlineStr">
         <is>
-          <t>Schule(7240)@schule.hessen.de</t>
+          <t>Schule7240@schule.hessen.de</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Schulleitung(7240)@schule.hessen.de</t>
+          <t>Schulleitung7240@schule.hessen.de</t>
         </is>
       </c>
       <c r="L231" t="n">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="J232" s="9" t="inlineStr">
         <is>
-          <t>Schule(7244)@schule.hessen.de</t>
+          <t>Schule7244@schule.hessen.de</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Schulleitung(7244)@schule.hessen.de</t>
+          <t>Schulleitung7244@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -17068,12 +17068,12 @@
       </c>
       <c r="J233" s="9" t="inlineStr">
         <is>
-          <t>Schule(7249)@schule.hessen.de</t>
+          <t>Schule7249@schule.hessen.de</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Schulleitung(7249)@schule.hessen.de</t>
+          <t>Schulleitung7249@schule.hessen.de</t>
         </is>
       </c>
       <c r="L233" t="n">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="J234" s="9" t="inlineStr">
         <is>
-          <t>Schule(7260)@schule.hessen.de</t>
+          <t>Schule7260@schule.hessen.de</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Schulleitung(7260)@schule.hessen.de</t>
+          <t>Schulleitung7260@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -17201,12 +17201,12 @@
       </c>
       <c r="J235" s="9" t="inlineStr">
         <is>
-          <t>Schule(7267)@schule.hessen.de</t>
+          <t>Schule7267@schule.hessen.de</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Schulleitung(7267)@schule.hessen.de</t>
+          <t>Schulleitung7267@schule.hessen.de</t>
         </is>
       </c>
       <c r="L235" t="n">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="J236" s="9" t="inlineStr">
         <is>
-          <t>Schule(7271)@schule.hessen.de</t>
+          <t>Schule7271@schule.hessen.de</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Schulleitung(7271)@schule.hessen.de</t>
+          <t>Schulleitung7271@schule.hessen.de</t>
         </is>
       </c>
       <c r="L236" t="n">
@@ -17367,12 +17367,12 @@
       </c>
       <c r="J237" s="9" t="inlineStr">
         <is>
-          <t>Schule(7292)@schule.hessen.de</t>
+          <t>Schule7292@schule.hessen.de</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Schulleitung(7292)@schule.hessen.de</t>
+          <t>Schulleitung7292@schule.hessen.de</t>
         </is>
       </c>
       <c r="L237" t="n">
@@ -17450,12 +17450,12 @@
       </c>
       <c r="J238" s="9" t="inlineStr">
         <is>
-          <t>Schule(7305)@schule.hessen.de</t>
+          <t>Schule7305@schule.hessen.de</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Schulleitung(7305)@schule.hessen.de</t>
+          <t>Schulleitung7305@schule.hessen.de</t>
         </is>
       </c>
       <c r="L238" t="n">
@@ -17533,12 +17533,12 @@
       </c>
       <c r="J239" s="9" t="inlineStr">
         <is>
-          <t>Schule(7306)@schule.hessen.de</t>
+          <t>Schule7306@schule.hessen.de</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Schulleitung(7306)@schule.hessen.de</t>
+          <t>Schulleitung7306@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -17583,12 +17583,12 @@
       </c>
       <c r="J240" s="9" t="inlineStr">
         <is>
-          <t>Schule(7316)@schule.hessen.de</t>
+          <t>Schule7316@schule.hessen.de</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Schulleitung(7316)@schule.hessen.de</t>
+          <t>Schulleitung7316@schule.hessen.de</t>
         </is>
       </c>
       <c r="L240" t="n">
@@ -17666,12 +17666,12 @@
       </c>
       <c r="J241" s="9" t="inlineStr">
         <is>
-          <t>Schule(7322)@schule.hessen.de</t>
+          <t>Schule7322@schule.hessen.de</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Schulleitung(7322)@schule.hessen.de</t>
+          <t>Schulleitung7322@schule.hessen.de</t>
         </is>
       </c>
       <c r="L241" t="n">
@@ -17749,12 +17749,12 @@
       </c>
       <c r="J242" s="9" t="inlineStr">
         <is>
-          <t>Schule(7344)@schule.hessen.de</t>
+          <t>Schule7344@schule.hessen.de</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Schulleitung(7344)@schule.hessen.de</t>
+          <t>Schulleitung7344@schule.hessen.de</t>
         </is>
       </c>
       <c r="L242" t="n">
@@ -17832,12 +17832,12 @@
       </c>
       <c r="J243" s="9" t="inlineStr">
         <is>
-          <t>Schule(7357)@schule.hessen.de</t>
+          <t>Schule7357@schule.hessen.de</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Schulleitung(7357)@schule.hessen.de</t>
+          <t>Schulleitung7357@schule.hessen.de</t>
         </is>
       </c>
       <c r="L243" t="n">
@@ -17915,12 +17915,12 @@
       </c>
       <c r="J244" s="9" t="inlineStr">
         <is>
-          <t>Schule(7376)@schule.hessen.de</t>
+          <t>Schule7376@schule.hessen.de</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Schulleitung(7376)@schule.hessen.de</t>
+          <t>Schulleitung7376@schule.hessen.de</t>
         </is>
       </c>
       <c r="L244" t="n">
@@ -17998,12 +17998,12 @@
       </c>
       <c r="J245" s="9" t="inlineStr">
         <is>
-          <t>Schule(7392)@schule.hessen.de</t>
+          <t>Schule7392@schule.hessen.de</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Schulleitung(7392)@schule.hessen.de</t>
+          <t>Schulleitung7392@schule.hessen.de</t>
         </is>
       </c>
       <c r="L245" t="n">
@@ -18076,12 +18076,12 @@
       </c>
       <c r="J246" s="9" t="inlineStr">
         <is>
-          <t>Schule(7395)@schule.hessen.de</t>
+          <t>Schule7395@schule.hessen.de</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Schulleitung(7395)@schule.hessen.de</t>
+          <t>Schulleitung7395@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="J247" s="9" t="inlineStr">
         <is>
-          <t>Schule(7400)@schule.hessen.de</t>
+          <t>Schule7400@schule.hessen.de</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Schulleitung(7400)@schule.hessen.de</t>
+          <t>Schulleitung7400@schule.hessen.de</t>
         </is>
       </c>
       <c r="L247" t="n">
@@ -18209,12 +18209,12 @@
       </c>
       <c r="J248" s="9" t="inlineStr">
         <is>
-          <t>Schule(7401)@schule.hessen.de</t>
+          <t>Schule7401@schule.hessen.de</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Schulleitung(7401)@schule.hessen.de</t>
+          <t>Schulleitung7401@schule.hessen.de</t>
         </is>
       </c>
       <c r="L248" t="n">
@@ -18292,12 +18292,12 @@
       </c>
       <c r="J249" s="9" t="inlineStr">
         <is>
-          <t>Schule(7405)@schule.hessen.de</t>
+          <t>Schule7405@schule.hessen.de</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Schulleitung(7405)@schule.hessen.de</t>
+          <t>Schulleitung7405@schule.hessen.de</t>
         </is>
       </c>
       <c r="L249" t="n">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="J250" s="9" t="inlineStr">
         <is>
-          <t>Schule(7409)@schule.hessen.de</t>
+          <t>Schule7409@schule.hessen.de</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Schulleitung(7409)@schule.hessen.de</t>
+          <t>Schulleitung7409@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -18420,12 +18420,12 @@
       </c>
       <c r="J251" s="9" t="inlineStr">
         <is>
-          <t>Schule(7439)@schule.hessen.de</t>
+          <t>Schule7439@schule.hessen.de</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Schulleitung(7439)@schule.hessen.de</t>
+          <t>Schulleitung7439@schule.hessen.de</t>
         </is>
       </c>
       <c r="L251" t="n">
@@ -18503,12 +18503,12 @@
       </c>
       <c r="J252" s="9" t="inlineStr">
         <is>
-          <t>Schule(7440)@schule.hessen.de</t>
+          <t>Schule7440@schule.hessen.de</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Schulleitung(7440)@schule.hessen.de</t>
+          <t>Schulleitung7440@schule.hessen.de</t>
         </is>
       </c>
       <c r="L252" t="n">
@@ -18586,12 +18586,12 @@
       </c>
       <c r="J253" s="9" t="inlineStr">
         <is>
-          <t>Schule(7446)@schule.hessen.de</t>
+          <t>Schule7446@schule.hessen.de</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Schulleitung(7446)@schule.hessen.de</t>
+          <t>Schulleitung7446@schule.hessen.de</t>
         </is>
       </c>
       <c r="L253" t="n">
@@ -18669,12 +18669,12 @@
       </c>
       <c r="J254" s="9" t="inlineStr">
         <is>
-          <t>Schule(7455)@schule.hessen.de</t>
+          <t>Schule7455@schule.hessen.de</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Schulleitung(7455)@schule.hessen.de</t>
+          <t>Schulleitung7455@schule.hessen.de</t>
         </is>
       </c>
       <c r="L254" t="n">
@@ -18752,12 +18752,12 @@
       </c>
       <c r="J255" s="9" t="inlineStr">
         <is>
-          <t>Schule(7469)@schule.hessen.de</t>
+          <t>Schule7469@schule.hessen.de</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Schulleitung(7469)@schule.hessen.de</t>
+          <t>Schulleitung7469@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -18802,12 +18802,12 @@
       </c>
       <c r="J256" s="9" t="inlineStr">
         <is>
-          <t>Schule(7473)@schule.hessen.de</t>
+          <t>Schule7473@schule.hessen.de</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Schulleitung(7473)@schule.hessen.de</t>
+          <t>Schulleitung7473@schule.hessen.de</t>
         </is>
       </c>
       <c r="L256" t="n">
@@ -18885,12 +18885,12 @@
       </c>
       <c r="J257" s="9" t="inlineStr">
         <is>
-          <t>Schule(7479)@schule.hessen.de</t>
+          <t>Schule7479@schule.hessen.de</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Schulleitung(7479)@schule.hessen.de</t>
+          <t>Schulleitung7479@schule.hessen.de</t>
         </is>
       </c>
       <c r="L257" t="n">
@@ -18968,12 +18968,12 @@
       </c>
       <c r="J258" s="9" t="inlineStr">
         <is>
-          <t>Schule(7503)@schule.hessen.de</t>
+          <t>Schule7503@schule.hessen.de</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Schulleitung(7503)@schule.hessen.de</t>
+          <t>Schulleitung7503@schule.hessen.de</t>
         </is>
       </c>
       <c r="L258" t="n">
@@ -19046,12 +19046,12 @@
       </c>
       <c r="J259" s="9" t="inlineStr">
         <is>
-          <t>Schule(7517)@schule.hessen.de</t>
+          <t>Schule7517@schule.hessen.de</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Schulleitung(7517)@schule.hessen.de</t>
+          <t>Schulleitung7517@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -19091,12 +19091,12 @@
       </c>
       <c r="J260" s="9" t="inlineStr">
         <is>
-          <t>Schule(7519)@schule.hessen.de</t>
+          <t>Schule7519@schule.hessen.de</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Schulleitung(7519)@schule.hessen.de</t>
+          <t>Schulleitung7519@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -19141,12 +19141,12 @@
       </c>
       <c r="J261" s="9" t="inlineStr">
         <is>
-          <t>Schule(7526)@schule.hessen.de</t>
+          <t>Schule7526@schule.hessen.de</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Schulleitung(7526)@schule.hessen.de</t>
+          <t>Schulleitung7526@schule.hessen.de</t>
         </is>
       </c>
       <c r="L261" t="n">
@@ -19224,12 +19224,12 @@
       </c>
       <c r="J262" s="9" t="inlineStr">
         <is>
-          <t>Schule(7537)@schule.hessen.de</t>
+          <t>Schule7537@schule.hessen.de</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Schulleitung(7537)@schule.hessen.de</t>
+          <t>Schulleitung7537@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -19269,12 +19269,12 @@
       </c>
       <c r="J263" s="9" t="inlineStr">
         <is>
-          <t>Schule(7542)@schule.hessen.de</t>
+          <t>Schule7542@schule.hessen.de</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Schulleitung(7542)@schule.hessen.de</t>
+          <t>Schulleitung7542@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -19319,12 +19319,12 @@
       </c>
       <c r="J264" s="9" t="inlineStr">
         <is>
-          <t>Schule(7567)@schule.hessen.de</t>
+          <t>Schule7567@schule.hessen.de</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Schulleitung(7567)@schule.hessen.de</t>
+          <t>Schulleitung7567@schule.hessen.de</t>
         </is>
       </c>
       <c r="L264" t="n">
@@ -19402,12 +19402,12 @@
       </c>
       <c r="J265" s="9" t="inlineStr">
         <is>
-          <t>Schule(7577)@schule.hessen.de</t>
+          <t>Schule7577@schule.hessen.de</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Schulleitung(7577)@schule.hessen.de</t>
+          <t>Schulleitung7577@schule.hessen.de</t>
         </is>
       </c>
       <c r="L265" t="n">
@@ -19485,12 +19485,12 @@
       </c>
       <c r="J266" s="9" t="inlineStr">
         <is>
-          <t>Schule(7581)@schule.hessen.de</t>
+          <t>Schule7581@schule.hessen.de</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Schulleitung(7581)@schule.hessen.de</t>
+          <t>Schulleitung7581@schule.hessen.de</t>
         </is>
       </c>
       <c r="L266" t="n">
@@ -19568,12 +19568,12 @@
       </c>
       <c r="J267" s="9" t="inlineStr">
         <is>
-          <t>Schule(7584)@schule.hessen.de</t>
+          <t>Schule7584@schule.hessen.de</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Schulleitung(7584)@schule.hessen.de</t>
+          <t>Schulleitung7584@schule.hessen.de</t>
         </is>
       </c>
       <c r="L267" t="n">
@@ -19651,12 +19651,12 @@
       </c>
       <c r="J268" s="9" t="inlineStr">
         <is>
-          <t>Schule(7586)@schule.hessen.de</t>
+          <t>Schule7586@schule.hessen.de</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Schulleitung(7586)@schule.hessen.de</t>
+          <t>Schulleitung7586@schule.hessen.de</t>
         </is>
       </c>
       <c r="L268" t="n">
@@ -19734,12 +19734,12 @@
       </c>
       <c r="J269" s="9" t="inlineStr">
         <is>
-          <t>Schule(7591)@schule.hessen.de</t>
+          <t>Schule7591@schule.hessen.de</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Schulleitung(7591)@schule.hessen.de</t>
+          <t>Schulleitung7591@schule.hessen.de</t>
         </is>
       </c>
       <c r="L269" t="n">
@@ -19817,12 +19817,12 @@
       </c>
       <c r="J270" s="9" t="inlineStr">
         <is>
-          <t>Schule(7616)@schule.hessen.de</t>
+          <t>Schule7616@schule.hessen.de</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Schulleitung(7616)@schule.hessen.de</t>
+          <t>Schulleitung7616@schule.hessen.de</t>
         </is>
       </c>
       <c r="L270" t="n">
@@ -19900,12 +19900,12 @@
       </c>
       <c r="J271" s="9" t="inlineStr">
         <is>
-          <t>Schule(7629)@schule.hessen.de</t>
+          <t>Schule7629@schule.hessen.de</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Schulleitung(7629)@schule.hessen.de</t>
+          <t>Schulleitung7629@schule.hessen.de</t>
         </is>
       </c>
       <c r="L271" t="n">
@@ -19983,12 +19983,12 @@
       </c>
       <c r="J272" s="9" t="inlineStr">
         <is>
-          <t>Schule(7649)@schule.hessen.de</t>
+          <t>Schule7649@schule.hessen.de</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Schulleitung(7649)@schule.hessen.de</t>
+          <t>Schulleitung7649@schule.hessen.de</t>
         </is>
       </c>
       <c r="L272" t="n">
@@ -20066,12 +20066,12 @@
       </c>
       <c r="J273" s="9" t="inlineStr">
         <is>
-          <t>Schule(7651)@schule.hessen.de</t>
+          <t>Schule7651@schule.hessen.de</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Schulleitung(7651)@schule.hessen.de</t>
+          <t>Schulleitung7651@schule.hessen.de</t>
         </is>
       </c>
       <c r="L273" t="n">
@@ -20144,12 +20144,12 @@
       </c>
       <c r="J274" s="9" t="inlineStr">
         <is>
-          <t>Schule(7652)@schule.hessen.de</t>
+          <t>Schule7652@schule.hessen.de</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Schulleitung(7652)@schule.hessen.de</t>
+          <t>Schulleitung7652@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -20194,12 +20194,12 @@
       </c>
       <c r="J275" s="9" t="inlineStr">
         <is>
-          <t>Schule(7655)@schule.hessen.de</t>
+          <t>Schule7655@schule.hessen.de</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Schulleitung(7655)@schule.hessen.de</t>
+          <t>Schulleitung7655@schule.hessen.de</t>
         </is>
       </c>
       <c r="L275" t="n">
@@ -20277,12 +20277,12 @@
       </c>
       <c r="J276" s="9" t="inlineStr">
         <is>
-          <t>Schule(7656)@schule.hessen.de</t>
+          <t>Schule7656@schule.hessen.de</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Schulleitung(7656)@schule.hessen.de</t>
+          <t>Schulleitung7656@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -20327,12 +20327,12 @@
       </c>
       <c r="J277" s="9" t="inlineStr">
         <is>
-          <t>Schule(7657)@schule.hessen.de</t>
+          <t>Schule7657@schule.hessen.de</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Schulleitung(7657)@schule.hessen.de</t>
+          <t>Schulleitung7657@schule.hessen.de</t>
         </is>
       </c>
       <c r="L277" t="n">
@@ -20405,12 +20405,12 @@
       </c>
       <c r="J278" s="9" t="inlineStr">
         <is>
-          <t>Schule(7663)@schule.hessen.de</t>
+          <t>Schule7663@schule.hessen.de</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Schulleitung(7663)@schule.hessen.de</t>
+          <t>Schulleitung7663@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -20455,12 +20455,12 @@
       </c>
       <c r="J279" s="9" t="inlineStr">
         <is>
-          <t>Schule(7665)@schule.hessen.de</t>
+          <t>Schule7665@schule.hessen.de</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>Schulleitung(7665)@schule.hessen.de</t>
+          <t>Schulleitung7665@schule.hessen.de</t>
         </is>
       </c>
       <c r="L279" t="n">
@@ -20538,12 +20538,12 @@
       </c>
       <c r="J280" s="9" t="inlineStr">
         <is>
-          <t>Schule(7672)@schule.hessen.de</t>
+          <t>Schule7672@schule.hessen.de</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Schulleitung(7672)@schule.hessen.de</t>
+          <t>Schulleitung7672@schule.hessen.de</t>
         </is>
       </c>
       <c r="L280" t="n">
@@ -20621,12 +20621,12 @@
       </c>
       <c r="J281" s="9" t="inlineStr">
         <is>
-          <t>Schule(7674)@schule.hessen.de</t>
+          <t>Schule7674@schule.hessen.de</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Schulleitung(7674)@schule.hessen.de</t>
+          <t>Schulleitung7674@schule.hessen.de</t>
         </is>
       </c>
       <c r="L281" t="n">
@@ -20704,12 +20704,12 @@
       </c>
       <c r="J282" s="9" t="inlineStr">
         <is>
-          <t>Schule(7677)@schule.hessen.de</t>
+          <t>Schule7677@schule.hessen.de</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Schulleitung(7677)@schule.hessen.de</t>
+          <t>Schulleitung7677@schule.hessen.de</t>
         </is>
       </c>
       <c r="L282" t="n">
@@ -20787,12 +20787,12 @@
       </c>
       <c r="J283" s="9" t="inlineStr">
         <is>
-          <t>Schule(7678)@schule.hessen.de</t>
+          <t>Schule7678@schule.hessen.de</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Schulleitung(7678)@schule.hessen.de</t>
+          <t>Schulleitung7678@schule.hessen.de</t>
         </is>
       </c>
       <c r="L283" t="n">
@@ -20870,12 +20870,12 @@
       </c>
       <c r="J284" s="9" t="inlineStr">
         <is>
-          <t>Schule(7683)@schule.hessen.de</t>
+          <t>Schule7683@schule.hessen.de</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Schulleitung(7683)@schule.hessen.de</t>
+          <t>Schulleitung7683@schule.hessen.de</t>
         </is>
       </c>
       <c r="L284" t="n">
@@ -20933,12 +20933,12 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Schule(3333)@schule.hessen.de</t>
+          <t>Schule3333@schule.hessen.de</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Schulleitung(3333)@schule.hessen.de</t>
+          <t>Schulleitung3333@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -20963,12 +20963,12 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Schule(3386)@schule.hessen.de</t>
+          <t>Schule3386@schule.hessen.de</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Schulleitung(3386)@schule.hessen.de</t>
+          <t>Schulleitung3386@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -20993,12 +20993,12 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Schule(4230)@schule.hessen.de</t>
+          <t>Schule4230@schule.hessen.de</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Schulleitung(4230)@schule.hessen.de</t>
+          <t>Schulleitung4230@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21023,12 +21023,12 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Schule(3602)@schule.hessen.de</t>
+          <t>Schule3602@schule.hessen.de</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Schulleitung(3602)@schule.hessen.de</t>
+          <t>Schulleitung3602@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21053,12 +21053,12 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Schule(3334)@schule.hessen.de</t>
+          <t>Schule3334@schule.hessen.de</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Schulleitung(3334)@schule.hessen.de</t>
+          <t>Schulleitung3334@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21083,12 +21083,12 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Schule(3384)@schule.hessen.de</t>
+          <t>Schule3384@schule.hessen.de</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Schulleitung(3384)@schule.hessen.de</t>
+          <t>Schulleitung3384@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21113,12 +21113,12 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Schule(3510)@schule.hessen.de</t>
+          <t>Schule3510@schule.hessen.de</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Schulleitung(3510)@schule.hessen.de</t>
+          <t>Schulleitung3510@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21143,12 +21143,12 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Schule(3325)@schule.hessen.de</t>
+          <t>Schule3325@schule.hessen.de</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Schulleitung(3325)@schule.hessen.de</t>
+          <t>Schulleitung3325@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21173,12 +21173,12 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Schule(3344)@schule.hessen.de</t>
+          <t>Schule3344@schule.hessen.de</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Schulleitung(3344)@schule.hessen.de</t>
+          <t>Schulleitung3344@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21203,12 +21203,12 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Schule(3379)@schule.hessen.de</t>
+          <t>Schule3379@schule.hessen.de</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Schulleitung(3379)@schule.hessen.de</t>
+          <t>Schulleitung3379@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21233,12 +21233,12 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Schule(3605)@schule.hessen.de</t>
+          <t>Schule3605@schule.hessen.de</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Schulleitung(3605)@schule.hessen.de</t>
+          <t>Schulleitung3605@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21263,12 +21263,12 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Schule(3385)@schule.hessen.de</t>
+          <t>Schule3385@schule.hessen.de</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Schulleitung(3385)@schule.hessen.de</t>
+          <t>Schulleitung3385@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21293,12 +21293,12 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Schule(4237)@schule.hessen.de</t>
+          <t>Schule4237@schule.hessen.de</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Schulleitung(4237)@schule.hessen.de</t>
+          <t>Schulleitung4237@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21323,12 +21323,12 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Schule(3370)@schule.hessen.de</t>
+          <t>Schule3370@schule.hessen.de</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Schulleitung(3370)@schule.hessen.de</t>
+          <t>Schulleitung3370@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21353,12 +21353,12 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Schule(3348)@schule.hessen.de</t>
+          <t>Schule3348@schule.hessen.de</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Schulleitung(3348)@schule.hessen.de</t>
+          <t>Schulleitung3348@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21383,12 +21383,12 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Schule(3614)@schule.hessen.de</t>
+          <t>Schule3614@schule.hessen.de</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Schulleitung(3614)@schule.hessen.de</t>
+          <t>Schulleitung3614@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21413,12 +21413,12 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Schule(3599)@schule.hessen.de</t>
+          <t>Schule3599@schule.hessen.de</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Schulleitung(3599)@schule.hessen.de</t>
+          <t>Schulleitung3599@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21443,12 +21443,12 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Schule(3323)@schule.hessen.de</t>
+          <t>Schule3323@schule.hessen.de</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Schulleitung(3323)@schule.hessen.de</t>
+          <t>Schulleitung3323@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21473,12 +21473,12 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Schule(3390)@schule.hessen.de</t>
+          <t>Schule3390@schule.hessen.de</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Schulleitung(3390)@schule.hessen.de</t>
+          <t>Schulleitung3390@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21503,12 +21503,12 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Schule(3608)@schule.hessen.de</t>
+          <t>Schule3608@schule.hessen.de</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Schulleitung(3608)@schule.hessen.de</t>
+          <t>Schulleitung3608@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21533,12 +21533,12 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Schule(3539)@schule.hessen.de</t>
+          <t>Schule3539@schule.hessen.de</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Schulleitung(3539)@schule.hessen.de</t>
+          <t>Schulleitung3539@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21563,12 +21563,12 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Schule(3509)@schule.hessen.de</t>
+          <t>Schule3509@schule.hessen.de</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Schulleitung(3509)@schule.hessen.de</t>
+          <t>Schulleitung3509@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21593,12 +21593,12 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Schule(3482)@schule.hessen.de</t>
+          <t>Schule3482@schule.hessen.de</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Schulleitung(3482)@schule.hessen.de</t>
+          <t>Schulleitung3482@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21623,12 +21623,12 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Schule(3525)@schule.hessen.de</t>
+          <t>Schule3525@schule.hessen.de</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Schulleitung(3525)@schule.hessen.de</t>
+          <t>Schulleitung3525@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21653,12 +21653,12 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Schule(3502)@schule.hessen.de</t>
+          <t>Schule3502@schule.hessen.de</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Schulleitung(3502)@schule.hessen.de</t>
+          <t>Schulleitung3502@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21683,12 +21683,12 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Schule(3201)@schule.hessen.de</t>
+          <t>Schule3201@schule.hessen.de</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Schulleitung(3201)@schule.hessen.de</t>
+          <t>Schulleitung3201@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21713,12 +21713,12 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Schule(3489)@schule.hessen.de</t>
+          <t>Schule3489@schule.hessen.de</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Schulleitung(3489)@schule.hessen.de</t>
+          <t>Schulleitung3489@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21743,12 +21743,12 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Schule(4338)@schule.hessen.de</t>
+          <t>Schule4338@schule.hessen.de</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Schulleitung(4338)@schule.hessen.de</t>
+          <t>Schulleitung4338@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21773,12 +21773,12 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>Schule(3224)@schule.hessen.de</t>
+          <t>Schule3224@schule.hessen.de</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Schulleitung(3224)@schule.hessen.de</t>
+          <t>Schulleitung3224@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21803,12 +21803,12 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Schule(4253)@schule.hessen.de</t>
+          <t>Schule4253@schule.hessen.de</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Schulleitung(4253)@schule.hessen.de</t>
+          <t>Schulleitung4253@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21833,12 +21833,12 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>Schule(3511)@schule.hessen.de</t>
+          <t>Schule3511@schule.hessen.de</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Schulleitung(3511)@schule.hessen.de</t>
+          <t>Schulleitung3511@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21863,12 +21863,12 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>Schule(4188)@schule.hessen.de</t>
+          <t>Schule4188@schule.hessen.de</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Schulleitung(4188)@schule.hessen.de</t>
+          <t>Schulleitung4188@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21893,12 +21893,12 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Schule(3481)@schule.hessen.de</t>
+          <t>Schule3481@schule.hessen.de</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Schulleitung(3481)@schule.hessen.de</t>
+          <t>Schulleitung3481@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21923,12 +21923,12 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>Schule(3480)@schule.hessen.de</t>
+          <t>Schule3480@schule.hessen.de</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Schulleitung(3480)@schule.hessen.de</t>
+          <t>Schulleitung3480@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21953,12 +21953,12 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Schule(4284)@schule.hessen.de</t>
+          <t>Schule4284@schule.hessen.de</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Schulleitung(4284)@schule.hessen.de</t>
+          <t>Schulleitung4284@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -21983,12 +21983,12 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Schule(4336)@schule.hessen.de</t>
+          <t>Schule4336@schule.hessen.de</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Schulleitung(4336)@schule.hessen.de</t>
+          <t>Schulleitung4336@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22013,12 +22013,12 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Schule(3523)@schule.hessen.de</t>
+          <t>Schule3523@schule.hessen.de</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Schulleitung(3523)@schule.hessen.de</t>
+          <t>Schulleitung3523@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22043,12 +22043,12 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Schule(3528)@schule.hessen.de</t>
+          <t>Schule3528@schule.hessen.de</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Schulleitung(3528)@schule.hessen.de</t>
+          <t>Schulleitung3528@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22073,12 +22073,12 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Schule(4191)@schule.hessen.de</t>
+          <t>Schule4191@schule.hessen.de</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Schulleitung(4191)@schule.hessen.de</t>
+          <t>Schulleitung4191@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22103,12 +22103,12 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Schule(4231)@schule.hessen.de</t>
+          <t>Schule4231@schule.hessen.de</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Schulleitung(4231)@schule.hessen.de</t>
+          <t>Schulleitung4231@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22133,12 +22133,12 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>Schule(3172)@schule.hessen.de</t>
+          <t>Schule3172@schule.hessen.de</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Schulleitung(3172)@schule.hessen.de</t>
+          <t>Schulleitung3172@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22163,12 +22163,12 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>Schule(4262)@schule.hessen.de</t>
+          <t>Schule4262@schule.hessen.de</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Schulleitung(4262)@schule.hessen.de</t>
+          <t>Schulleitung4262@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22193,12 +22193,12 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>Schule(3666)@schule.hessen.de</t>
+          <t>Schule3666@schule.hessen.de</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Schulleitung(3666)@schule.hessen.de</t>
+          <t>Schulleitung3666@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22223,12 +22223,12 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>Schule(3166)@schule.hessen.de</t>
+          <t>Schule3166@schule.hessen.de</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Schulleitung(3166)@schule.hessen.de</t>
+          <t>Schulleitung3166@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22253,12 +22253,12 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>Schule(3131)@schule.hessen.de</t>
+          <t>Schule3131@schule.hessen.de</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Schulleitung(3131)@schule.hessen.de</t>
+          <t>Schulleitung3131@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22283,12 +22283,12 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>Schule(3167)@schule.hessen.de</t>
+          <t>Schule3167@schule.hessen.de</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Schulleitung(3167)@schule.hessen.de</t>
+          <t>Schulleitung3167@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22313,12 +22313,12 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Schule(3104)@schule.hessen.de</t>
+          <t>Schule3104@schule.hessen.de</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Schulleitung(3104)@schule.hessen.de</t>
+          <t>Schulleitung3104@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22343,12 +22343,12 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Schule(3168)@schule.hessen.de</t>
+          <t>Schule3168@schule.hessen.de</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Schulleitung(3168)@schule.hessen.de</t>
+          <t>Schulleitung3168@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22373,12 +22373,12 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Schule(3154)@schule.hessen.de</t>
+          <t>Schule3154@schule.hessen.de</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Schulleitung(3154)@schule.hessen.de</t>
+          <t>Schulleitung3154@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22403,12 +22403,12 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Schule(3118)@schule.hessen.de</t>
+          <t>Schule3118@schule.hessen.de</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Schulleitung(3118)@schule.hessen.de</t>
+          <t>Schulleitung3118@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Schule(4381)@schule.hessen.de</t>
+          <t>Schule4381@schule.hessen.de</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Schulleitung(4381)@schule.hessen.de</t>
+          <t>Schulleitung4381@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22463,12 +22463,12 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Schule(3153)@schule.hessen.de</t>
+          <t>Schule3153@schule.hessen.de</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Schulleitung(3153)@schule.hessen.de</t>
+          <t>Schulleitung3153@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22493,12 +22493,12 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>Schule(4396)@schule.hessen.de</t>
+          <t>Schule4396@schule.hessen.de</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Schulleitung(4396)@schule.hessen.de</t>
+          <t>Schulleitung4396@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22523,12 +22523,12 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Schule(3107)@schule.hessen.de</t>
+          <t>Schule3107@schule.hessen.de</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Schulleitung(3107)@schule.hessen.de</t>
+          <t>Schulleitung3107@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22553,12 +22553,12 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>Schule(4301)@schule.hessen.de</t>
+          <t>Schule4301@schule.hessen.de</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Schulleitung(4301)@schule.hessen.de</t>
+          <t>Schulleitung4301@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22583,12 +22583,12 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Schule(3165)@schule.hessen.de</t>
+          <t>Schule3165@schule.hessen.de</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Schulleitung(3165)@schule.hessen.de</t>
+          <t>Schulleitung3165@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22613,12 +22613,12 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Schule(3122)@schule.hessen.de</t>
+          <t>Schule3122@schule.hessen.de</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Schulleitung(3122)@schule.hessen.de</t>
+          <t>Schulleitung3122@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22643,12 +22643,12 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>Schule(3111)@schule.hessen.de</t>
+          <t>Schule3111@schule.hessen.de</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Schulleitung(3111)@schule.hessen.de</t>
+          <t>Schulleitung3111@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22673,12 +22673,12 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Schule(3155)@schule.hessen.de</t>
+          <t>Schule3155@schule.hessen.de</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Schulleitung(3155)@schule.hessen.de</t>
+          <t>Schulleitung3155@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22703,12 +22703,12 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>Schule(3116)@schule.hessen.de</t>
+          <t>Schule3116@schule.hessen.de</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Schulleitung(3116)@schule.hessen.de</t>
+          <t>Schulleitung3116@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22733,12 +22733,12 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>Schule(7356)@schule.hessen.de</t>
+          <t>Schule7356@schule.hessen.de</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Schulleitung(7356)@schule.hessen.de</t>
+          <t>Schulleitung7356@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22763,12 +22763,12 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>Schule(7258)@schule.hessen.de</t>
+          <t>Schule7258@schule.hessen.de</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Schulleitung(7258)@schule.hessen.de</t>
+          <t>Schulleitung7258@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22793,12 +22793,12 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>Schule(7254)@schule.hessen.de</t>
+          <t>Schule7254@schule.hessen.de</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Schulleitung(7254)@schule.hessen.de</t>
+          <t>Schulleitung7254@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22823,12 +22823,12 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Schule(7263)@schule.hessen.de</t>
+          <t>Schule7263@schule.hessen.de</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Schulleitung(7263)@schule.hessen.de</t>
+          <t>Schulleitung7263@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22853,12 +22853,12 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Schule(7238)@schule.hessen.de</t>
+          <t>Schule7238@schule.hessen.de</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Schulleitung(7238)@schule.hessen.de</t>
+          <t>Schulleitung7238@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22883,12 +22883,12 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Schule(7237)@schule.hessen.de</t>
+          <t>Schule7237@schule.hessen.de</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Schulleitung(7237)@schule.hessen.de</t>
+          <t>Schulleitung7237@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22913,12 +22913,12 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>Schule(7367)@schule.hessen.de</t>
+          <t>Schule7367@schule.hessen.de</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Schulleitung(7367)@schule.hessen.de</t>
+          <t>Schulleitung7367@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22943,12 +22943,12 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>Schule(7283)@schule.hessen.de</t>
+          <t>Schule7283@schule.hessen.de</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Schulleitung(7283)@schule.hessen.de</t>
+          <t>Schulleitung7283@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -22973,12 +22973,12 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Schule(7285)@schule.hessen.de</t>
+          <t>Schule7285@schule.hessen.de</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Schulleitung(7285)@schule.hessen.de</t>
+          <t>Schulleitung7285@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23003,12 +23003,12 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Schule(7234)@schule.hessen.de</t>
+          <t>Schule7234@schule.hessen.de</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Schulleitung(7234)@schule.hessen.de</t>
+          <t>Schulleitung7234@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23033,12 +23033,12 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>Schule(7245)@schule.hessen.de</t>
+          <t>Schule7245@schule.hessen.de</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Schulleitung(7245)@schule.hessen.de</t>
+          <t>Schulleitung7245@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23063,12 +23063,12 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Schule(7290)@schule.hessen.de</t>
+          <t>Schule7290@schule.hessen.de</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Schulleitung(7290)@schule.hessen.de</t>
+          <t>Schulleitung7290@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23093,12 +23093,12 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>Schule(7100)@schule.hessen.de</t>
+          <t>Schule7100@schule.hessen.de</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Schulleitung(7100)@schule.hessen.de</t>
+          <t>Schulleitung7100@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23123,12 +23123,12 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>Schule(7236)@schule.hessen.de</t>
+          <t>Schule7236@schule.hessen.de</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Schulleitung(7236)@schule.hessen.de</t>
+          <t>Schulleitung7236@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23153,12 +23153,12 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>Schule(7288)@schule.hessen.de</t>
+          <t>Schule7288@schule.hessen.de</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Schulleitung(7288)@schule.hessen.de</t>
+          <t>Schulleitung7288@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23183,12 +23183,12 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>Schule(7294)@schule.hessen.de</t>
+          <t>Schule7294@schule.hessen.de</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>Schulleitung(7294)@schule.hessen.de</t>
+          <t>Schulleitung7294@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23213,12 +23213,12 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Schule(7373)@schule.hessen.de</t>
+          <t>Schule7373@schule.hessen.de</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Schulleitung(7373)@schule.hessen.de</t>
+          <t>Schulleitung7373@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23243,12 +23243,12 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Schule(7661)@schule.hessen.de</t>
+          <t>Schule7661@schule.hessen.de</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Schulleitung(7661)@schule.hessen.de</t>
+          <t>Schulleitung7661@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23273,12 +23273,12 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>Schule(7281)@schule.hessen.de</t>
+          <t>Schule7281@schule.hessen.de</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Schulleitung(7281)@schule.hessen.de</t>
+          <t>Schulleitung7281@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23303,12 +23303,12 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Schule(7248)@schule.hessen.de</t>
+          <t>Schule7248@schule.hessen.de</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Schulleitung(7248)@schule.hessen.de</t>
+          <t>Schulleitung7248@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23333,12 +23333,12 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Schule(3782)@schule.hessen.de</t>
+          <t>Schule3782@schule.hessen.de</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Schulleitung(3782)@schule.hessen.de</t>
+          <t>Schulleitung3782@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23363,12 +23363,12 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Schule(3932)@schule.hessen.de</t>
+          <t>Schule3932@schule.hessen.de</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Schulleitung(3932)@schule.hessen.de</t>
+          <t>Schulleitung3932@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23393,12 +23393,12 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Schule(3934)@schule.hessen.de</t>
+          <t>Schule3934@schule.hessen.de</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Schulleitung(3934)@schule.hessen.de</t>
+          <t>Schulleitung3934@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Schule(3796)@schule.hessen.de</t>
+          <t>Schule3796@schule.hessen.de</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Schulleitung(3796)@schule.hessen.de</t>
+          <t>Schulleitung3796@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23453,12 +23453,12 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>Schule(3813)@schule.hessen.de</t>
+          <t>Schule3813@schule.hessen.de</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Schulleitung(3813)@schule.hessen.de</t>
+          <t>Schulleitung3813@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23483,12 +23483,12 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>Schule(3933)@schule.hessen.de</t>
+          <t>Schule3933@schule.hessen.de</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Schulleitung(3933)@schule.hessen.de</t>
+          <t>Schulleitung3933@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23513,12 +23513,12 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Schule(3936)@schule.hessen.de</t>
+          <t>Schule3936@schule.hessen.de</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Schulleitung(3936)@schule.hessen.de</t>
+          <t>Schulleitung3936@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23543,12 +23543,12 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>Schule(4196)@schule.hessen.de</t>
+          <t>Schule4196@schule.hessen.de</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Schulleitung(4196)@schule.hessen.de</t>
+          <t>Schulleitung4196@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23573,12 +23573,12 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>Schule(3780)@schule.hessen.de</t>
+          <t>Schule3780@schule.hessen.de</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Schulleitung(3780)@schule.hessen.de</t>
+          <t>Schulleitung3780@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23603,12 +23603,12 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>Schule(3956)@schule.hessen.de</t>
+          <t>Schule3956@schule.hessen.de</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Schulleitung(3956)@schule.hessen.de</t>
+          <t>Schulleitung3956@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23633,12 +23633,12 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Schule(3787)@schule.hessen.de</t>
+          <t>Schule3787@schule.hessen.de</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Schulleitung(3787)@schule.hessen.de</t>
+          <t>Schulleitung3787@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23663,12 +23663,12 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>Schule(3794)@schule.hessen.de</t>
+          <t>Schule3794@schule.hessen.de</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Schulleitung(3794)@schule.hessen.de</t>
+          <t>Schulleitung3794@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23693,12 +23693,12 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Schule(3921)@schule.hessen.de</t>
+          <t>Schule3921@schule.hessen.de</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Schulleitung(3921)@schule.hessen.de</t>
+          <t>Schulleitung3921@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23723,12 +23723,12 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Schule(3789)@schule.hessen.de</t>
+          <t>Schule3789@schule.hessen.de</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>Schulleitung(3789)@schule.hessen.de</t>
+          <t>Schulleitung3789@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23753,12 +23753,12 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>Schule(3812)@schule.hessen.de</t>
+          <t>Schule3812@schule.hessen.de</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Schulleitung(3812)@schule.hessen.de</t>
+          <t>Schulleitung3812@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23783,12 +23783,12 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>Schule(4308)@schule.hessen.de</t>
+          <t>Schule4308@schule.hessen.de</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>Schulleitung(4308)@schule.hessen.de</t>
+          <t>Schulleitung4308@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23813,12 +23813,12 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>Schule(3930)@schule.hessen.de</t>
+          <t>Schule3930@schule.hessen.de</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Schulleitung(3930)@schule.hessen.de</t>
+          <t>Schulleitung3930@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23843,12 +23843,12 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>Schule(3795)@schule.hessen.de</t>
+          <t>Schule3795@schule.hessen.de</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Schulleitung(3795)@schule.hessen.de</t>
+          <t>Schulleitung3795@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23873,12 +23873,12 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Schule(3792)@schule.hessen.de</t>
+          <t>Schule3792@schule.hessen.de</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Schulleitung(3792)@schule.hessen.de</t>
+          <t>Schulleitung3792@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23903,12 +23903,12 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Schule(3776)@schule.hessen.de</t>
+          <t>Schule3776@schule.hessen.de</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Schulleitung(3776)@schule.hessen.de</t>
+          <t>Schulleitung3776@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23933,12 +23933,12 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>Schule(3869)@schule.hessen.de</t>
+          <t>Schule3869@schule.hessen.de</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Schulleitung(3869)@schule.hessen.de</t>
+          <t>Schulleitung3869@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23963,12 +23963,12 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Schule(3862)@schule.hessen.de</t>
+          <t>Schule3862@schule.hessen.de</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Schulleitung(3862)@schule.hessen.de</t>
+          <t>Schulleitung3862@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -23993,12 +23993,12 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>Schule(3767)@schule.hessen.de</t>
+          <t>Schule3767@schule.hessen.de</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Schulleitung(3767)@schule.hessen.de</t>
+          <t>Schulleitung3767@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24023,12 +24023,12 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>Schule(3772)@schule.hessen.de</t>
+          <t>Schule3772@schule.hessen.de</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Schulleitung(3772)@schule.hessen.de</t>
+          <t>Schulleitung3772@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24053,12 +24053,12 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>Schule(4285)@schule.hessen.de</t>
+          <t>Schule4285@schule.hessen.de</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Schulleitung(4285)@schule.hessen.de</t>
+          <t>Schulleitung4285@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24083,12 +24083,12 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>Schule(4157)@schule.hessen.de</t>
+          <t>Schule4157@schule.hessen.de</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Schulleitung(4157)@schule.hessen.de</t>
+          <t>Schulleitung4157@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24113,12 +24113,12 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>Schule(3304)@schule.hessen.de</t>
+          <t>Schule3304@schule.hessen.de</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Schulleitung(3304)@schule.hessen.de</t>
+          <t>Schulleitung3304@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24143,12 +24143,12 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>Schule(3301)@schule.hessen.de</t>
+          <t>Schule3301@schule.hessen.de</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>Schulleitung(3301)@schule.hessen.de</t>
+          <t>Schulleitung3301@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24173,12 +24173,12 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Schule(3764)@schule.hessen.de</t>
+          <t>Schule3764@schule.hessen.de</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Schulleitung(3764)@schule.hessen.de</t>
+          <t>Schulleitung3764@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24203,12 +24203,12 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>Schule(3724)@schule.hessen.de</t>
+          <t>Schule3724@schule.hessen.de</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Schulleitung(3724)@schule.hessen.de</t>
+          <t>Schulleitung3724@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24233,12 +24233,12 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>Schule(4178)@schule.hessen.de</t>
+          <t>Schule4178@schule.hessen.de</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>Schulleitung(4178)@schule.hessen.de</t>
+          <t>Schulleitung4178@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24263,12 +24263,12 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>Schule(3228)@schule.hessen.de</t>
+          <t>Schule3228@schule.hessen.de</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>Schulleitung(3228)@schule.hessen.de</t>
+          <t>Schulleitung3228@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24293,12 +24293,12 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>Schule(4222)@schule.hessen.de</t>
+          <t>Schule4222@schule.hessen.de</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>Schulleitung(4222)@schule.hessen.de</t>
+          <t>Schulleitung4222@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24323,12 +24323,12 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>Schule(3311)@schule.hessen.de</t>
+          <t>Schule3311@schule.hessen.de</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>Schulleitung(3311)@schule.hessen.de</t>
+          <t>Schulleitung3311@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24353,12 +24353,12 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Schule(3733)@schule.hessen.de</t>
+          <t>Schule3733@schule.hessen.de</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>Schulleitung(3733)@schule.hessen.de</t>
+          <t>Schulleitung3733@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24383,12 +24383,12 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>Schule(4181)@schule.hessen.de</t>
+          <t>Schule4181@schule.hessen.de</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>Schulleitung(4181)@schule.hessen.de</t>
+          <t>Schulleitung4181@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24413,12 +24413,12 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>Schule(3229)@schule.hessen.de</t>
+          <t>Schule3229@schule.hessen.de</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>Schulleitung(3229)@schule.hessen.de</t>
+          <t>Schulleitung3229@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24443,12 +24443,12 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>Schule(3735)@schule.hessen.de</t>
+          <t>Schule3735@schule.hessen.de</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Schulleitung(3735)@schule.hessen.de</t>
+          <t>Schulleitung3735@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24473,12 +24473,12 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>Schule(3740)@schule.hessen.de</t>
+          <t>Schule3740@schule.hessen.de</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Schulleitung(3740)@schule.hessen.de</t>
+          <t>Schulleitung3740@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24503,12 +24503,12 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>Schule(3758)@schule.hessen.de</t>
+          <t>Schule3758@schule.hessen.de</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>Schulleitung(3758)@schule.hessen.de</t>
+          <t>Schulleitung3758@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24533,12 +24533,12 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>Schule(7522)@schule.hessen.de</t>
+          <t>Schule7522@schule.hessen.de</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Schulleitung(7522)@schule.hessen.de</t>
+          <t>Schulleitung7522@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24563,12 +24563,12 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>Schule(7512)@schule.hessen.de</t>
+          <t>Schule7512@schule.hessen.de</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Schulleitung(7512)@schule.hessen.de</t>
+          <t>Schulleitung7512@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24593,12 +24593,12 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>Schule(7508)@schule.hessen.de</t>
+          <t>Schule7508@schule.hessen.de</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Schulleitung(7508)@schule.hessen.de</t>
+          <t>Schulleitung7508@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24623,12 +24623,12 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>Schule(7607)@schule.hessen.de</t>
+          <t>Schule7607@schule.hessen.de</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>Schulleitung(7607)@schule.hessen.de</t>
+          <t>Schulleitung7607@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24653,12 +24653,12 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>Schule(7308)@schule.hessen.de</t>
+          <t>Schule7308@schule.hessen.de</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Schulleitung(7308)@schule.hessen.de</t>
+          <t>Schulleitung7308@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24683,12 +24683,12 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>Schule(7330)@schule.hessen.de</t>
+          <t>Schule7330@schule.hessen.de</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>Schulleitung(7330)@schule.hessen.de</t>
+          <t>Schulleitung7330@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24713,12 +24713,12 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>Schule(7146)@schule.hessen.de</t>
+          <t>Schule7146@schule.hessen.de</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Schulleitung(7146)@schule.hessen.de</t>
+          <t>Schulleitung7146@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24743,12 +24743,12 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>Schule(7579)@schule.hessen.de</t>
+          <t>Schule7579@schule.hessen.de</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>Schulleitung(7579)@schule.hessen.de</t>
+          <t>Schulleitung7579@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24773,12 +24773,12 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>Schule(7510)@schule.hessen.de</t>
+          <t>Schule7510@schule.hessen.de</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>Schulleitung(7510)@schule.hessen.de</t>
+          <t>Schulleitung7510@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24803,12 +24803,12 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Schule(7331)@schule.hessen.de</t>
+          <t>Schule7331@schule.hessen.de</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>Schulleitung(7331)@schule.hessen.de</t>
+          <t>Schulleitung7331@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24833,12 +24833,12 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>Schule(7524)@schule.hessen.de</t>
+          <t>Schule7524@schule.hessen.de</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>Schulleitung(7524)@schule.hessen.de</t>
+          <t>Schulleitung7524@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24863,12 +24863,12 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>Schule(7583)@schule.hessen.de</t>
+          <t>Schule7583@schule.hessen.de</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>Schulleitung(7583)@schule.hessen.de</t>
+          <t>Schulleitung7583@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24893,12 +24893,12 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>Schule(7158)@schule.hessen.de</t>
+          <t>Schule7158@schule.hessen.de</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>Schulleitung(7158)@schule.hessen.de</t>
+          <t>Schulleitung7158@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24923,12 +24923,12 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>Schule(7334)@schule.hessen.de</t>
+          <t>Schule7334@schule.hessen.de</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Schulleitung(7334)@schule.hessen.de</t>
+          <t>Schulleitung7334@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24953,12 +24953,12 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Schule(7300)@schule.hessen.de</t>
+          <t>Schule7300@schule.hessen.de</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>Schulleitung(7300)@schule.hessen.de</t>
+          <t>Schulleitung7300@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -24983,12 +24983,12 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>Schule(7485)@schule.hessen.de</t>
+          <t>Schule7485@schule.hessen.de</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>Schulleitung(7485)@schule.hessen.de</t>
+          <t>Schulleitung7485@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25013,12 +25013,12 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>Schule(7582)@schule.hessen.de</t>
+          <t>Schule7582@schule.hessen.de</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>Schulleitung(7582)@schule.hessen.de</t>
+          <t>Schulleitung7582@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25043,12 +25043,12 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>Schule(7299)@schule.hessen.de</t>
+          <t>Schule7299@schule.hessen.de</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>Schulleitung(7299)@schule.hessen.de</t>
+          <t>Schulleitung7299@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25073,12 +25073,12 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>Schule(7658)@schule.hessen.de</t>
+          <t>Schule7658@schule.hessen.de</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>Schulleitung(7658)@schule.hessen.de</t>
+          <t>Schulleitung7658@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25103,12 +25103,12 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>Schule(7148)@schule.hessen.de</t>
+          <t>Schule7148@schule.hessen.de</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>Schulleitung(7148)@schule.hessen.de</t>
+          <t>Schulleitung7148@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25133,12 +25133,12 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>Schule(3454)@schule.hessen.de</t>
+          <t>Schule3454@schule.hessen.de</t>
         </is>
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>Schulleitung(3454)@schule.hessen.de</t>
+          <t>Schulleitung3454@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25163,12 +25163,12 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Schule(4871)@schule.hessen.de</t>
+          <t>Schule4871@schule.hessen.de</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>Schulleitung(4871)@schule.hessen.de</t>
+          <t>Schulleitung4871@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25193,12 +25193,12 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Schule(3650)@schule.hessen.de</t>
+          <t>Schule3650@schule.hessen.de</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Schulleitung(3650)@schule.hessen.de</t>
+          <t>Schulleitung3650@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25223,12 +25223,12 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>Schule(4873)@schule.hessen.de</t>
+          <t>Schule4873@schule.hessen.de</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Schulleitung(4873)@schule.hessen.de</t>
+          <t>Schulleitung4873@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25253,12 +25253,12 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Schule(3440)@schule.hessen.de</t>
+          <t>Schule3440@schule.hessen.de</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>Schulleitung(3440)@schule.hessen.de</t>
+          <t>Schulleitung3440@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25283,12 +25283,12 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>Schule(3660)@schule.hessen.de</t>
+          <t>Schule3660@schule.hessen.de</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>Schulleitung(3660)@schule.hessen.de</t>
+          <t>Schulleitung3660@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25313,12 +25313,12 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>Schule(3439)@schule.hessen.de</t>
+          <t>Schule3439@schule.hessen.de</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>Schulleitung(3439)@schule.hessen.de</t>
+          <t>Schulleitung3439@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25343,12 +25343,12 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>Schule(3628)@schule.hessen.de</t>
+          <t>Schule3628@schule.hessen.de</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>Schulleitung(3628)@schule.hessen.de</t>
+          <t>Schulleitung3628@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25373,12 +25373,12 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>Schule(4014)@schule.hessen.de</t>
+          <t>Schule4014@schule.hessen.de</t>
         </is>
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>Schulleitung(4014)@schule.hessen.de</t>
+          <t>Schulleitung4014@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25403,12 +25403,12 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>Schule(4009)@schule.hessen.de</t>
+          <t>Schule4009@schule.hessen.de</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>Schulleitung(4009)@schule.hessen.de</t>
+          <t>Schulleitung4009@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25433,12 +25433,12 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>Schule(3672)@schule.hessen.de</t>
+          <t>Schule3672@schule.hessen.de</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>Schulleitung(3672)@schule.hessen.de</t>
+          <t>Schulleitung3672@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25463,12 +25463,12 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Schule(4000)@schule.hessen.de</t>
+          <t>Schule4000@schule.hessen.de</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>Schulleitung(4000)@schule.hessen.de</t>
+          <t>Schulleitung4000@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25493,12 +25493,12 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Schule(4282)@schule.hessen.de</t>
+          <t>Schule4282@schule.hessen.de</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>Schulleitung(4282)@schule.hessen.de</t>
+          <t>Schulleitung4282@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25523,12 +25523,12 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>Schule(3630)@schule.hessen.de</t>
+          <t>Schule3630@schule.hessen.de</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>Schulleitung(3630)@schule.hessen.de</t>
+          <t>Schulleitung3630@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25553,12 +25553,12 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>Schule(3671)@schule.hessen.de</t>
+          <t>Schule3671@schule.hessen.de</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>Schulleitung(3671)@schule.hessen.de</t>
+          <t>Schulleitung3671@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25583,12 +25583,12 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Schule(4261)@schule.hessen.de</t>
+          <t>Schule4261@schule.hessen.de</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>Schulleitung(4261)@schule.hessen.de</t>
+          <t>Schulleitung4261@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25613,12 +25613,12 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>Schule(4246)@schule.hessen.de</t>
+          <t>Schule4246@schule.hessen.de</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>Schulleitung(4246)@schule.hessen.de</t>
+          <t>Schulleitung4246@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25643,12 +25643,12 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Schule(3998)@schule.hessen.de</t>
+          <t>Schule3998@schule.hessen.de</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>Schulleitung(3998)@schule.hessen.de</t>
+          <t>Schulleitung3998@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25673,12 +25673,12 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Schule(3631)@schule.hessen.de</t>
+          <t>Schule3631@schule.hessen.de</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>Schulleitung(3631)@schule.hessen.de</t>
+          <t>Schulleitung3631@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25703,12 +25703,12 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>Schule(4013)@schule.hessen.de</t>
+          <t>Schule4013@schule.hessen.de</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>Schulleitung(4013)@schule.hessen.de</t>
+          <t>Schulleitung4013@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25733,12 +25733,12 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>Schule(7354)@schule.hessen.de</t>
+          <t>Schule7354@schule.hessen.de</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>Schulleitung(7354)@schule.hessen.de</t>
+          <t>Schulleitung7354@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25763,12 +25763,12 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Schule(7350)@schule.hessen.de</t>
+          <t>Schule7350@schule.hessen.de</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>Schulleitung(7350)@schule.hessen.de</t>
+          <t>Schulleitung7350@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25793,12 +25793,12 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>Schule(7340)@schule.hessen.de</t>
+          <t>Schule7340@schule.hessen.de</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>Schulleitung(7340)@schule.hessen.de</t>
+          <t>Schulleitung7340@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25823,12 +25823,12 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Schule(7403)@schule.hessen.de</t>
+          <t>Schule7403@schule.hessen.de</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>Schulleitung(7403)@schule.hessen.de</t>
+          <t>Schulleitung7403@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25853,12 +25853,12 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Schule(7355)@schule.hessen.de</t>
+          <t>Schule7355@schule.hessen.de</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>Schulleitung(7355)@schule.hessen.de</t>
+          <t>Schulleitung7355@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25883,12 +25883,12 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>Schule(7593)@schule.hessen.de</t>
+          <t>Schule7593@schule.hessen.de</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>Schulleitung(7593)@schule.hessen.de</t>
+          <t>Schulleitung7593@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25913,12 +25913,12 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>Schule(7351)@schule.hessen.de</t>
+          <t>Schule7351@schule.hessen.de</t>
         </is>
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>Schulleitung(7351)@schule.hessen.de</t>
+          <t>Schulleitung7351@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25943,12 +25943,12 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>Schule(7588)@schule.hessen.de</t>
+          <t>Schule7588@schule.hessen.de</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Schulleitung(7588)@schule.hessen.de</t>
+          <t>Schulleitung7588@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -25973,12 +25973,12 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>Schule(7404)@schule.hessen.de</t>
+          <t>Schule7404@schule.hessen.de</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Schulleitung(7404)@schule.hessen.de</t>
+          <t>Schulleitung7404@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26003,12 +26003,12 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>Schule(7406)@schule.hessen.de</t>
+          <t>Schule7406@schule.hessen.de</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>Schulleitung(7406)@schule.hessen.de</t>
+          <t>Schulleitung7406@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26033,12 +26033,12 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>Schule(7646)@schule.hessen.de</t>
+          <t>Schule7646@schule.hessen.de</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>Schulleitung(7646)@schule.hessen.de</t>
+          <t>Schulleitung7646@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26063,12 +26063,12 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>Schule(7388)@schule.hessen.de</t>
+          <t>Schule7388@schule.hessen.de</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>Schulleitung(7388)@schule.hessen.de</t>
+          <t>Schulleitung7388@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26093,12 +26093,12 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Schule(7660)@schule.hessen.de</t>
+          <t>Schule7660@schule.hessen.de</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>Schulleitung(7660)@schule.hessen.de</t>
+          <t>Schulleitung7660@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26123,12 +26123,12 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>Schule(7650)@schule.hessen.de</t>
+          <t>Schule7650@schule.hessen.de</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>Schulleitung(7650)@schule.hessen.de</t>
+          <t>Schulleitung7650@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26153,12 +26153,12 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>Schule(7109)@schule.hessen.de</t>
+          <t>Schule7109@schule.hessen.de</t>
         </is>
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>Schulleitung(7109)@schule.hessen.de</t>
+          <t>Schulleitung7109@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26183,12 +26183,12 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>Schule(7135)@schule.hessen.de</t>
+          <t>Schule7135@schule.hessen.de</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>Schulleitung(7135)@schule.hessen.de</t>
+          <t>Schulleitung7135@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26213,12 +26213,12 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>Schule(7132)@schule.hessen.de</t>
+          <t>Schule7132@schule.hessen.de</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Schulleitung(7132)@schule.hessen.de</t>
+          <t>Schulleitung7132@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26243,12 +26243,12 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Schule(7112)@schule.hessen.de</t>
+          <t>Schule7112@schule.hessen.de</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>Schulleitung(7112)@schule.hessen.de</t>
+          <t>Schulleitung7112@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26273,12 +26273,12 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>Schule(7382)@schule.hessen.de</t>
+          <t>Schule7382@schule.hessen.de</t>
         </is>
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>Schulleitung(7382)@schule.hessen.de</t>
+          <t>Schulleitung7382@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26303,12 +26303,12 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Schule(7662)@schule.hessen.de</t>
+          <t>Schule7662@schule.hessen.de</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>Schulleitung(7662)@schule.hessen.de</t>
+          <t>Schulleitung7662@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26333,12 +26333,12 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>Schule(3592)@schule.hessen.de</t>
+          <t>Schule3592@schule.hessen.de</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>Schulleitung(3592)@schule.hessen.de</t>
+          <t>Schulleitung3592@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26363,12 +26363,12 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>Schule(4143)@schule.hessen.de</t>
+          <t>Schule4143@schule.hessen.de</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>Schulleitung(4143)@schule.hessen.de</t>
+          <t>Schulleitung4143@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26393,12 +26393,12 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>Schule(3980)@schule.hessen.de</t>
+          <t>Schule3980@schule.hessen.de</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>Schulleitung(3980)@schule.hessen.de</t>
+          <t>Schulleitung3980@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26423,12 +26423,12 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>Schule(4158)@schule.hessen.de</t>
+          <t>Schule4158@schule.hessen.de</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>Schulleitung(4158)@schule.hessen.de</t>
+          <t>Schulleitung4158@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26453,12 +26453,12 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>Schule(4161)@schule.hessen.de</t>
+          <t>Schule4161@schule.hessen.de</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>Schulleitung(4161)@schule.hessen.de</t>
+          <t>Schulleitung4161@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26483,12 +26483,12 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>Schule(3912)@schule.hessen.de</t>
+          <t>Schule3912@schule.hessen.de</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>Schulleitung(3912)@schule.hessen.de</t>
+          <t>Schulleitung3912@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26513,12 +26513,12 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>Schule(4155)@schule.hessen.de</t>
+          <t>Schule4155@schule.hessen.de</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Schulleitung(4155)@schule.hessen.de</t>
+          <t>Schulleitung4155@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26543,12 +26543,12 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>Schule(4148)@schule.hessen.de</t>
+          <t>Schule4148@schule.hessen.de</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>Schulleitung(4148)@schule.hessen.de</t>
+          <t>Schulleitung4148@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26573,12 +26573,12 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>Schule(3897)@schule.hessen.de</t>
+          <t>Schule3897@schule.hessen.de</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>Schulleitung(3897)@schule.hessen.de</t>
+          <t>Schulleitung3897@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26603,12 +26603,12 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>Schule(4142)@schule.hessen.de</t>
+          <t>Schule4142@schule.hessen.de</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>Schulleitung(4142)@schule.hessen.de</t>
+          <t>Schulleitung4142@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26633,12 +26633,12 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>Schule(3551)@schule.hessen.de</t>
+          <t>Schule3551@schule.hessen.de</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>Schulleitung(3551)@schule.hessen.de</t>
+          <t>Schulleitung3551@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26663,12 +26663,12 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>Schule(3993)@schule.hessen.de</t>
+          <t>Schule3993@schule.hessen.de</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>Schulleitung(3993)@schule.hessen.de</t>
+          <t>Schulleitung3993@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26693,12 +26693,12 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>Schule(3961)@schule.hessen.de</t>
+          <t>Schule3961@schule.hessen.de</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>Schulleitung(3961)@schule.hessen.de</t>
+          <t>Schulleitung3961@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26723,12 +26723,12 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>Schule(3558)@schule.hessen.de</t>
+          <t>Schule3558@schule.hessen.de</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>Schulleitung(3558)@schule.hessen.de</t>
+          <t>Schulleitung3558@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26753,12 +26753,12 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>Schule(4160)@schule.hessen.de</t>
+          <t>Schule4160@schule.hessen.de</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>Schulleitung(4160)@schule.hessen.de</t>
+          <t>Schulleitung4160@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26783,12 +26783,12 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>Schule(3891)@schule.hessen.de</t>
+          <t>Schule3891@schule.hessen.de</t>
         </is>
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>Schulleitung(3891)@schule.hessen.de</t>
+          <t>Schulleitung3891@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26813,12 +26813,12 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>Schule(4173)@schule.hessen.de</t>
+          <t>Schule4173@schule.hessen.de</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>Schulleitung(4173)@schule.hessen.de</t>
+          <t>Schulleitung4173@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26843,12 +26843,12 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>Schule(4162)@schule.hessen.de</t>
+          <t>Schule4162@schule.hessen.de</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>Schulleitung(4162)@schule.hessen.de</t>
+          <t>Schulleitung4162@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26873,12 +26873,12 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>Schule(3572)@schule.hessen.de</t>
+          <t>Schule3572@schule.hessen.de</t>
         </is>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>Schulleitung(3572)@schule.hessen.de</t>
+          <t>Schulleitung3572@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26903,12 +26903,12 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>Schule(3578)@schule.hessen.de</t>
+          <t>Schule3578@schule.hessen.de</t>
         </is>
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>Schulleitung(3578)@schule.hessen.de</t>
+          <t>Schulleitung3578@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26933,12 +26933,12 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>Schule(4088)@schule.hessen.de</t>
+          <t>Schule4088@schule.hessen.de</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>Schulleitung(4088)@schule.hessen.de</t>
+          <t>Schulleitung4088@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26963,12 +26963,12 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>Schule(3722)@schule.hessen.de</t>
+          <t>Schule3722@schule.hessen.de</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>Schulleitung(3722)@schule.hessen.de</t>
+          <t>Schulleitung3722@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -26993,12 +26993,12 @@
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>Schule(3698)@schule.hessen.de</t>
+          <t>Schule3698@schule.hessen.de</t>
         </is>
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>Schulleitung(3698)@schule.hessen.de</t>
+          <t>Schulleitung3698@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27023,12 +27023,12 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>Schule(3697)@schule.hessen.de</t>
+          <t>Schule3697@schule.hessen.de</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>Schulleitung(3697)@schule.hessen.de</t>
+          <t>Schulleitung3697@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27053,12 +27053,12 @@
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>Schule(3708)@schule.hessen.de</t>
+          <t>Schule3708@schule.hessen.de</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>Schulleitung(3708)@schule.hessen.de</t>
+          <t>Schulleitung3708@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27083,12 +27083,12 @@
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>Schule(3714)@schule.hessen.de</t>
+          <t>Schule3714@schule.hessen.de</t>
         </is>
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>Schulleitung(3714)@schule.hessen.de</t>
+          <t>Schulleitung3714@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27113,12 +27113,12 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>Schule(4936)@schule.hessen.de</t>
+          <t>Schule4936@schule.hessen.de</t>
         </is>
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>Schulleitung(4936)@schule.hessen.de</t>
+          <t>Schulleitung4936@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27143,12 +27143,12 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>Schule(4931)@schule.hessen.de</t>
+          <t>Schule4931@schule.hessen.de</t>
         </is>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>Schulleitung(4931)@schule.hessen.de</t>
+          <t>Schulleitung4931@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27173,12 +27173,12 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>Schule(3710)@schule.hessen.de</t>
+          <t>Schule3710@schule.hessen.de</t>
         </is>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>Schulleitung(3710)@schule.hessen.de</t>
+          <t>Schulleitung3710@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27203,12 +27203,12 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>Schule(3703)@schule.hessen.de</t>
+          <t>Schule3703@schule.hessen.de</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>Schulleitung(3703)@schule.hessen.de</t>
+          <t>Schulleitung3703@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27233,12 +27233,12 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>Schule(3834)@schule.hessen.de</t>
+          <t>Schule3834@schule.hessen.de</t>
         </is>
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>Schulleitung(3834)@schule.hessen.de</t>
+          <t>Schulleitung3834@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27263,12 +27263,12 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>Schule(3849)@schule.hessen.de</t>
+          <t>Schule3849@schule.hessen.de</t>
         </is>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>Schulleitung(3849)@schule.hessen.de</t>
+          <t>Schulleitung3849@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27293,12 +27293,12 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>Schule(3845)@schule.hessen.de</t>
+          <t>Schule3845@schule.hessen.de</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>Schulleitung(3845)@schule.hessen.de</t>
+          <t>Schulleitung3845@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27323,12 +27323,12 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>Schule(4939)@schule.hessen.de</t>
+          <t>Schule4939@schule.hessen.de</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>Schulleitung(4939)@schule.hessen.de</t>
+          <t>Schulleitung4939@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27353,12 +27353,12 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>Schule(3236)@schule.hessen.de</t>
+          <t>Schule3236@schule.hessen.de</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>Schulleitung(3236)@schule.hessen.de</t>
+          <t>Schulleitung3236@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27383,12 +27383,12 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>Schule(3843)@schule.hessen.de</t>
+          <t>Schule3843@schule.hessen.de</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Schulleitung(3843)@schule.hessen.de</t>
+          <t>Schulleitung3843@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27413,12 +27413,12 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>Schule(3840)@schule.hessen.de</t>
+          <t>Schule3840@schule.hessen.de</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>Schulleitung(3840)@schule.hessen.de</t>
+          <t>Schulleitung3840@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27443,12 +27443,12 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>Schule(4212)@schule.hessen.de</t>
+          <t>Schule4212@schule.hessen.de</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>Schulleitung(4212)@schule.hessen.de</t>
+          <t>Schulleitung4212@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27473,12 +27473,12 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>Schule(3826)@schule.hessen.de</t>
+          <t>Schule3826@schule.hessen.de</t>
         </is>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>Schulleitung(3826)@schule.hessen.de</t>
+          <t>Schulleitung3826@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27503,12 +27503,12 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>Schule(3239)@schule.hessen.de</t>
+          <t>Schule3239@schule.hessen.de</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Schulleitung(3239)@schule.hessen.de</t>
+          <t>Schulleitung3239@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27533,12 +27533,12 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>Schule(7419)@schule.hessen.de</t>
+          <t>Schule7419@schule.hessen.de</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>Schulleitung(7419)@schule.hessen.de</t>
+          <t>Schulleitung7419@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27563,12 +27563,12 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>Schule(7411)@schule.hessen.de</t>
+          <t>Schule7411@schule.hessen.de</t>
         </is>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>Schulleitung(7411)@schule.hessen.de</t>
+          <t>Schulleitung7411@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27593,12 +27593,12 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>Schule(3411)@schule.hessen.de</t>
+          <t>Schule3411@schule.hessen.de</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>Schulleitung(3411)@schule.hessen.de</t>
+          <t>Schulleitung3411@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27623,12 +27623,12 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>Schule(3416)@schule.hessen.de</t>
+          <t>Schule3416@schule.hessen.de</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>Schulleitung(3416)@schule.hessen.de</t>
+          <t>Schulleitung3416@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27653,12 +27653,12 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>Schule(3400)@schule.hessen.de</t>
+          <t>Schule3400@schule.hessen.de</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t>Schulleitung(3400)@schule.hessen.de</t>
+          <t>Schulleitung3400@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27683,12 +27683,12 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>Schule(7430)@schule.hessen.de</t>
+          <t>Schule7430@schule.hessen.de</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Schulleitung(7430)@schule.hessen.de</t>
+          <t>Schulleitung7430@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27713,12 +27713,12 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>Schule(7470)@schule.hessen.de</t>
+          <t>Schule7470@schule.hessen.de</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>Schulleitung(7470)@schule.hessen.de</t>
+          <t>Schulleitung7470@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27743,12 +27743,12 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>Schule(7442)@schule.hessen.de</t>
+          <t>Schule7442@schule.hessen.de</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>Schulleitung(7442)@schule.hessen.de</t>
+          <t>Schulleitung7442@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27773,12 +27773,12 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>Schule(7418)@schule.hessen.de</t>
+          <t>Schule7418@schule.hessen.de</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Schulleitung(7418)@schule.hessen.de</t>
+          <t>Schulleitung7418@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27803,12 +27803,12 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>Schule(3393)@schule.hessen.de</t>
+          <t>Schule3393@schule.hessen.de</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>Schulleitung(3393)@schule.hessen.de</t>
+          <t>Schulleitung3393@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27833,12 +27833,12 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>Schule(3401)@schule.hessen.de</t>
+          <t>Schule3401@schule.hessen.de</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t>Schulleitung(3401)@schule.hessen.de</t>
+          <t>Schulleitung3401@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27863,12 +27863,12 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>Schule(7427)@schule.hessen.de</t>
+          <t>Schule7427@schule.hessen.de</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>Schulleitung(7427)@schule.hessen.de</t>
+          <t>Schulleitung7427@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27893,12 +27893,12 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>Schule(7422)@schule.hessen.de</t>
+          <t>Schule7422@schule.hessen.de</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>Schulleitung(7422)@schule.hessen.de</t>
+          <t>Schulleitung7422@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27923,12 +27923,12 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>Schule(7443)@schule.hessen.de</t>
+          <t>Schule7443@schule.hessen.de</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Schulleitung(7443)@schule.hessen.de</t>
+          <t>Schulleitung7443@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27953,12 +27953,12 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>Schule(7138)@schule.hessen.de</t>
+          <t>Schule7138@schule.hessen.de</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>Schulleitung(7138)@schule.hessen.de</t>
+          <t>Schulleitung7138@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -27983,12 +27983,12 @@
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>Schule(3414)@schule.hessen.de</t>
+          <t>Schule3414@schule.hessen.de</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Schulleitung(3414)@schule.hessen.de</t>
+          <t>Schulleitung3414@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28013,12 +28013,12 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>Schule(7464)@schule.hessen.de</t>
+          <t>Schule7464@schule.hessen.de</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Schulleitung(7464)@schule.hessen.de</t>
+          <t>Schulleitung7464@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28043,12 +28043,12 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>Schule(7417)@schule.hessen.de</t>
+          <t>Schule7417@schule.hessen.de</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Schulleitung(7417)@schule.hessen.de</t>
+          <t>Schulleitung7417@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28073,12 +28073,12 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>Schule(7457)@schule.hessen.de</t>
+          <t>Schule7457@schule.hessen.de</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Schulleitung(7457)@schule.hessen.de</t>
+          <t>Schulleitung7457@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28103,12 +28103,12 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>Schule(7426)@schule.hessen.de</t>
+          <t>Schule7426@schule.hessen.de</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>Schulleitung(7426)@schule.hessen.de</t>
+          <t>Schulleitung7426@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28133,12 +28133,12 @@
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>Schule(4442)@schule.hessen.de</t>
+          <t>Schule4442@schule.hessen.de</t>
         </is>
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t>Schulleitung(4442)@schule.hessen.de</t>
+          <t>Schulleitung4442@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28163,12 +28163,12 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>Schule(4026)@schule.hessen.de</t>
+          <t>Schule4026@schule.hessen.de</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>Schulleitung(4026)@schule.hessen.de</t>
+          <t>Schulleitung4026@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28193,12 +28193,12 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>Schule(4201)@schule.hessen.de</t>
+          <t>Schule4201@schule.hessen.de</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>Schulleitung(4201)@schule.hessen.de</t>
+          <t>Schulleitung4201@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28223,12 +28223,12 @@
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>Schule(4040)@schule.hessen.de</t>
+          <t>Schule4040@schule.hessen.de</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Schulleitung(4040)@schule.hessen.de</t>
+          <t>Schulleitung4040@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28253,12 +28253,12 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>Schule(4249)@schule.hessen.de</t>
+          <t>Schule4249@schule.hessen.de</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t>Schulleitung(4249)@schule.hessen.de</t>
+          <t>Schulleitung4249@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28283,12 +28283,12 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>Schule(4027)@schule.hessen.de</t>
+          <t>Schule4027@schule.hessen.de</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>Schulleitung(4027)@schule.hessen.de</t>
+          <t>Schulleitung4027@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>Schule(4060)@schule.hessen.de</t>
+          <t>Schule4060@schule.hessen.de</t>
         </is>
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t>Schulleitung(4060)@schule.hessen.de</t>
+          <t>Schulleitung4060@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28343,12 +28343,12 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>Schule(3537)@schule.hessen.de</t>
+          <t>Schule3537@schule.hessen.de</t>
         </is>
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Schulleitung(3537)@schule.hessen.de</t>
+          <t>Schulleitung3537@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28373,12 +28373,12 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>Schule(4036)@schule.hessen.de</t>
+          <t>Schule4036@schule.hessen.de</t>
         </is>
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Schulleitung(4036)@schule.hessen.de</t>
+          <t>Schulleitung4036@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28403,12 +28403,12 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>Schule(4023)@schule.hessen.de</t>
+          <t>Schule4023@schule.hessen.de</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Schulleitung(4023)@schule.hessen.de</t>
+          <t>Schulleitung4023@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28433,12 +28433,12 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>Schule(4209)@schule.hessen.de</t>
+          <t>Schule4209@schule.hessen.de</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t>Schulleitung(4209)@schule.hessen.de</t>
+          <t>Schulleitung4209@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28463,12 +28463,12 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>Schule(4056)@schule.hessen.de</t>
+          <t>Schule4056@schule.hessen.de</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t>Schulleitung(4056)@schule.hessen.de</t>
+          <t>Schulleitung4056@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28493,12 +28493,12 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>Schule(3255)@schule.hessen.de</t>
+          <t>Schule3255@schule.hessen.de</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t>Schulleitung(3255)@schule.hessen.de</t>
+          <t>Schulleitung3255@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28523,12 +28523,12 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>Schule(3242)@schule.hessen.de</t>
+          <t>Schule3242@schule.hessen.de</t>
         </is>
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t>Schulleitung(3242)@schule.hessen.de</t>
+          <t>Schulleitung3242@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28553,12 +28553,12 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>Schule(3246)@schule.hessen.de</t>
+          <t>Schule3246@schule.hessen.de</t>
         </is>
       </c>
       <c r="K539" t="inlineStr">
         <is>
-          <t>Schulleitung(3246)@schule.hessen.de</t>
+          <t>Schulleitung3246@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28583,12 +28583,12 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>Schule(4032)@schule.hessen.de</t>
+          <t>Schule4032@schule.hessen.de</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>Schulleitung(4032)@schule.hessen.de</t>
+          <t>Schulleitung4032@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28613,12 +28613,12 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>Schule(4251)@schule.hessen.de</t>
+          <t>Schule4251@schule.hessen.de</t>
         </is>
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t>Schulleitung(4251)@schule.hessen.de</t>
+          <t>Schulleitung4251@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28643,12 +28643,12 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>Schule(3243)@schule.hessen.de</t>
+          <t>Schule3243@schule.hessen.de</t>
         </is>
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t>Schulleitung(3243)@schule.hessen.de</t>
+          <t>Schulleitung3243@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28673,12 +28673,12 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>Schule(4278)@schule.hessen.de</t>
+          <t>Schule4278@schule.hessen.de</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>Schulleitung(4278)@schule.hessen.de</t>
+          <t>Schulleitung4278@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28703,12 +28703,12 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>Schule(4030)@schule.hessen.de</t>
+          <t>Schule4030@schule.hessen.de</t>
         </is>
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t>Schulleitung(4030)@schule.hessen.de</t>
+          <t>Schulleitung4030@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28733,12 +28733,12 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>Schule(4110)@schule.hessen.de</t>
+          <t>Schule4110@schule.hessen.de</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Schulleitung(4110)@schule.hessen.de</t>
+          <t>Schulleitung4110@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28763,12 +28763,12 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>Schule(3196)@schule.hessen.de</t>
+          <t>Schule3196@schule.hessen.de</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Schulleitung(3196)@schule.hessen.de</t>
+          <t>Schulleitung3196@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28793,12 +28793,12 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>Schule(3188)@schule.hessen.de</t>
+          <t>Schule3188@schule.hessen.de</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>Schulleitung(3188)@schule.hessen.de</t>
+          <t>Schulleitung3188@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28823,12 +28823,12 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>Schule(3187)@schule.hessen.de</t>
+          <t>Schule3187@schule.hessen.de</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t>Schulleitung(3187)@schule.hessen.de</t>
+          <t>Schulleitung3187@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28853,12 +28853,12 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>Schule(3293)@schule.hessen.de</t>
+          <t>Schule3293@schule.hessen.de</t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>Schulleitung(3293)@schule.hessen.de</t>
+          <t>Schulleitung3293@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28883,12 +28883,12 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>Schule(4109)@schule.hessen.de</t>
+          <t>Schule4109@schule.hessen.de</t>
         </is>
       </c>
       <c r="K550" t="inlineStr">
         <is>
-          <t>Schulleitung(4109)@schule.hessen.de</t>
+          <t>Schulleitung4109@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28913,12 +28913,12 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>Schule(4111)@schule.hessen.de</t>
+          <t>Schule4111@schule.hessen.de</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t>Schulleitung(4111)@schule.hessen.de</t>
+          <t>Schulleitung4111@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28943,12 +28943,12 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>Schule(4116)@schule.hessen.de</t>
+          <t>Schule4116@schule.hessen.de</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>Schulleitung(4116)@schule.hessen.de</t>
+          <t>Schulleitung4116@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -28973,12 +28973,12 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>Schule(3184)@schule.hessen.de</t>
+          <t>Schule3184@schule.hessen.de</t>
         </is>
       </c>
       <c r="K553" t="inlineStr">
         <is>
-          <t>Schulleitung(3184)@schule.hessen.de</t>
+          <t>Schulleitung3184@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29003,12 +29003,12 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>Schule(4256)@schule.hessen.de</t>
+          <t>Schule4256@schule.hessen.de</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
         <is>
-          <t>Schulleitung(4256)@schule.hessen.de</t>
+          <t>Schulleitung4256@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29033,12 +29033,12 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>Schule(3286)@schule.hessen.de</t>
+          <t>Schule3286@schule.hessen.de</t>
         </is>
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>Schulleitung(3286)@schule.hessen.de</t>
+          <t>Schulleitung3286@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29063,12 +29063,12 @@
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>Schule(3259)@schule.hessen.de</t>
+          <t>Schule3259@schule.hessen.de</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t>Schulleitung(3259)@schule.hessen.de</t>
+          <t>Schulleitung3259@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29093,12 +29093,12 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>Schule(4125)@schule.hessen.de</t>
+          <t>Schule4125@schule.hessen.de</t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t>Schulleitung(4125)@schule.hessen.de</t>
+          <t>Schulleitung4125@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29123,12 +29123,12 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>Schule(3186)@schule.hessen.de</t>
+          <t>Schule3186@schule.hessen.de</t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>Schulleitung(3186)@schule.hessen.de</t>
+          <t>Schulleitung3186@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29153,12 +29153,12 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>Schule(3285)@schule.hessen.de</t>
+          <t>Schule3285@schule.hessen.de</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t>Schulleitung(3285)@schule.hessen.de</t>
+          <t>Schulleitung3285@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29183,12 +29183,12 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>Schule(3282)@schule.hessen.de</t>
+          <t>Schule3282@schule.hessen.de</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t>Schulleitung(3282)@schule.hessen.de</t>
+          <t>Schulleitung3282@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29213,12 +29213,12 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>Schule(3277)@schule.hessen.de</t>
+          <t>Schule3277@schule.hessen.de</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t>Schulleitung(3277)@schule.hessen.de</t>
+          <t>Schulleitung3277@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29243,12 +29243,12 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>Schule(3266)@schule.hessen.de</t>
+          <t>Schule3266@schule.hessen.de</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
         <is>
-          <t>Schulleitung(3266)@schule.hessen.de</t>
+          <t>Schulleitung3266@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29273,12 +29273,12 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>Schule(3294)@schule.hessen.de</t>
+          <t>Schule3294@schule.hessen.de</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t>Schulleitung(3294)@schule.hessen.de</t>
+          <t>Schulleitung3294@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29303,12 +29303,12 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>Schule(3271)@schule.hessen.de</t>
+          <t>Schule3271@schule.hessen.de</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>Schulleitung(3271)@schule.hessen.de</t>
+          <t>Schulleitung3271@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29333,12 +29333,12 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>Schule(7516)@schule.hessen.de</t>
+          <t>Schule7516@schule.hessen.de</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>Schulleitung(7516)@schule.hessen.de</t>
+          <t>Schulleitung7516@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29363,12 +29363,12 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>Schule(7490)@schule.hessen.de</t>
+          <t>Schule7490@schule.hessen.de</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t>Schulleitung(7490)@schule.hessen.de</t>
+          <t>Schulleitung7490@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29393,12 +29393,12 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>Schule(7218)@schule.hessen.de</t>
+          <t>Schule7218@schule.hessen.de</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>Schulleitung(7218)@schule.hessen.de</t>
+          <t>Schulleitung7218@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29423,12 +29423,12 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>Schule(7196)@schule.hessen.de</t>
+          <t>Schule7196@schule.hessen.de</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Schulleitung(7196)@schule.hessen.de</t>
+          <t>Schulleitung7196@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29453,12 +29453,12 @@
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>Schule(7475)@schule.hessen.de</t>
+          <t>Schule7475@schule.hessen.de</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t>Schulleitung(7475)@schule.hessen.de</t>
+          <t>Schulleitung7475@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29483,12 +29483,12 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>Schule(7630)@schule.hessen.de</t>
+          <t>Schule7630@schule.hessen.de</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>Schulleitung(7630)@schule.hessen.de</t>
+          <t>Schulleitung7630@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29513,12 +29513,12 @@
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>Schule(7184)@schule.hessen.de</t>
+          <t>Schule7184@schule.hessen.de</t>
         </is>
       </c>
       <c r="K571" t="inlineStr">
         <is>
-          <t>Schulleitung(7184)@schule.hessen.de</t>
+          <t>Schulleitung7184@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29543,12 +29543,12 @@
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>Schule(7232)@schule.hessen.de</t>
+          <t>Schule7232@schule.hessen.de</t>
         </is>
       </c>
       <c r="K572" t="inlineStr">
         <is>
-          <t>Schulleitung(7232)@schule.hessen.de</t>
+          <t>Schulleitung7232@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29573,12 +29573,12 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>Schule(7186)@schule.hessen.de</t>
+          <t>Schule7186@schule.hessen.de</t>
         </is>
       </c>
       <c r="K573" t="inlineStr">
         <is>
-          <t>Schulleitung(7186)@schule.hessen.de</t>
+          <t>Schulleitung7186@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29603,12 +29603,12 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>Schule(7621)@schule.hessen.de</t>
+          <t>Schule7621@schule.hessen.de</t>
         </is>
       </c>
       <c r="K574" t="inlineStr">
         <is>
-          <t>Schulleitung(7621)@schule.hessen.de</t>
+          <t>Schulleitung7621@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29633,12 +29633,12 @@
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>Schule(7221)@schule.hessen.de</t>
+          <t>Schule7221@schule.hessen.de</t>
         </is>
       </c>
       <c r="K575" t="inlineStr">
         <is>
-          <t>Schulleitung(7221)@schule.hessen.de</t>
+          <t>Schulleitung7221@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29663,12 +29663,12 @@
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>Schule(7568)@schule.hessen.de</t>
+          <t>Schule7568@schule.hessen.de</t>
         </is>
       </c>
       <c r="K576" t="inlineStr">
         <is>
-          <t>Schulleitung(7568)@schule.hessen.de</t>
+          <t>Schulleitung7568@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29693,12 +29693,12 @@
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>Schule(7173)@schule.hessen.de</t>
+          <t>Schule7173@schule.hessen.de</t>
         </is>
       </c>
       <c r="K577" t="inlineStr">
         <is>
-          <t>Schulleitung(7173)@schule.hessen.de</t>
+          <t>Schulleitung7173@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29723,12 +29723,12 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>Schule(7679)@schule.hessen.de</t>
+          <t>Schule7679@schule.hessen.de</t>
         </is>
       </c>
       <c r="K578" t="inlineStr">
         <is>
-          <t>Schulleitung(7679)@schule.hessen.de</t>
+          <t>Schulleitung7679@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29753,12 +29753,12 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>Schule(7664)@schule.hessen.de</t>
+          <t>Schule7664@schule.hessen.de</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
         <is>
-          <t>Schulleitung(7664)@schule.hessen.de</t>
+          <t>Schulleitung7664@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29783,12 +29783,12 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>Schule(7670)@schule.hessen.de</t>
+          <t>Schule7670@schule.hessen.de</t>
         </is>
       </c>
       <c r="K580" t="inlineStr">
         <is>
-          <t>Schulleitung(7670)@schule.hessen.de</t>
+          <t>Schulleitung7670@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29813,12 +29813,12 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>Schule(7556)@schule.hessen.de</t>
+          <t>Schule7556@schule.hessen.de</t>
         </is>
       </c>
       <c r="K581" t="inlineStr">
         <is>
-          <t>Schulleitung(7556)@schule.hessen.de</t>
+          <t>Schulleitung7556@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29843,12 +29843,12 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>Schule(7205)@schule.hessen.de</t>
+          <t>Schule7205@schule.hessen.de</t>
         </is>
       </c>
       <c r="K582" t="inlineStr">
         <is>
-          <t>Schulleitung(7205)@schule.hessen.de</t>
+          <t>Schulleitung7205@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29873,12 +29873,12 @@
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>Schule(7216)@schule.hessen.de</t>
+          <t>Schule7216@schule.hessen.de</t>
         </is>
       </c>
       <c r="K583" t="inlineStr">
         <is>
-          <t>Schulleitung(7216)@schule.hessen.de</t>
+          <t>Schulleitung7216@schule.hessen.de</t>
         </is>
       </c>
     </row>
@@ -29903,12 +29903,12 @@
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>Schule(7482)@schule.hessen.de</t>
+          <t>Schule7482@schule.hessen.de</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
         <is>
-          <t>Schulleitung(7482)@schule.hessen.de</t>
+          <t>Schulleitung7482@schule.hessen.de</t>
         </is>
       </c>
     </row>
